--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -8188,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="D290" t="s">
         <v>292</v>
@@ -8216,7 +8216,7 @@
         <v>3</v>
       </c>
       <c r="C292">
-        <v>4950</v>
+        <v>4920</v>
       </c>
       <c r="D292" t="s">
         <v>294</v>
@@ -8230,7 +8230,7 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>4890</v>
+        <v>4870</v>
       </c>
       <c r="D293" t="s">
         <v>295</v>
@@ -8244,7 +8244,7 @@
         <v>5</v>
       </c>
       <c r="C294">
-        <v>4830</v>
+        <v>4820</v>
       </c>
       <c r="D294" t="s">
         <v>296</v>
@@ -8258,7 +8258,7 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>4780</v>
+        <v>4770</v>
       </c>
       <c r="D295" t="s">
         <v>297</v>
@@ -8272,7 +8272,7 @@
         <v>7</v>
       </c>
       <c r="C296">
-        <v>4740</v>
+        <v>4720</v>
       </c>
       <c r="D296" t="s">
         <v>298</v>
@@ -8286,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="C297">
-        <v>4710</v>
+        <v>4690</v>
       </c>
       <c r="D297" t="s">
         <v>299</v>
@@ -8300,7 +8300,7 @@
         <v>9</v>
       </c>
       <c r="C298">
-        <v>4680</v>
+        <v>4640</v>
       </c>
       <c r="D298" t="s">
         <v>300</v>
@@ -8314,7 +8314,7 @@
         <v>10</v>
       </c>
       <c r="C299">
-        <v>4670</v>
+        <v>4610</v>
       </c>
       <c r="D299" t="s">
         <v>301</v>
@@ -8328,7 +8328,7 @@
         <v>11</v>
       </c>
       <c r="C300">
-        <v>4660</v>
+        <v>4590</v>
       </c>
       <c r="D300" t="s">
         <v>302</v>
@@ -8342,7 +8342,7 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>4650</v>
+        <v>4560</v>
       </c>
       <c r="D301" t="s">
         <v>303</v>
@@ -8356,7 +8356,7 @@
         <v>13</v>
       </c>
       <c r="C302">
-        <v>4650</v>
+        <v>4540</v>
       </c>
       <c r="D302" t="s">
         <v>304</v>
@@ -8370,7 +8370,7 @@
         <v>14</v>
       </c>
       <c r="C303">
-        <v>4650</v>
+        <v>4530</v>
       </c>
       <c r="D303" t="s">
         <v>305</v>
@@ -8384,7 +8384,7 @@
         <v>15</v>
       </c>
       <c r="C304">
-        <v>4660</v>
+        <v>4530</v>
       </c>
       <c r="D304" t="s">
         <v>306</v>
@@ -8398,7 +8398,7 @@
         <v>16</v>
       </c>
       <c r="C305">
-        <v>4670</v>
+        <v>4520</v>
       </c>
       <c r="D305" t="s">
         <v>307</v>
@@ -8412,7 +8412,7 @@
         <v>17</v>
       </c>
       <c r="C306">
-        <v>4690</v>
+        <v>4500</v>
       </c>
       <c r="D306" t="s">
         <v>308</v>
@@ -8426,7 +8426,7 @@
         <v>18</v>
       </c>
       <c r="C307">
-        <v>4700</v>
+        <v>4490</v>
       </c>
       <c r="D307" t="s">
         <v>309</v>
@@ -8440,7 +8440,7 @@
         <v>19</v>
       </c>
       <c r="C308">
-        <v>4700</v>
+        <v>4500</v>
       </c>
       <c r="D308" t="s">
         <v>310</v>
@@ -8454,7 +8454,7 @@
         <v>20</v>
       </c>
       <c r="C309">
-        <v>4710</v>
+        <v>4510</v>
       </c>
       <c r="D309" t="s">
         <v>311</v>
@@ -8468,7 +8468,7 @@
         <v>21</v>
       </c>
       <c r="C310">
-        <v>4710</v>
+        <v>4550</v>
       </c>
       <c r="D310" t="s">
         <v>312</v>
@@ -8482,7 +8482,7 @@
         <v>22</v>
       </c>
       <c r="C311">
-        <v>4710</v>
+        <v>4570</v>
       </c>
       <c r="D311" t="s">
         <v>313</v>
@@ -8496,7 +8496,7 @@
         <v>23</v>
       </c>
       <c r="C312">
-        <v>4710</v>
+        <v>4590</v>
       </c>
       <c r="D312" t="s">
         <v>314</v>
@@ -8510,7 +8510,7 @@
         <v>24</v>
       </c>
       <c r="C313">
-        <v>4710</v>
+        <v>4610</v>
       </c>
       <c r="D313" t="s">
         <v>315</v>
@@ -8524,7 +8524,7 @@
         <v>25</v>
       </c>
       <c r="C314">
-        <v>4720</v>
+        <v>4650</v>
       </c>
       <c r="D314" t="s">
         <v>316</v>
@@ -8538,7 +8538,7 @@
         <v>26</v>
       </c>
       <c r="C315">
-        <v>4730</v>
+        <v>4670</v>
       </c>
       <c r="D315" t="s">
         <v>317</v>
@@ -8552,7 +8552,7 @@
         <v>27</v>
       </c>
       <c r="C316">
-        <v>4750</v>
+        <v>4690</v>
       </c>
       <c r="D316" t="s">
         <v>318</v>
@@ -8566,7 +8566,7 @@
         <v>28</v>
       </c>
       <c r="C317">
-        <v>4780</v>
+        <v>4710</v>
       </c>
       <c r="D317" t="s">
         <v>319</v>
@@ -8580,7 +8580,7 @@
         <v>29</v>
       </c>
       <c r="C318">
-        <v>4800</v>
+        <v>4740</v>
       </c>
       <c r="D318" t="s">
         <v>320</v>
@@ -8594,7 +8594,7 @@
         <v>30</v>
       </c>
       <c r="C319">
-        <v>4830</v>
+        <v>4760</v>
       </c>
       <c r="D319" t="s">
         <v>321</v>
@@ -8608,7 +8608,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>4840</v>
+        <v>4760</v>
       </c>
       <c r="D320" t="s">
         <v>322</v>
@@ -8622,7 +8622,7 @@
         <v>32</v>
       </c>
       <c r="C321">
-        <v>4850</v>
+        <v>4740</v>
       </c>
       <c r="D321" t="s">
         <v>323</v>
@@ -8636,7 +8636,7 @@
         <v>33</v>
       </c>
       <c r="C322">
-        <v>4850</v>
+        <v>4720</v>
       </c>
       <c r="D322" t="s">
         <v>324</v>
@@ -8650,7 +8650,7 @@
         <v>34</v>
       </c>
       <c r="C323">
-        <v>4800</v>
+        <v>4690</v>
       </c>
       <c r="D323" t="s">
         <v>325</v>
@@ -8664,7 +8664,7 @@
         <v>35</v>
       </c>
       <c r="C324">
-        <v>4740</v>
+        <v>4640</v>
       </c>
       <c r="D324" t="s">
         <v>326</v>
@@ -8678,7 +8678,7 @@
         <v>36</v>
       </c>
       <c r="C325">
-        <v>4650</v>
+        <v>4550</v>
       </c>
       <c r="D325" t="s">
         <v>327</v>
@@ -8692,7 +8692,7 @@
         <v>37</v>
       </c>
       <c r="C326">
-        <v>4540</v>
+        <v>4370</v>
       </c>
       <c r="D326" t="s">
         <v>328</v>
@@ -8706,7 +8706,7 @@
         <v>38</v>
       </c>
       <c r="C327">
-        <v>4400</v>
+        <v>4210</v>
       </c>
       <c r="D327" t="s">
         <v>329</v>
@@ -8720,7 +8720,7 @@
         <v>39</v>
       </c>
       <c r="C328">
-        <v>4250</v>
+        <v>4060</v>
       </c>
       <c r="D328" t="s">
         <v>330</v>
@@ -8734,7 +8734,7 @@
         <v>40</v>
       </c>
       <c r="C329">
-        <v>4090</v>
+        <v>3920</v>
       </c>
       <c r="D329" t="s">
         <v>331</v>
@@ -8748,7 +8748,7 @@
         <v>41</v>
       </c>
       <c r="C330">
-        <v>3920</v>
+        <v>3790</v>
       </c>
       <c r="D330" t="s">
         <v>332</v>
@@ -8762,7 +8762,7 @@
         <v>42</v>
       </c>
       <c r="C331">
-        <v>3770</v>
+        <v>3660</v>
       </c>
       <c r="D331" t="s">
         <v>333</v>
@@ -8776,7 +8776,7 @@
         <v>43</v>
       </c>
       <c r="C332">
-        <v>3620</v>
+        <v>3500</v>
       </c>
       <c r="D332" t="s">
         <v>334</v>
@@ -8790,7 +8790,7 @@
         <v>44</v>
       </c>
       <c r="C333">
-        <v>3490</v>
+        <v>3370</v>
       </c>
       <c r="D333" t="s">
         <v>335</v>
@@ -8804,7 +8804,7 @@
         <v>45</v>
       </c>
       <c r="C334">
-        <v>3380</v>
+        <v>3220</v>
       </c>
       <c r="D334" t="s">
         <v>336</v>
@@ -8818,7 +8818,7 @@
         <v>46</v>
       </c>
       <c r="C335">
-        <v>3300</v>
+        <v>3110</v>
       </c>
       <c r="D335" t="s">
         <v>337</v>
@@ -8832,7 +8832,7 @@
         <v>47</v>
       </c>
       <c r="C336">
-        <v>3230</v>
+        <v>3050</v>
       </c>
       <c r="D336" t="s">
         <v>338</v>
@@ -8846,7 +8846,7 @@
         <v>48</v>
       </c>
       <c r="C337">
-        <v>3190</v>
+        <v>3020</v>
       </c>
       <c r="D337" t="s">
         <v>339</v>
@@ -8860,7 +8860,7 @@
         <v>49</v>
       </c>
       <c r="C338">
-        <v>3160</v>
+        <v>3000</v>
       </c>
       <c r="D338" t="s">
         <v>340</v>
@@ -8874,7 +8874,7 @@
         <v>50</v>
       </c>
       <c r="C339">
-        <v>3150</v>
+        <v>2990</v>
       </c>
       <c r="D339" t="s">
         <v>341</v>
@@ -8888,7 +8888,7 @@
         <v>51</v>
       </c>
       <c r="C340">
-        <v>3150</v>
+        <v>2990</v>
       </c>
       <c r="D340" t="s">
         <v>342</v>
@@ -8902,7 +8902,7 @@
         <v>52</v>
       </c>
       <c r="C341">
-        <v>3150</v>
+        <v>3020</v>
       </c>
       <c r="D341" t="s">
         <v>343</v>
@@ -8916,7 +8916,7 @@
         <v>53</v>
       </c>
       <c r="C342">
-        <v>3170</v>
+        <v>3050</v>
       </c>
       <c r="D342" t="s">
         <v>344</v>
@@ -8930,7 +8930,7 @@
         <v>54</v>
       </c>
       <c r="C343">
-        <v>3190</v>
+        <v>3080</v>
       </c>
       <c r="D343" t="s">
         <v>345</v>
@@ -8944,7 +8944,7 @@
         <v>55</v>
       </c>
       <c r="C344">
-        <v>3210</v>
+        <v>3110</v>
       </c>
       <c r="D344" t="s">
         <v>346</v>
@@ -8958,7 +8958,7 @@
         <v>56</v>
       </c>
       <c r="C345">
-        <v>3240</v>
+        <v>3160</v>
       </c>
       <c r="D345" t="s">
         <v>347</v>
@@ -8972,7 +8972,7 @@
         <v>57</v>
       </c>
       <c r="C346">
-        <v>3270</v>
+        <v>3210</v>
       </c>
       <c r="D346" t="s">
         <v>348</v>
@@ -8986,7 +8986,7 @@
         <v>58</v>
       </c>
       <c r="C347">
-        <v>3310</v>
+        <v>3270</v>
       </c>
       <c r="D347" t="s">
         <v>349</v>
@@ -9000,7 +9000,7 @@
         <v>59</v>
       </c>
       <c r="C348">
-        <v>3350</v>
+        <v>3330</v>
       </c>
       <c r="D348" t="s">
         <v>350</v>
@@ -9014,7 +9014,7 @@
         <v>60</v>
       </c>
       <c r="C349">
-        <v>3400</v>
+        <v>3390</v>
       </c>
       <c r="D349" t="s">
         <v>351</v>
@@ -9056,7 +9056,7 @@
         <v>63</v>
       </c>
       <c r="C352">
-        <v>3590</v>
+        <v>3580</v>
       </c>
       <c r="D352" t="s">
         <v>354</v>
@@ -9070,7 +9070,7 @@
         <v>64</v>
       </c>
       <c r="C353">
-        <v>3680</v>
+        <v>3660</v>
       </c>
       <c r="D353" t="s">
         <v>355</v>
@@ -9084,7 +9084,7 @@
         <v>65</v>
       </c>
       <c r="C354">
-        <v>3780</v>
+        <v>3750</v>
       </c>
       <c r="D354" t="s">
         <v>356</v>
@@ -9098,7 +9098,7 @@
         <v>66</v>
       </c>
       <c r="C355">
-        <v>3910</v>
+        <v>3870</v>
       </c>
       <c r="D355" t="s">
         <v>357</v>
@@ -9112,7 +9112,7 @@
         <v>67</v>
       </c>
       <c r="C356">
-        <v>4050</v>
+        <v>4010</v>
       </c>
       <c r="D356" t="s">
         <v>358</v>
@@ -9126,7 +9126,7 @@
         <v>68</v>
       </c>
       <c r="C357">
-        <v>4210</v>
+        <v>4170</v>
       </c>
       <c r="D357" t="s">
         <v>359</v>
@@ -9182,7 +9182,7 @@
         <v>72</v>
       </c>
       <c r="C361">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="D361" t="s">
         <v>363</v>
@@ -9196,7 +9196,7 @@
         <v>73</v>
       </c>
       <c r="C362">
-        <v>5070</v>
+        <v>5090</v>
       </c>
       <c r="D362" t="s">
         <v>364</v>
@@ -9238,7 +9238,7 @@
         <v>76</v>
       </c>
       <c r="C365">
-        <v>5520</v>
+        <v>5510</v>
       </c>
       <c r="D365" t="s">
         <v>367</v>
@@ -9252,7 +9252,7 @@
         <v>77</v>
       </c>
       <c r="C366">
-        <v>5650</v>
+        <v>5670</v>
       </c>
       <c r="D366" t="s">
         <v>368</v>
@@ -9266,7 +9266,7 @@
         <v>78</v>
       </c>
       <c r="C367">
-        <v>5780</v>
+        <v>5810</v>
       </c>
       <c r="D367" t="s">
         <v>369</v>
@@ -9280,7 +9280,7 @@
         <v>79</v>
       </c>
       <c r="C368">
-        <v>5900</v>
+        <v>5920</v>
       </c>
       <c r="D368" t="s">
         <v>370</v>
@@ -9294,7 +9294,7 @@
         <v>80</v>
       </c>
       <c r="C369">
-        <v>5980</v>
+        <v>6000</v>
       </c>
       <c r="D369" t="s">
         <v>371</v>
@@ -9308,7 +9308,7 @@
         <v>81</v>
       </c>
       <c r="C370">
-        <v>6030</v>
+        <v>6050</v>
       </c>
       <c r="D370" t="s">
         <v>372</v>
@@ -9322,7 +9322,7 @@
         <v>82</v>
       </c>
       <c r="C371">
-        <v>6050</v>
+        <v>6070</v>
       </c>
       <c r="D371" t="s">
         <v>373</v>
@@ -9336,7 +9336,7 @@
         <v>83</v>
       </c>
       <c r="C372">
-        <v>6050</v>
+        <v>6060</v>
       </c>
       <c r="D372" t="s">
         <v>374</v>
@@ -9350,7 +9350,7 @@
         <v>84</v>
       </c>
       <c r="C373">
-        <v>6000</v>
+        <v>6020</v>
       </c>
       <c r="D373" t="s">
         <v>375</v>
@@ -9364,7 +9364,7 @@
         <v>85</v>
       </c>
       <c r="C374">
-        <v>5850</v>
+        <v>5900</v>
       </c>
       <c r="D374" t="s">
         <v>376</v>
@@ -9378,7 +9378,7 @@
         <v>86</v>
       </c>
       <c r="C375">
-        <v>5700</v>
+        <v>5750</v>
       </c>
       <c r="D375" t="s">
         <v>377</v>
@@ -9392,7 +9392,7 @@
         <v>87</v>
       </c>
       <c r="C376">
-        <v>5580</v>
+        <v>5620</v>
       </c>
       <c r="D376" t="s">
         <v>378</v>
@@ -9406,7 +9406,7 @@
         <v>88</v>
       </c>
       <c r="C377">
-        <v>5540</v>
+        <v>5530</v>
       </c>
       <c r="D377" t="s">
         <v>379</v>
@@ -9420,7 +9420,7 @@
         <v>89</v>
       </c>
       <c r="C378">
-        <v>5430</v>
+        <v>5420</v>
       </c>
       <c r="D378" t="s">
         <v>380</v>
@@ -9434,7 +9434,7 @@
         <v>90</v>
       </c>
       <c r="C379">
-        <v>5320</v>
+        <v>5340</v>
       </c>
       <c r="D379" t="s">
         <v>381</v>
@@ -9448,7 +9448,7 @@
         <v>91</v>
       </c>
       <c r="C380">
-        <v>5150</v>
+        <v>5260</v>
       </c>
       <c r="D380" t="s">
         <v>382</v>
@@ -9462,7 +9462,7 @@
         <v>92</v>
       </c>
       <c r="C381">
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="D381" t="s">
         <v>383</v>
@@ -9476,7 +9476,7 @@
         <v>93</v>
       </c>
       <c r="C382">
-        <v>5020</v>
+        <v>5090</v>
       </c>
       <c r="D382" t="s">
         <v>384</v>
@@ -9490,7 +9490,7 @@
         <v>94</v>
       </c>
       <c r="C383">
-        <v>4980</v>
+        <v>5010</v>
       </c>
       <c r="D383" t="s">
         <v>385</v>
@@ -9504,7 +9504,7 @@
         <v>95</v>
       </c>
       <c r="C384">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="D384" t="s">
         <v>386</v>
@@ -9518,7 +9518,7 @@
         <v>96</v>
       </c>
       <c r="C385">
-        <v>4930</v>
+        <v>4940</v>
       </c>
       <c r="D385" t="s">
         <v>387</v>
@@ -9532,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="C386">
-        <v>4940</v>
+        <v>4920</v>
       </c>
       <c r="D386" t="s">
         <v>388</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1348">
   <si>
     <t>Date</t>
   </si>
@@ -3770,6 +3770,294 @@
   </si>
   <si>
     <t>13.10.202696.0</t>
+  </si>
+  <si>
+    <t>14.10.20261.0</t>
+  </si>
+  <si>
+    <t>14.10.20262.0</t>
+  </si>
+  <si>
+    <t>14.10.20263.0</t>
+  </si>
+  <si>
+    <t>14.10.20264.0</t>
+  </si>
+  <si>
+    <t>14.10.20265.0</t>
+  </si>
+  <si>
+    <t>14.10.20266.0</t>
+  </si>
+  <si>
+    <t>14.10.20267.0</t>
+  </si>
+  <si>
+    <t>14.10.20268.0</t>
+  </si>
+  <si>
+    <t>14.10.20269.0</t>
+  </si>
+  <si>
+    <t>14.10.202610.0</t>
+  </si>
+  <si>
+    <t>14.10.202611.0</t>
+  </si>
+  <si>
+    <t>14.10.202612.0</t>
+  </si>
+  <si>
+    <t>14.10.202613.0</t>
+  </si>
+  <si>
+    <t>14.10.202614.0</t>
+  </si>
+  <si>
+    <t>14.10.202615.0</t>
+  </si>
+  <si>
+    <t>14.10.202616.0</t>
+  </si>
+  <si>
+    <t>14.10.202617.0</t>
+  </si>
+  <si>
+    <t>14.10.202618.0</t>
+  </si>
+  <si>
+    <t>14.10.202619.0</t>
+  </si>
+  <si>
+    <t>14.10.202620.0</t>
+  </si>
+  <si>
+    <t>14.10.202621.0</t>
+  </si>
+  <si>
+    <t>14.10.202622.0</t>
+  </si>
+  <si>
+    <t>14.10.202623.0</t>
+  </si>
+  <si>
+    <t>14.10.202624.0</t>
+  </si>
+  <si>
+    <t>14.10.202625.0</t>
+  </si>
+  <si>
+    <t>14.10.202626.0</t>
+  </si>
+  <si>
+    <t>14.10.202627.0</t>
+  </si>
+  <si>
+    <t>14.10.202628.0</t>
+  </si>
+  <si>
+    <t>14.10.202629.0</t>
+  </si>
+  <si>
+    <t>14.10.202630.0</t>
+  </si>
+  <si>
+    <t>14.10.202631.0</t>
+  </si>
+  <si>
+    <t>14.10.202632.0</t>
+  </si>
+  <si>
+    <t>14.10.202633.0</t>
+  </si>
+  <si>
+    <t>14.10.202634.0</t>
+  </si>
+  <si>
+    <t>14.10.202635.0</t>
+  </si>
+  <si>
+    <t>14.10.202636.0</t>
+  </si>
+  <si>
+    <t>14.10.202637.0</t>
+  </si>
+  <si>
+    <t>14.10.202638.0</t>
+  </si>
+  <si>
+    <t>14.10.202639.0</t>
+  </si>
+  <si>
+    <t>14.10.202640.0</t>
+  </si>
+  <si>
+    <t>14.10.202641.0</t>
+  </si>
+  <si>
+    <t>14.10.202642.0</t>
+  </si>
+  <si>
+    <t>14.10.202643.0</t>
+  </si>
+  <si>
+    <t>14.10.202644.0</t>
+  </si>
+  <si>
+    <t>14.10.202645.0</t>
+  </si>
+  <si>
+    <t>14.10.202646.0</t>
+  </si>
+  <si>
+    <t>14.10.202647.0</t>
+  </si>
+  <si>
+    <t>14.10.202648.0</t>
+  </si>
+  <si>
+    <t>14.10.202649.0</t>
+  </si>
+  <si>
+    <t>14.10.202650.0</t>
+  </si>
+  <si>
+    <t>14.10.202651.0</t>
+  </si>
+  <si>
+    <t>14.10.202652.0</t>
+  </si>
+  <si>
+    <t>14.10.202653.0</t>
+  </si>
+  <si>
+    <t>14.10.202654.0</t>
+  </si>
+  <si>
+    <t>14.10.202655.0</t>
+  </si>
+  <si>
+    <t>14.10.202656.0</t>
+  </si>
+  <si>
+    <t>14.10.202657.0</t>
+  </si>
+  <si>
+    <t>14.10.202658.0</t>
+  </si>
+  <si>
+    <t>14.10.202659.0</t>
+  </si>
+  <si>
+    <t>14.10.202660.0</t>
+  </si>
+  <si>
+    <t>14.10.202661.0</t>
+  </si>
+  <si>
+    <t>14.10.202662.0</t>
+  </si>
+  <si>
+    <t>14.10.202663.0</t>
+  </si>
+  <si>
+    <t>14.10.202664.0</t>
+  </si>
+  <si>
+    <t>14.10.202665.0</t>
+  </si>
+  <si>
+    <t>14.10.202666.0</t>
+  </si>
+  <si>
+    <t>14.10.202667.0</t>
+  </si>
+  <si>
+    <t>14.10.202668.0</t>
+  </si>
+  <si>
+    <t>14.10.202669.0</t>
+  </si>
+  <si>
+    <t>14.10.202670.0</t>
+  </si>
+  <si>
+    <t>14.10.202671.0</t>
+  </si>
+  <si>
+    <t>14.10.202672.0</t>
+  </si>
+  <si>
+    <t>14.10.202673.0</t>
+  </si>
+  <si>
+    <t>14.10.202674.0</t>
+  </si>
+  <si>
+    <t>14.10.202675.0</t>
+  </si>
+  <si>
+    <t>14.10.202676.0</t>
+  </si>
+  <si>
+    <t>14.10.202677.0</t>
+  </si>
+  <si>
+    <t>14.10.202678.0</t>
+  </si>
+  <si>
+    <t>14.10.202679.0</t>
+  </si>
+  <si>
+    <t>14.10.202680.0</t>
+  </si>
+  <si>
+    <t>14.10.202681.0</t>
+  </si>
+  <si>
+    <t>14.10.202682.0</t>
+  </si>
+  <si>
+    <t>14.10.202683.0</t>
+  </si>
+  <si>
+    <t>14.10.202684.0</t>
+  </si>
+  <si>
+    <t>14.10.202685.0</t>
+  </si>
+  <si>
+    <t>14.10.202686.0</t>
+  </si>
+  <si>
+    <t>14.10.202687.0</t>
+  </si>
+  <si>
+    <t>14.10.202688.0</t>
+  </si>
+  <si>
+    <t>14.10.202689.0</t>
+  </si>
+  <si>
+    <t>14.10.202690.0</t>
+  </si>
+  <si>
+    <t>14.10.202691.0</t>
+  </si>
+  <si>
+    <t>14.10.202692.0</t>
+  </si>
+  <si>
+    <t>14.10.202693.0</t>
+  </si>
+  <si>
+    <t>14.10.202694.0</t>
+  </si>
+  <si>
+    <t>14.10.202695.0</t>
+  </si>
+  <si>
+    <t>14.10.202696.0</t>
   </si>
 </sst>
 </file>
@@ -4131,7 +4419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1249"/>
+  <dimension ref="A1:D1345"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9532,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="C386">
-        <v>4920</v>
+        <v>4930</v>
       </c>
       <c r="D386" t="s">
         <v>388</v>
@@ -9546,7 +9834,7 @@
         <v>2</v>
       </c>
       <c r="C387">
-        <v>4900</v>
+        <v>4870</v>
       </c>
       <c r="D387" t="s">
         <v>389</v>
@@ -9560,7 +9848,7 @@
         <v>3</v>
       </c>
       <c r="C388">
-        <v>4840</v>
+        <v>4800</v>
       </c>
       <c r="D388" t="s">
         <v>390</v>
@@ -9574,7 +9862,7 @@
         <v>4</v>
       </c>
       <c r="C389">
-        <v>4770</v>
+        <v>4750</v>
       </c>
       <c r="D389" t="s">
         <v>391</v>
@@ -9588,7 +9876,7 @@
         <v>5</v>
       </c>
       <c r="C390">
-        <v>4720</v>
+        <v>4670</v>
       </c>
       <c r="D390" t="s">
         <v>392</v>
@@ -9602,7 +9890,7 @@
         <v>6</v>
       </c>
       <c r="C391">
-        <v>4680</v>
+        <v>4610</v>
       </c>
       <c r="D391" t="s">
         <v>393</v>
@@ -9616,7 +9904,7 @@
         <v>7</v>
       </c>
       <c r="C392">
-        <v>4650</v>
+        <v>4570</v>
       </c>
       <c r="D392" t="s">
         <v>394</v>
@@ -9630,7 +9918,7 @@
         <v>8</v>
       </c>
       <c r="C393">
-        <v>4630</v>
+        <v>4550</v>
       </c>
       <c r="D393" t="s">
         <v>395</v>
@@ -9644,7 +9932,7 @@
         <v>9</v>
       </c>
       <c r="C394">
-        <v>4610</v>
+        <v>4560</v>
       </c>
       <c r="D394" t="s">
         <v>396</v>
@@ -9658,7 +9946,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>4600</v>
+        <v>4550</v>
       </c>
       <c r="D395" t="s">
         <v>397</v>
@@ -9672,7 +9960,7 @@
         <v>11</v>
       </c>
       <c r="C396">
-        <v>4600</v>
+        <v>4540</v>
       </c>
       <c r="D396" t="s">
         <v>398</v>
@@ -9686,7 +9974,7 @@
         <v>12</v>
       </c>
       <c r="C397">
-        <v>4610</v>
+        <v>4550</v>
       </c>
       <c r="D397" t="s">
         <v>399</v>
@@ -9700,7 +9988,7 @@
         <v>13</v>
       </c>
       <c r="C398">
-        <v>4630</v>
+        <v>4560</v>
       </c>
       <c r="D398" t="s">
         <v>400</v>
@@ -9714,7 +10002,7 @@
         <v>14</v>
       </c>
       <c r="C399">
-        <v>4650</v>
+        <v>4590</v>
       </c>
       <c r="D399" t="s">
         <v>401</v>
@@ -9728,7 +10016,7 @@
         <v>15</v>
       </c>
       <c r="C400">
-        <v>4690</v>
+        <v>4610</v>
       </c>
       <c r="D400" t="s">
         <v>402</v>
@@ -9742,7 +10030,7 @@
         <v>16</v>
       </c>
       <c r="C401">
-        <v>4720</v>
+        <v>4640</v>
       </c>
       <c r="D401" t="s">
         <v>403</v>
@@ -9756,7 +10044,7 @@
         <v>17</v>
       </c>
       <c r="C402">
-        <v>4750</v>
+        <v>4690</v>
       </c>
       <c r="D402" t="s">
         <v>404</v>
@@ -9770,7 +10058,7 @@
         <v>18</v>
       </c>
       <c r="C403">
-        <v>4790</v>
+        <v>4720</v>
       </c>
       <c r="D403" t="s">
         <v>405</v>
@@ -9784,7 +10072,7 @@
         <v>19</v>
       </c>
       <c r="C404">
-        <v>4830</v>
+        <v>4770</v>
       </c>
       <c r="D404" t="s">
         <v>406</v>
@@ -9798,7 +10086,7 @@
         <v>20</v>
       </c>
       <c r="C405">
-        <v>4890</v>
+        <v>4820</v>
       </c>
       <c r="D405" t="s">
         <v>407</v>
@@ -9812,7 +10100,7 @@
         <v>21</v>
       </c>
       <c r="C406">
-        <v>4950</v>
+        <v>4870</v>
       </c>
       <c r="D406" t="s">
         <v>408</v>
@@ -9826,7 +10114,7 @@
         <v>22</v>
       </c>
       <c r="C407">
-        <v>5040</v>
+        <v>4940</v>
       </c>
       <c r="D407" t="s">
         <v>409</v>
@@ -9840,7 +10128,7 @@
         <v>23</v>
       </c>
       <c r="C408">
-        <v>5140</v>
+        <v>5040</v>
       </c>
       <c r="D408" t="s">
         <v>410</v>
@@ -9854,7 +10142,7 @@
         <v>24</v>
       </c>
       <c r="C409">
-        <v>5270</v>
+        <v>5150</v>
       </c>
       <c r="D409" t="s">
         <v>411</v>
@@ -9868,7 +10156,7 @@
         <v>25</v>
       </c>
       <c r="C410">
-        <v>5420</v>
+        <v>5270</v>
       </c>
       <c r="D410" t="s">
         <v>412</v>
@@ -9882,7 +10170,7 @@
         <v>26</v>
       </c>
       <c r="C411">
-        <v>5580</v>
+        <v>5440</v>
       </c>
       <c r="D411" t="s">
         <v>413</v>
@@ -9896,7 +10184,7 @@
         <v>27</v>
       </c>
       <c r="C412">
-        <v>5750</v>
+        <v>5630</v>
       </c>
       <c r="D412" t="s">
         <v>414</v>
@@ -9910,7 +10198,7 @@
         <v>28</v>
       </c>
       <c r="C413">
-        <v>5910</v>
+        <v>5860</v>
       </c>
       <c r="D413" t="s">
         <v>415</v>
@@ -9938,7 +10226,7 @@
         <v>30</v>
       </c>
       <c r="C415">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="D415" t="s">
         <v>417</v>
@@ -9952,7 +10240,7 @@
         <v>31</v>
       </c>
       <c r="C416">
-        <v>6270</v>
+        <v>6200</v>
       </c>
       <c r="D416" t="s">
         <v>418</v>
@@ -9966,7 +10254,7 @@
         <v>32</v>
       </c>
       <c r="C417">
-        <v>6300</v>
+        <v>6180</v>
       </c>
       <c r="D417" t="s">
         <v>419</v>
@@ -9980,7 +10268,7 @@
         <v>33</v>
       </c>
       <c r="C418">
-        <v>6290</v>
+        <v>6170</v>
       </c>
       <c r="D418" t="s">
         <v>420</v>
@@ -9994,7 +10282,7 @@
         <v>34</v>
       </c>
       <c r="C419">
-        <v>6270</v>
+        <v>6150</v>
       </c>
       <c r="D419" t="s">
         <v>421</v>
@@ -10008,7 +10296,7 @@
         <v>35</v>
       </c>
       <c r="C420">
-        <v>6210</v>
+        <v>6100</v>
       </c>
       <c r="D420" t="s">
         <v>422</v>
@@ -10022,7 +10310,7 @@
         <v>36</v>
       </c>
       <c r="C421">
-        <v>6090</v>
+        <v>5980</v>
       </c>
       <c r="D421" t="s">
         <v>423</v>
@@ -10036,7 +10324,7 @@
         <v>37</v>
       </c>
       <c r="C422">
-        <v>5940</v>
+        <v>5770</v>
       </c>
       <c r="D422" t="s">
         <v>424</v>
@@ -10050,7 +10338,7 @@
         <v>38</v>
       </c>
       <c r="C423">
-        <v>5770</v>
+        <v>5600</v>
       </c>
       <c r="D423" t="s">
         <v>425</v>
@@ -10064,7 +10352,7 @@
         <v>39</v>
       </c>
       <c r="C424">
-        <v>5580</v>
+        <v>5410</v>
       </c>
       <c r="D424" t="s">
         <v>426</v>
@@ -10078,7 +10366,7 @@
         <v>40</v>
       </c>
       <c r="C425">
-        <v>5380</v>
+        <v>5220</v>
       </c>
       <c r="D425" t="s">
         <v>427</v>
@@ -10092,7 +10380,7 @@
         <v>41</v>
       </c>
       <c r="C426">
-        <v>5190</v>
+        <v>5060</v>
       </c>
       <c r="D426" t="s">
         <v>428</v>
@@ -10106,7 +10394,7 @@
         <v>42</v>
       </c>
       <c r="C427">
-        <v>5000</v>
+        <v>4870</v>
       </c>
       <c r="D427" t="s">
         <v>429</v>
@@ -10120,7 +10408,7 @@
         <v>43</v>
       </c>
       <c r="C428">
-        <v>4820</v>
+        <v>4710</v>
       </c>
       <c r="D428" t="s">
         <v>430</v>
@@ -10134,7 +10422,7 @@
         <v>44</v>
       </c>
       <c r="C429">
-        <v>4670</v>
+        <v>4560</v>
       </c>
       <c r="D429" t="s">
         <v>431</v>
@@ -10148,7 +10436,7 @@
         <v>45</v>
       </c>
       <c r="C430">
-        <v>4530</v>
+        <v>4410</v>
       </c>
       <c r="D430" t="s">
         <v>432</v>
@@ -10162,7 +10450,7 @@
         <v>46</v>
       </c>
       <c r="C431">
-        <v>4420</v>
+        <v>4280</v>
       </c>
       <c r="D431" t="s">
         <v>433</v>
@@ -10176,7 +10464,7 @@
         <v>47</v>
       </c>
       <c r="C432">
-        <v>4330</v>
+        <v>4180</v>
       </c>
       <c r="D432" t="s">
         <v>434</v>
@@ -10190,7 +10478,7 @@
         <v>48</v>
       </c>
       <c r="C433">
-        <v>4260</v>
+        <v>4130</v>
       </c>
       <c r="D433" t="s">
         <v>435</v>
@@ -10204,7 +10492,7 @@
         <v>49</v>
       </c>
       <c r="C434">
-        <v>4220</v>
+        <v>4120</v>
       </c>
       <c r="D434" t="s">
         <v>436</v>
@@ -10218,7 +10506,7 @@
         <v>50</v>
       </c>
       <c r="C435">
-        <v>4200</v>
+        <v>4130</v>
       </c>
       <c r="D435" t="s">
         <v>437</v>
@@ -10232,7 +10520,7 @@
         <v>51</v>
       </c>
       <c r="C436">
-        <v>4190</v>
+        <v>4130</v>
       </c>
       <c r="D436" t="s">
         <v>438</v>
@@ -10246,7 +10534,7 @@
         <v>52</v>
       </c>
       <c r="C437">
-        <v>4200</v>
+        <v>4140</v>
       </c>
       <c r="D437" t="s">
         <v>439</v>
@@ -10260,7 +10548,7 @@
         <v>53</v>
       </c>
       <c r="C438">
-        <v>4220</v>
+        <v>4160</v>
       </c>
       <c r="D438" t="s">
         <v>440</v>
@@ -10274,7 +10562,7 @@
         <v>54</v>
       </c>
       <c r="C439">
-        <v>4240</v>
+        <v>4190</v>
       </c>
       <c r="D439" t="s">
         <v>441</v>
@@ -10288,7 +10576,7 @@
         <v>55</v>
       </c>
       <c r="C440">
-        <v>4260</v>
+        <v>4210</v>
       </c>
       <c r="D440" t="s">
         <v>442</v>
@@ -10302,7 +10590,7 @@
         <v>56</v>
       </c>
       <c r="C441">
-        <v>4290</v>
+        <v>4240</v>
       </c>
       <c r="D441" t="s">
         <v>443</v>
@@ -10316,7 +10604,7 @@
         <v>57</v>
       </c>
       <c r="C442">
-        <v>4320</v>
+        <v>4280</v>
       </c>
       <c r="D442" t="s">
         <v>444</v>
@@ -10330,7 +10618,7 @@
         <v>58</v>
       </c>
       <c r="C443">
-        <v>4360</v>
+        <v>4320</v>
       </c>
       <c r="D443" t="s">
         <v>445</v>
@@ -10344,7 +10632,7 @@
         <v>59</v>
       </c>
       <c r="C444">
-        <v>4400</v>
+        <v>4370</v>
       </c>
       <c r="D444" t="s">
         <v>446</v>
@@ -10358,7 +10646,7 @@
         <v>60</v>
       </c>
       <c r="C445">
-        <v>4460</v>
+        <v>4430</v>
       </c>
       <c r="D445" t="s">
         <v>447</v>
@@ -10372,7 +10660,7 @@
         <v>61</v>
       </c>
       <c r="C446">
-        <v>4520</v>
+        <v>4510</v>
       </c>
       <c r="D446" t="s">
         <v>448</v>
@@ -10400,7 +10688,7 @@
         <v>63</v>
       </c>
       <c r="C448">
-        <v>4700</v>
+        <v>4690</v>
       </c>
       <c r="D448" t="s">
         <v>450</v>
@@ -10428,7 +10716,7 @@
         <v>65</v>
       </c>
       <c r="C450">
-        <v>4920</v>
+        <v>4910</v>
       </c>
       <c r="D450" t="s">
         <v>452</v>
@@ -10442,7 +10730,7 @@
         <v>66</v>
       </c>
       <c r="C451">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="D451" t="s">
         <v>453</v>
@@ -10456,7 +10744,7 @@
         <v>67</v>
       </c>
       <c r="C452">
-        <v>5180</v>
+        <v>5160</v>
       </c>
       <c r="D452" t="s">
         <v>454</v>
@@ -10470,7 +10758,7 @@
         <v>68</v>
       </c>
       <c r="C453">
-        <v>5330</v>
+        <v>5300</v>
       </c>
       <c r="D453" t="s">
         <v>455</v>
@@ -10484,7 +10772,7 @@
         <v>69</v>
       </c>
       <c r="C454">
-        <v>5470</v>
+        <v>5460</v>
       </c>
       <c r="D454" t="s">
         <v>456</v>
@@ -10498,7 +10786,7 @@
         <v>70</v>
       </c>
       <c r="C455">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="D455" t="s">
         <v>457</v>
@@ -10540,7 +10828,7 @@
         <v>73</v>
       </c>
       <c r="C458">
-        <v>6090</v>
+        <v>6120</v>
       </c>
       <c r="D458" t="s">
         <v>460</v>
@@ -10554,7 +10842,7 @@
         <v>74</v>
       </c>
       <c r="C459">
-        <v>6230</v>
+        <v>6280</v>
       </c>
       <c r="D459" t="s">
         <v>461</v>
@@ -10568,7 +10856,7 @@
         <v>75</v>
       </c>
       <c r="C460">
-        <v>6360</v>
+        <v>6430</v>
       </c>
       <c r="D460" t="s">
         <v>462</v>
@@ -10582,7 +10870,7 @@
         <v>76</v>
       </c>
       <c r="C461">
-        <v>6480</v>
+        <v>6570</v>
       </c>
       <c r="D461" t="s">
         <v>463</v>
@@ -10596,7 +10884,7 @@
         <v>77</v>
       </c>
       <c r="C462">
-        <v>6590</v>
+        <v>6700</v>
       </c>
       <c r="D462" t="s">
         <v>464</v>
@@ -10610,7 +10898,7 @@
         <v>78</v>
       </c>
       <c r="C463">
-        <v>6700</v>
+        <v>6810</v>
       </c>
       <c r="D463" t="s">
         <v>465</v>
@@ -10624,7 +10912,7 @@
         <v>79</v>
       </c>
       <c r="C464">
-        <v>6810</v>
+        <v>6910</v>
       </c>
       <c r="D464" t="s">
         <v>466</v>
@@ -10638,7 +10926,7 @@
         <v>80</v>
       </c>
       <c r="C465">
-        <v>6910</v>
+        <v>6980</v>
       </c>
       <c r="D465" t="s">
         <v>467</v>
@@ -10652,7 +10940,7 @@
         <v>81</v>
       </c>
       <c r="C466">
-        <v>7010</v>
+        <v>7020</v>
       </c>
       <c r="D466" t="s">
         <v>468</v>
@@ -10680,7 +10968,7 @@
         <v>83</v>
       </c>
       <c r="C468">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="D468" t="s">
         <v>470</v>
@@ -10694,7 +10982,7 @@
         <v>84</v>
       </c>
       <c r="C469">
-        <v>6940</v>
+        <v>6910</v>
       </c>
       <c r="D469" t="s">
         <v>471</v>
@@ -10708,7 +10996,7 @@
         <v>85</v>
       </c>
       <c r="C470">
-        <v>6720</v>
+        <v>6690</v>
       </c>
       <c r="D470" t="s">
         <v>472</v>
@@ -10722,7 +11010,7 @@
         <v>86</v>
       </c>
       <c r="C471">
-        <v>6480</v>
+        <v>6500</v>
       </c>
       <c r="D471" t="s">
         <v>473</v>
@@ -10736,7 +11024,7 @@
         <v>87</v>
       </c>
       <c r="C472">
-        <v>6360</v>
+        <v>6380</v>
       </c>
       <c r="D472" t="s">
         <v>474</v>
@@ -10750,7 +11038,7 @@
         <v>88</v>
       </c>
       <c r="C473">
-        <v>6310</v>
+        <v>6230</v>
       </c>
       <c r="D473" t="s">
         <v>475</v>
@@ -10764,7 +11052,7 @@
         <v>89</v>
       </c>
       <c r="C474">
-        <v>6220</v>
+        <v>6110</v>
       </c>
       <c r="D474" t="s">
         <v>476</v>
@@ -10778,7 +11066,7 @@
         <v>90</v>
       </c>
       <c r="C475">
-        <v>6100</v>
+        <v>5990</v>
       </c>
       <c r="D475" t="s">
         <v>477</v>
@@ -10792,7 +11080,7 @@
         <v>91</v>
       </c>
       <c r="C476">
-        <v>5880</v>
+        <v>5890</v>
       </c>
       <c r="D476" t="s">
         <v>478</v>
@@ -10806,7 +11094,7 @@
         <v>92</v>
       </c>
       <c r="C477">
-        <v>5800</v>
+        <v>5810</v>
       </c>
       <c r="D477" t="s">
         <v>479</v>
@@ -10820,7 +11108,7 @@
         <v>93</v>
       </c>
       <c r="C478">
-        <v>5750</v>
+        <v>5740</v>
       </c>
       <c r="D478" t="s">
         <v>480</v>
@@ -10834,7 +11122,7 @@
         <v>94</v>
       </c>
       <c r="C479">
-        <v>5670</v>
+        <v>5690</v>
       </c>
       <c r="D479" t="s">
         <v>481</v>
@@ -10862,7 +11150,7 @@
         <v>96</v>
       </c>
       <c r="C481">
-        <v>5530</v>
+        <v>5550</v>
       </c>
       <c r="D481" t="s">
         <v>483</v>
@@ -10876,7 +11164,7 @@
         <v>1</v>
       </c>
       <c r="C482">
-        <v>5490</v>
+        <v>5250</v>
       </c>
       <c r="D482" t="s">
         <v>484</v>
@@ -10890,7 +11178,7 @@
         <v>2</v>
       </c>
       <c r="C483">
-        <v>5460</v>
+        <v>5180</v>
       </c>
       <c r="D483" t="s">
         <v>485</v>
@@ -10904,7 +11192,7 @@
         <v>3</v>
       </c>
       <c r="C484">
-        <v>5390</v>
+        <v>5130</v>
       </c>
       <c r="D484" t="s">
         <v>486</v>
@@ -10918,7 +11206,7 @@
         <v>4</v>
       </c>
       <c r="C485">
-        <v>5310</v>
+        <v>5090</v>
       </c>
       <c r="D485" t="s">
         <v>487</v>
@@ -10932,7 +11220,7 @@
         <v>5</v>
       </c>
       <c r="C486">
-        <v>5270</v>
+        <v>5040</v>
       </c>
       <c r="D486" t="s">
         <v>488</v>
@@ -10946,7 +11234,7 @@
         <v>6</v>
       </c>
       <c r="C487">
-        <v>5240</v>
+        <v>5000</v>
       </c>
       <c r="D487" t="s">
         <v>489</v>
@@ -10960,7 +11248,7 @@
         <v>7</v>
       </c>
       <c r="C488">
-        <v>5210</v>
+        <v>4990</v>
       </c>
       <c r="D488" t="s">
         <v>490</v>
@@ -10974,7 +11262,7 @@
         <v>8</v>
       </c>
       <c r="C489">
-        <v>5190</v>
+        <v>4980</v>
       </c>
       <c r="D489" t="s">
         <v>491</v>
@@ -10988,7 +11276,7 @@
         <v>9</v>
       </c>
       <c r="C490">
-        <v>5160</v>
+        <v>4950</v>
       </c>
       <c r="D490" t="s">
         <v>492</v>
@@ -11002,7 +11290,7 @@
         <v>10</v>
       </c>
       <c r="C491">
-        <v>5140</v>
+        <v>4950</v>
       </c>
       <c r="D491" t="s">
         <v>493</v>
@@ -11016,7 +11304,7 @@
         <v>11</v>
       </c>
       <c r="C492">
-        <v>5130</v>
+        <v>4950</v>
       </c>
       <c r="D492" t="s">
         <v>494</v>
@@ -11030,7 +11318,7 @@
         <v>12</v>
       </c>
       <c r="C493">
-        <v>5120</v>
+        <v>4960</v>
       </c>
       <c r="D493" t="s">
         <v>495</v>
@@ -11044,7 +11332,7 @@
         <v>13</v>
       </c>
       <c r="C494">
-        <v>5120</v>
+        <v>4980</v>
       </c>
       <c r="D494" t="s">
         <v>496</v>
@@ -11058,7 +11346,7 @@
         <v>14</v>
       </c>
       <c r="C495">
-        <v>5110</v>
+        <v>4990</v>
       </c>
       <c r="D495" t="s">
         <v>497</v>
@@ -11072,7 +11360,7 @@
         <v>15</v>
       </c>
       <c r="C496">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="D496" t="s">
         <v>498</v>
@@ -11086,7 +11374,7 @@
         <v>16</v>
       </c>
       <c r="C497">
-        <v>5120</v>
+        <v>5020</v>
       </c>
       <c r="D497" t="s">
         <v>499</v>
@@ -11100,7 +11388,7 @@
         <v>17</v>
       </c>
       <c r="C498">
-        <v>5140</v>
+        <v>5040</v>
       </c>
       <c r="D498" t="s">
         <v>500</v>
@@ -11114,7 +11402,7 @@
         <v>18</v>
       </c>
       <c r="C499">
-        <v>5140</v>
+        <v>5050</v>
       </c>
       <c r="D499" t="s">
         <v>501</v>
@@ -11128,7 +11416,7 @@
         <v>19</v>
       </c>
       <c r="C500">
-        <v>5140</v>
+        <v>5050</v>
       </c>
       <c r="D500" t="s">
         <v>502</v>
@@ -11142,7 +11430,7 @@
         <v>20</v>
       </c>
       <c r="C501">
-        <v>5150</v>
+        <v>5070</v>
       </c>
       <c r="D501" t="s">
         <v>503</v>
@@ -11156,7 +11444,7 @@
         <v>21</v>
       </c>
       <c r="C502">
-        <v>5180</v>
+        <v>5090</v>
       </c>
       <c r="D502" t="s">
         <v>504</v>
@@ -11170,7 +11458,7 @@
         <v>22</v>
       </c>
       <c r="C503">
-        <v>5230</v>
+        <v>5140</v>
       </c>
       <c r="D503" t="s">
         <v>505</v>
@@ -11184,7 +11472,7 @@
         <v>23</v>
       </c>
       <c r="C504">
-        <v>5310</v>
+        <v>5210</v>
       </c>
       <c r="D504" t="s">
         <v>506</v>
@@ -11198,7 +11486,7 @@
         <v>24</v>
       </c>
       <c r="C505">
-        <v>5420</v>
+        <v>5300</v>
       </c>
       <c r="D505" t="s">
         <v>507</v>
@@ -11212,7 +11500,7 @@
         <v>25</v>
       </c>
       <c r="C506">
-        <v>5560</v>
+        <v>5400</v>
       </c>
       <c r="D506" t="s">
         <v>508</v>
@@ -11226,7 +11514,7 @@
         <v>26</v>
       </c>
       <c r="C507">
-        <v>5710</v>
+        <v>5520</v>
       </c>
       <c r="D507" t="s">
         <v>509</v>
@@ -11240,7 +11528,7 @@
         <v>27</v>
       </c>
       <c r="C508">
-        <v>5870</v>
+        <v>5650</v>
       </c>
       <c r="D508" t="s">
         <v>510</v>
@@ -11254,7 +11542,7 @@
         <v>28</v>
       </c>
       <c r="C509">
-        <v>6030</v>
+        <v>5780</v>
       </c>
       <c r="D509" t="s">
         <v>511</v>
@@ -11268,7 +11556,7 @@
         <v>29</v>
       </c>
       <c r="C510">
-        <v>6170</v>
+        <v>5970</v>
       </c>
       <c r="D510" t="s">
         <v>512</v>
@@ -11282,7 +11570,7 @@
         <v>30</v>
       </c>
       <c r="C511">
-        <v>6290</v>
+        <v>6090</v>
       </c>
       <c r="D511" t="s">
         <v>513</v>
@@ -11296,7 +11584,7 @@
         <v>31</v>
       </c>
       <c r="C512">
-        <v>6370</v>
+        <v>6180</v>
       </c>
       <c r="D512" t="s">
         <v>514</v>
@@ -11310,7 +11598,7 @@
         <v>32</v>
       </c>
       <c r="C513">
-        <v>6400</v>
+        <v>6240</v>
       </c>
       <c r="D513" t="s">
         <v>515</v>
@@ -11324,7 +11612,7 @@
         <v>33</v>
       </c>
       <c r="C514">
-        <v>6400</v>
+        <v>6260</v>
       </c>
       <c r="D514" t="s">
         <v>516</v>
@@ -11338,7 +11626,7 @@
         <v>34</v>
       </c>
       <c r="C515">
-        <v>6350</v>
+        <v>6260</v>
       </c>
       <c r="D515" t="s">
         <v>517</v>
@@ -11352,7 +11640,7 @@
         <v>35</v>
       </c>
       <c r="C516">
-        <v>6260</v>
+        <v>6230</v>
       </c>
       <c r="D516" t="s">
         <v>518</v>
@@ -11380,7 +11668,7 @@
         <v>37</v>
       </c>
       <c r="C518">
-        <v>5970</v>
+        <v>6010</v>
       </c>
       <c r="D518" t="s">
         <v>520</v>
@@ -11394,7 +11682,7 @@
         <v>38</v>
       </c>
       <c r="C519">
-        <v>5800</v>
+        <v>5870</v>
       </c>
       <c r="D519" t="s">
         <v>521</v>
@@ -11408,7 +11696,7 @@
         <v>39</v>
       </c>
       <c r="C520">
-        <v>5610</v>
+        <v>5700</v>
       </c>
       <c r="D520" t="s">
         <v>522</v>
@@ -11422,7 +11710,7 @@
         <v>40</v>
       </c>
       <c r="C521">
-        <v>5430</v>
+        <v>5520</v>
       </c>
       <c r="D521" t="s">
         <v>523</v>
@@ -11436,7 +11724,7 @@
         <v>41</v>
       </c>
       <c r="C522">
-        <v>5240</v>
+        <v>5310</v>
       </c>
       <c r="D522" t="s">
         <v>524</v>
@@ -11450,7 +11738,7 @@
         <v>42</v>
       </c>
       <c r="C523">
-        <v>5070</v>
+        <v>5130</v>
       </c>
       <c r="D523" t="s">
         <v>525</v>
@@ -11464,7 +11752,7 @@
         <v>43</v>
       </c>
       <c r="C524">
-        <v>4910</v>
+        <v>4960</v>
       </c>
       <c r="D524" t="s">
         <v>526</v>
@@ -11478,7 +11766,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>4760</v>
+        <v>4810</v>
       </c>
       <c r="D525" t="s">
         <v>527</v>
@@ -11492,7 +11780,7 @@
         <v>45</v>
       </c>
       <c r="C526">
-        <v>4640</v>
+        <v>4650</v>
       </c>
       <c r="D526" t="s">
         <v>528</v>
@@ -11534,7 +11822,7 @@
         <v>48</v>
       </c>
       <c r="C529">
-        <v>4390</v>
+        <v>4370</v>
       </c>
       <c r="D529" t="s">
         <v>531</v>
@@ -11548,7 +11836,7 @@
         <v>49</v>
       </c>
       <c r="C530">
-        <v>4350</v>
+        <v>4320</v>
       </c>
       <c r="D530" t="s">
         <v>532</v>
@@ -11562,7 +11850,7 @@
         <v>50</v>
       </c>
       <c r="C531">
-        <v>4320</v>
+        <v>4300</v>
       </c>
       <c r="D531" t="s">
         <v>533</v>
@@ -11576,7 +11864,7 @@
         <v>51</v>
       </c>
       <c r="C532">
-        <v>4310</v>
+        <v>4300</v>
       </c>
       <c r="D532" t="s">
         <v>534</v>
@@ -11590,7 +11878,7 @@
         <v>52</v>
       </c>
       <c r="C533">
-        <v>4310</v>
+        <v>4300</v>
       </c>
       <c r="D533" t="s">
         <v>535</v>
@@ -11618,7 +11906,7 @@
         <v>54</v>
       </c>
       <c r="C535">
-        <v>4330</v>
+        <v>4340</v>
       </c>
       <c r="D535" t="s">
         <v>537</v>
@@ -11646,7 +11934,7 @@
         <v>56</v>
       </c>
       <c r="C537">
-        <v>4380</v>
+        <v>4390</v>
       </c>
       <c r="D537" t="s">
         <v>539</v>
@@ -11660,7 +11948,7 @@
         <v>57</v>
       </c>
       <c r="C538">
-        <v>4420</v>
+        <v>4430</v>
       </c>
       <c r="D538" t="s">
         <v>540</v>
@@ -11674,7 +11962,7 @@
         <v>58</v>
       </c>
       <c r="C539">
-        <v>4450</v>
+        <v>4470</v>
       </c>
       <c r="D539" t="s">
         <v>541</v>
@@ -11688,7 +11976,7 @@
         <v>59</v>
       </c>
       <c r="C540">
-        <v>4500</v>
+        <v>4510</v>
       </c>
       <c r="D540" t="s">
         <v>542</v>
@@ -11716,7 +12004,7 @@
         <v>61</v>
       </c>
       <c r="C542">
-        <v>4630</v>
+        <v>4620</v>
       </c>
       <c r="D542" t="s">
         <v>544</v>
@@ -11730,7 +12018,7 @@
         <v>62</v>
       </c>
       <c r="C543">
-        <v>4710</v>
+        <v>4690</v>
       </c>
       <c r="D543" t="s">
         <v>545</v>
@@ -11744,7 +12032,7 @@
         <v>63</v>
       </c>
       <c r="C544">
-        <v>4810</v>
+        <v>4750</v>
       </c>
       <c r="D544" t="s">
         <v>546</v>
@@ -11758,7 +12046,7 @@
         <v>64</v>
       </c>
       <c r="C545">
-        <v>4920</v>
+        <v>4840</v>
       </c>
       <c r="D545" t="s">
         <v>547</v>
@@ -11772,7 +12060,7 @@
         <v>65</v>
       </c>
       <c r="C546">
-        <v>5050</v>
+        <v>4940</v>
       </c>
       <c r="D546" t="s">
         <v>548</v>
@@ -11786,7 +12074,7 @@
         <v>66</v>
       </c>
       <c r="C547">
-        <v>5180</v>
+        <v>5050</v>
       </c>
       <c r="D547" t="s">
         <v>549</v>
@@ -11800,7 +12088,7 @@
         <v>67</v>
       </c>
       <c r="C548">
-        <v>5320</v>
+        <v>5180</v>
       </c>
       <c r="D548" t="s">
         <v>550</v>
@@ -11814,7 +12102,7 @@
         <v>68</v>
       </c>
       <c r="C549">
-        <v>5460</v>
+        <v>5330</v>
       </c>
       <c r="D549" t="s">
         <v>551</v>
@@ -11828,7 +12116,7 @@
         <v>69</v>
       </c>
       <c r="C550">
-        <v>5610</v>
+        <v>5480</v>
       </c>
       <c r="D550" t="s">
         <v>552</v>
@@ -11842,7 +12130,7 @@
         <v>70</v>
       </c>
       <c r="C551">
-        <v>5750</v>
+        <v>5640</v>
       </c>
       <c r="D551" t="s">
         <v>553</v>
@@ -11856,7 +12144,7 @@
         <v>71</v>
       </c>
       <c r="C552">
-        <v>5880</v>
+        <v>5800</v>
       </c>
       <c r="D552" t="s">
         <v>554</v>
@@ -11870,7 +12158,7 @@
         <v>72</v>
       </c>
       <c r="C553">
-        <v>6000</v>
+        <v>5970</v>
       </c>
       <c r="D553" t="s">
         <v>555</v>
@@ -11884,7 +12172,7 @@
         <v>73</v>
       </c>
       <c r="C554">
-        <v>6120</v>
+        <v>6160</v>
       </c>
       <c r="D554" t="s">
         <v>556</v>
@@ -11898,7 +12186,7 @@
         <v>74</v>
       </c>
       <c r="C555">
-        <v>6230</v>
+        <v>6320</v>
       </c>
       <c r="D555" t="s">
         <v>557</v>
@@ -11912,7 +12200,7 @@
         <v>75</v>
       </c>
       <c r="C556">
-        <v>6330</v>
+        <v>6480</v>
       </c>
       <c r="D556" t="s">
         <v>558</v>
@@ -11926,7 +12214,7 @@
         <v>76</v>
       </c>
       <c r="C557">
-        <v>6440</v>
+        <v>6630</v>
       </c>
       <c r="D557" t="s">
         <v>559</v>
@@ -11940,7 +12228,7 @@
         <v>77</v>
       </c>
       <c r="C558">
-        <v>6550</v>
+        <v>6780</v>
       </c>
       <c r="D558" t="s">
         <v>560</v>
@@ -11954,7 +12242,7 @@
         <v>78</v>
       </c>
       <c r="C559">
-        <v>6670</v>
+        <v>6900</v>
       </c>
       <c r="D559" t="s">
         <v>561</v>
@@ -11968,7 +12256,7 @@
         <v>79</v>
       </c>
       <c r="C560">
-        <v>6800</v>
+        <v>6990</v>
       </c>
       <c r="D560" t="s">
         <v>562</v>
@@ -11982,7 +12270,7 @@
         <v>80</v>
       </c>
       <c r="C561">
-        <v>6930</v>
+        <v>7040</v>
       </c>
       <c r="D561" t="s">
         <v>563</v>
@@ -11996,7 +12284,7 @@
         <v>81</v>
       </c>
       <c r="C562">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="D562" t="s">
         <v>564</v>
@@ -12010,7 +12298,7 @@
         <v>82</v>
       </c>
       <c r="C563">
-        <v>7150</v>
+        <v>7040</v>
       </c>
       <c r="D563" t="s">
         <v>565</v>
@@ -12024,7 +12312,7 @@
         <v>83</v>
       </c>
       <c r="C564">
-        <v>7140</v>
+        <v>7000</v>
       </c>
       <c r="D564" t="s">
         <v>566</v>
@@ -12038,7 +12326,7 @@
         <v>84</v>
       </c>
       <c r="C565">
-        <v>7050</v>
+        <v>6910</v>
       </c>
       <c r="D565" t="s">
         <v>567</v>
@@ -12052,7 +12340,7 @@
         <v>85</v>
       </c>
       <c r="C566">
-        <v>6840</v>
+        <v>6770</v>
       </c>
       <c r="D566" t="s">
         <v>568</v>
@@ -12066,7 +12354,7 @@
         <v>86</v>
       </c>
       <c r="C567">
-        <v>6600</v>
+        <v>6630</v>
       </c>
       <c r="D567" t="s">
         <v>569</v>
@@ -12080,7 +12368,7 @@
         <v>87</v>
       </c>
       <c r="C568">
-        <v>6450</v>
+        <v>6510</v>
       </c>
       <c r="D568" t="s">
         <v>570</v>
@@ -12094,7 +12382,7 @@
         <v>88</v>
       </c>
       <c r="C569">
-        <v>6350</v>
+        <v>6400</v>
       </c>
       <c r="D569" t="s">
         <v>571</v>
@@ -12108,7 +12396,7 @@
         <v>89</v>
       </c>
       <c r="C570">
-        <v>6220</v>
+        <v>6270</v>
       </c>
       <c r="D570" t="s">
         <v>572</v>
@@ -12122,7 +12410,7 @@
         <v>90</v>
       </c>
       <c r="C571">
-        <v>6060</v>
+        <v>6140</v>
       </c>
       <c r="D571" t="s">
         <v>573</v>
@@ -12136,7 +12424,7 @@
         <v>91</v>
       </c>
       <c r="C572">
-        <v>5830</v>
+        <v>6010</v>
       </c>
       <c r="D572" t="s">
         <v>574</v>
@@ -12150,7 +12438,7 @@
         <v>92</v>
       </c>
       <c r="C573">
-        <v>5710</v>
+        <v>5900</v>
       </c>
       <c r="D573" t="s">
         <v>575</v>
@@ -12164,7 +12452,7 @@
         <v>93</v>
       </c>
       <c r="C574">
-        <v>5620</v>
+        <v>5800</v>
       </c>
       <c r="D574" t="s">
         <v>576</v>
@@ -12178,7 +12466,7 @@
         <v>94</v>
       </c>
       <c r="C575">
-        <v>5480</v>
+        <v>5670</v>
       </c>
       <c r="D575" t="s">
         <v>577</v>
@@ -12192,7 +12480,7 @@
         <v>95</v>
       </c>
       <c r="C576">
-        <v>5420</v>
+        <v>5560</v>
       </c>
       <c r="D576" t="s">
         <v>578</v>
@@ -12206,7 +12494,7 @@
         <v>96</v>
       </c>
       <c r="C577">
-        <v>5350</v>
+        <v>5450</v>
       </c>
       <c r="D577" t="s">
         <v>579</v>
@@ -12220,7 +12508,7 @@
         <v>1</v>
       </c>
       <c r="C578">
-        <v>5300</v>
+        <v>5430</v>
       </c>
       <c r="D578" t="s">
         <v>580</v>
@@ -12234,7 +12522,7 @@
         <v>2</v>
       </c>
       <c r="C579">
-        <v>5240</v>
+        <v>5360</v>
       </c>
       <c r="D579" t="s">
         <v>581</v>
@@ -12248,7 +12536,7 @@
         <v>3</v>
       </c>
       <c r="C580">
-        <v>5190</v>
+        <v>5300</v>
       </c>
       <c r="D580" t="s">
         <v>582</v>
@@ -12262,7 +12550,7 @@
         <v>4</v>
       </c>
       <c r="C581">
-        <v>5130</v>
+        <v>5230</v>
       </c>
       <c r="D581" t="s">
         <v>583</v>
@@ -12276,7 +12564,7 @@
         <v>5</v>
       </c>
       <c r="C582">
-        <v>5070</v>
+        <v>5120</v>
       </c>
       <c r="D582" t="s">
         <v>584</v>
@@ -12290,7 +12578,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>5030</v>
+        <v>5060</v>
       </c>
       <c r="D583" t="s">
         <v>585</v>
@@ -12304,7 +12592,7 @@
         <v>7</v>
       </c>
       <c r="C584">
-        <v>4990</v>
+        <v>5050</v>
       </c>
       <c r="D584" t="s">
         <v>586</v>
@@ -12318,7 +12606,7 @@
         <v>8</v>
       </c>
       <c r="C585">
-        <v>4970</v>
+        <v>5050</v>
       </c>
       <c r="D585" t="s">
         <v>587</v>
@@ -12332,7 +12620,7 @@
         <v>9</v>
       </c>
       <c r="C586">
-        <v>4960</v>
+        <v>5050</v>
       </c>
       <c r="D586" t="s">
         <v>588</v>
@@ -12346,7 +12634,7 @@
         <v>10</v>
       </c>
       <c r="C587">
-        <v>4960</v>
+        <v>5050</v>
       </c>
       <c r="D587" t="s">
         <v>589</v>
@@ -12360,7 +12648,7 @@
         <v>11</v>
       </c>
       <c r="C588">
-        <v>4970</v>
+        <v>5070</v>
       </c>
       <c r="D588" t="s">
         <v>590</v>
@@ -12374,7 +12662,7 @@
         <v>12</v>
       </c>
       <c r="C589">
-        <v>4980</v>
+        <v>5110</v>
       </c>
       <c r="D589" t="s">
         <v>591</v>
@@ -12388,7 +12676,7 @@
         <v>13</v>
       </c>
       <c r="C590">
-        <v>5010</v>
+        <v>5140</v>
       </c>
       <c r="D590" t="s">
         <v>592</v>
@@ -12402,7 +12690,7 @@
         <v>14</v>
       </c>
       <c r="C591">
-        <v>5040</v>
+        <v>5180</v>
       </c>
       <c r="D591" t="s">
         <v>593</v>
@@ -12416,7 +12704,7 @@
         <v>15</v>
       </c>
       <c r="C592">
-        <v>5070</v>
+        <v>5190</v>
       </c>
       <c r="D592" t="s">
         <v>594</v>
@@ -12430,7 +12718,7 @@
         <v>16</v>
       </c>
       <c r="C593">
-        <v>5090</v>
+        <v>5190</v>
       </c>
       <c r="D593" t="s">
         <v>595</v>
@@ -12444,7 +12732,7 @@
         <v>17</v>
       </c>
       <c r="C594">
-        <v>5120</v>
+        <v>5200</v>
       </c>
       <c r="D594" t="s">
         <v>596</v>
@@ -12458,7 +12746,7 @@
         <v>18</v>
       </c>
       <c r="C595">
-        <v>5140</v>
+        <v>5180</v>
       </c>
       <c r="D595" t="s">
         <v>597</v>
@@ -12486,7 +12774,7 @@
         <v>20</v>
       </c>
       <c r="C597">
-        <v>5190</v>
+        <v>5140</v>
       </c>
       <c r="D597" t="s">
         <v>599</v>
@@ -12500,7 +12788,7 @@
         <v>21</v>
       </c>
       <c r="C598">
-        <v>5240</v>
+        <v>5140</v>
       </c>
       <c r="D598" t="s">
         <v>600</v>
@@ -12514,7 +12802,7 @@
         <v>22</v>
       </c>
       <c r="C599">
-        <v>5300</v>
+        <v>5140</v>
       </c>
       <c r="D599" t="s">
         <v>601</v>
@@ -12528,7 +12816,7 @@
         <v>23</v>
       </c>
       <c r="C600">
-        <v>5380</v>
+        <v>5170</v>
       </c>
       <c r="D600" t="s">
         <v>602</v>
@@ -12542,7 +12830,7 @@
         <v>24</v>
       </c>
       <c r="C601">
-        <v>5490</v>
+        <v>5270</v>
       </c>
       <c r="D601" t="s">
         <v>603</v>
@@ -12556,7 +12844,7 @@
         <v>25</v>
       </c>
       <c r="C602">
-        <v>5620</v>
+        <v>5480</v>
       </c>
       <c r="D602" t="s">
         <v>604</v>
@@ -12570,7 +12858,7 @@
         <v>26</v>
       </c>
       <c r="C603">
-        <v>5760</v>
+        <v>5670</v>
       </c>
       <c r="D603" t="s">
         <v>605</v>
@@ -12584,7 +12872,7 @@
         <v>27</v>
       </c>
       <c r="C604">
-        <v>5910</v>
+        <v>5840</v>
       </c>
       <c r="D604" t="s">
         <v>606</v>
@@ -12598,7 +12886,7 @@
         <v>28</v>
       </c>
       <c r="C605">
-        <v>6050</v>
+        <v>6010</v>
       </c>
       <c r="D605" t="s">
         <v>607</v>
@@ -12612,7 +12900,7 @@
         <v>29</v>
       </c>
       <c r="C606">
-        <v>6190</v>
+        <v>6220</v>
       </c>
       <c r="D606" t="s">
         <v>608</v>
@@ -12626,7 +12914,7 @@
         <v>30</v>
       </c>
       <c r="C607">
-        <v>6290</v>
+        <v>6360</v>
       </c>
       <c r="D607" t="s">
         <v>609</v>
@@ -12640,7 +12928,7 @@
         <v>31</v>
       </c>
       <c r="C608">
-        <v>6370</v>
+        <v>6450</v>
       </c>
       <c r="D608" t="s">
         <v>610</v>
@@ -12654,7 +12942,7 @@
         <v>32</v>
       </c>
       <c r="C609">
-        <v>6400</v>
+        <v>6510</v>
       </c>
       <c r="D609" t="s">
         <v>611</v>
@@ -12668,7 +12956,7 @@
         <v>33</v>
       </c>
       <c r="C610">
-        <v>6400</v>
+        <v>6520</v>
       </c>
       <c r="D610" t="s">
         <v>612</v>
@@ -12682,7 +12970,7 @@
         <v>34</v>
       </c>
       <c r="C611">
-        <v>6350</v>
+        <v>6510</v>
       </c>
       <c r="D611" t="s">
         <v>613</v>
@@ -12696,7 +12984,7 @@
         <v>35</v>
       </c>
       <c r="C612">
-        <v>6260</v>
+        <v>6480</v>
       </c>
       <c r="D612" t="s">
         <v>614</v>
@@ -12710,7 +12998,7 @@
         <v>36</v>
       </c>
       <c r="C613">
-        <v>6140</v>
+        <v>6420</v>
       </c>
       <c r="D613" t="s">
         <v>615</v>
@@ -12724,7 +13012,7 @@
         <v>37</v>
       </c>
       <c r="C614">
-        <v>5990</v>
+        <v>6320</v>
       </c>
       <c r="D614" t="s">
         <v>616</v>
@@ -12738,7 +13026,7 @@
         <v>38</v>
       </c>
       <c r="C615">
-        <v>5830</v>
+        <v>6200</v>
       </c>
       <c r="D615" t="s">
         <v>617</v>
@@ -12752,7 +13040,7 @@
         <v>39</v>
       </c>
       <c r="C616">
-        <v>5660</v>
+        <v>6060</v>
       </c>
       <c r="D616" t="s">
         <v>618</v>
@@ -12766,7 +13054,7 @@
         <v>40</v>
       </c>
       <c r="C617">
-        <v>5480</v>
+        <v>5900</v>
       </c>
       <c r="D617" t="s">
         <v>619</v>
@@ -12780,7 +13068,7 @@
         <v>41</v>
       </c>
       <c r="C618">
-        <v>5310</v>
+        <v>5710</v>
       </c>
       <c r="D618" t="s">
         <v>620</v>
@@ -12794,7 +13082,7 @@
         <v>42</v>
       </c>
       <c r="C619">
-        <v>5140</v>
+        <v>5530</v>
       </c>
       <c r="D619" t="s">
         <v>621</v>
@@ -12808,7 +13096,7 @@
         <v>43</v>
       </c>
       <c r="C620">
-        <v>4990</v>
+        <v>5360</v>
       </c>
       <c r="D620" t="s">
         <v>622</v>
@@ -12822,7 +13110,7 @@
         <v>44</v>
       </c>
       <c r="C621">
-        <v>4850</v>
+        <v>5200</v>
       </c>
       <c r="D621" t="s">
         <v>623</v>
@@ -12836,7 +13124,7 @@
         <v>45</v>
       </c>
       <c r="C622">
-        <v>4720</v>
+        <v>5010</v>
       </c>
       <c r="D622" t="s">
         <v>624</v>
@@ -12850,7 +13138,7 @@
         <v>46</v>
       </c>
       <c r="C623">
-        <v>4600</v>
+        <v>4880</v>
       </c>
       <c r="D623" t="s">
         <v>625</v>
@@ -12864,7 +13152,7 @@
         <v>47</v>
       </c>
       <c r="C624">
-        <v>4500</v>
+        <v>4760</v>
       </c>
       <c r="D624" t="s">
         <v>626</v>
@@ -12878,7 +13166,7 @@
         <v>48</v>
       </c>
       <c r="C625">
-        <v>4420</v>
+        <v>4670</v>
       </c>
       <c r="D625" t="s">
         <v>627</v>
@@ -12892,7 +13180,7 @@
         <v>49</v>
       </c>
       <c r="C626">
-        <v>4360</v>
+        <v>4600</v>
       </c>
       <c r="D626" t="s">
         <v>628</v>
@@ -12906,7 +13194,7 @@
         <v>50</v>
       </c>
       <c r="C627">
-        <v>4310</v>
+        <v>4560</v>
       </c>
       <c r="D627" t="s">
         <v>629</v>
@@ -12920,7 +13208,7 @@
         <v>51</v>
       </c>
       <c r="C628">
-        <v>4280</v>
+        <v>4540</v>
       </c>
       <c r="D628" t="s">
         <v>630</v>
@@ -12934,7 +13222,7 @@
         <v>52</v>
       </c>
       <c r="C629">
-        <v>4260</v>
+        <v>4540</v>
       </c>
       <c r="D629" t="s">
         <v>631</v>
@@ -12948,7 +13236,7 @@
         <v>53</v>
       </c>
       <c r="C630">
-        <v>4260</v>
+        <v>4560</v>
       </c>
       <c r="D630" t="s">
         <v>632</v>
@@ -12962,7 +13250,7 @@
         <v>54</v>
       </c>
       <c r="C631">
-        <v>4270</v>
+        <v>4580</v>
       </c>
       <c r="D631" t="s">
         <v>633</v>
@@ -12976,7 +13264,7 @@
         <v>55</v>
       </c>
       <c r="C632">
-        <v>4300</v>
+        <v>4610</v>
       </c>
       <c r="D632" t="s">
         <v>634</v>
@@ -12990,7 +13278,7 @@
         <v>56</v>
       </c>
       <c r="C633">
-        <v>4330</v>
+        <v>4650</v>
       </c>
       <c r="D633" t="s">
         <v>635</v>
@@ -13004,7 +13292,7 @@
         <v>57</v>
       </c>
       <c r="C634">
-        <v>4360</v>
+        <v>4700</v>
       </c>
       <c r="D634" t="s">
         <v>636</v>
@@ -13018,7 +13306,7 @@
         <v>58</v>
       </c>
       <c r="C635">
-        <v>4400</v>
+        <v>4730</v>
       </c>
       <c r="D635" t="s">
         <v>637</v>
@@ -13032,7 +13320,7 @@
         <v>59</v>
       </c>
       <c r="C636">
-        <v>4440</v>
+        <v>4750</v>
       </c>
       <c r="D636" t="s">
         <v>638</v>
@@ -13046,7 +13334,7 @@
         <v>60</v>
       </c>
       <c r="C637">
-        <v>4490</v>
+        <v>4820</v>
       </c>
       <c r="D637" t="s">
         <v>639</v>
@@ -13060,7 +13348,7 @@
         <v>61</v>
       </c>
       <c r="C638">
-        <v>4560</v>
+        <v>4910</v>
       </c>
       <c r="D638" t="s">
         <v>640</v>
@@ -13074,7 +13362,7 @@
         <v>62</v>
       </c>
       <c r="C639">
-        <v>4630</v>
+        <v>4990</v>
       </c>
       <c r="D639" t="s">
         <v>641</v>
@@ -13088,7 +13376,7 @@
         <v>63</v>
       </c>
       <c r="C640">
-        <v>4720</v>
+        <v>5070</v>
       </c>
       <c r="D640" t="s">
         <v>642</v>
@@ -13102,7 +13390,7 @@
         <v>64</v>
       </c>
       <c r="C641">
-        <v>4820</v>
+        <v>5160</v>
       </c>
       <c r="D641" t="s">
         <v>643</v>
@@ -13116,7 +13404,7 @@
         <v>65</v>
       </c>
       <c r="C642">
-        <v>4940</v>
+        <v>5260</v>
       </c>
       <c r="D642" t="s">
         <v>644</v>
@@ -13130,7 +13418,7 @@
         <v>66</v>
       </c>
       <c r="C643">
-        <v>5070</v>
+        <v>5370</v>
       </c>
       <c r="D643" t="s">
         <v>645</v>
@@ -13144,7 +13432,7 @@
         <v>67</v>
       </c>
       <c r="C644">
-        <v>5210</v>
+        <v>5480</v>
       </c>
       <c r="D644" t="s">
         <v>646</v>
@@ -13158,7 +13446,7 @@
         <v>68</v>
       </c>
       <c r="C645">
-        <v>5360</v>
+        <v>5600</v>
       </c>
       <c r="D645" t="s">
         <v>647</v>
@@ -13172,7 +13460,7 @@
         <v>69</v>
       </c>
       <c r="C646">
-        <v>5510</v>
+        <v>5760</v>
       </c>
       <c r="D646" t="s">
         <v>648</v>
@@ -13186,7 +13474,7 @@
         <v>70</v>
       </c>
       <c r="C647">
-        <v>5650</v>
+        <v>5910</v>
       </c>
       <c r="D647" t="s">
         <v>649</v>
@@ -13200,7 +13488,7 @@
         <v>71</v>
       </c>
       <c r="C648">
-        <v>5800</v>
+        <v>6050</v>
       </c>
       <c r="D648" t="s">
         <v>650</v>
@@ -13214,7 +13502,7 @@
         <v>72</v>
       </c>
       <c r="C649">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="D649" t="s">
         <v>651</v>
@@ -13228,7 +13516,7 @@
         <v>73</v>
       </c>
       <c r="C650">
-        <v>6110</v>
+        <v>6350</v>
       </c>
       <c r="D650" t="s">
         <v>652</v>
@@ -13242,7 +13530,7 @@
         <v>74</v>
       </c>
       <c r="C651">
-        <v>6260</v>
+        <v>6490</v>
       </c>
       <c r="D651" t="s">
         <v>653</v>
@@ -13256,7 +13544,7 @@
         <v>75</v>
       </c>
       <c r="C652">
-        <v>6410</v>
+        <v>6620</v>
       </c>
       <c r="D652" t="s">
         <v>654</v>
@@ -13270,7 +13558,7 @@
         <v>76</v>
       </c>
       <c r="C653">
-        <v>6560</v>
+        <v>6740</v>
       </c>
       <c r="D653" t="s">
         <v>655</v>
@@ -13284,7 +13572,7 @@
         <v>77</v>
       </c>
       <c r="C654">
-        <v>6710</v>
+        <v>6870</v>
       </c>
       <c r="D654" t="s">
         <v>656</v>
@@ -13298,7 +13586,7 @@
         <v>78</v>
       </c>
       <c r="C655">
-        <v>6850</v>
+        <v>6980</v>
       </c>
       <c r="D655" t="s">
         <v>657</v>
@@ -13312,7 +13600,7 @@
         <v>79</v>
       </c>
       <c r="C656">
-        <v>6970</v>
+        <v>7060</v>
       </c>
       <c r="D656" t="s">
         <v>658</v>
@@ -13326,7 +13614,7 @@
         <v>80</v>
       </c>
       <c r="C657">
-        <v>7080</v>
+        <v>7100</v>
       </c>
       <c r="D657" t="s">
         <v>659</v>
@@ -13340,7 +13628,7 @@
         <v>81</v>
       </c>
       <c r="C658">
-        <v>7170</v>
+        <v>7100</v>
       </c>
       <c r="D658" t="s">
         <v>660</v>
@@ -13354,7 +13642,7 @@
         <v>82</v>
       </c>
       <c r="C659">
-        <v>7220</v>
+        <v>7090</v>
       </c>
       <c r="D659" t="s">
         <v>661</v>
@@ -13368,7 +13656,7 @@
         <v>83</v>
       </c>
       <c r="C660">
-        <v>7180</v>
+        <v>7050</v>
       </c>
       <c r="D660" t="s">
         <v>662</v>
@@ -13382,7 +13670,7 @@
         <v>84</v>
       </c>
       <c r="C661">
-        <v>7070</v>
+        <v>6970</v>
       </c>
       <c r="D661" t="s">
         <v>663</v>
@@ -13396,7 +13684,7 @@
         <v>85</v>
       </c>
       <c r="C662">
-        <v>6860</v>
+        <v>6840</v>
       </c>
       <c r="D662" t="s">
         <v>664</v>
@@ -13410,7 +13698,7 @@
         <v>86</v>
       </c>
       <c r="C663">
-        <v>6610</v>
+        <v>6710</v>
       </c>
       <c r="D663" t="s">
         <v>665</v>
@@ -13424,7 +13712,7 @@
         <v>87</v>
       </c>
       <c r="C664">
-        <v>6450</v>
+        <v>6580</v>
       </c>
       <c r="D664" t="s">
         <v>666</v>
@@ -13438,7 +13726,7 @@
         <v>88</v>
       </c>
       <c r="C665">
-        <v>6330</v>
+        <v>6470</v>
       </c>
       <c r="D665" t="s">
         <v>667</v>
@@ -13452,7 +13740,7 @@
         <v>89</v>
       </c>
       <c r="C666">
-        <v>6170</v>
+        <v>6280</v>
       </c>
       <c r="D666" t="s">
         <v>668</v>
@@ -13466,7 +13754,7 @@
         <v>90</v>
       </c>
       <c r="C667">
-        <v>6010</v>
+        <v>6140</v>
       </c>
       <c r="D667" t="s">
         <v>669</v>
@@ -13480,7 +13768,7 @@
         <v>91</v>
       </c>
       <c r="C668">
-        <v>5780</v>
+        <v>6000</v>
       </c>
       <c r="D668" t="s">
         <v>670</v>
@@ -13494,7 +13782,7 @@
         <v>92</v>
       </c>
       <c r="C669">
-        <v>5660</v>
+        <v>5890</v>
       </c>
       <c r="D669" t="s">
         <v>671</v>
@@ -13508,7 +13796,7 @@
         <v>93</v>
       </c>
       <c r="C670">
-        <v>5550</v>
+        <v>5800</v>
       </c>
       <c r="D670" t="s">
         <v>672</v>
@@ -13522,7 +13810,7 @@
         <v>94</v>
       </c>
       <c r="C671">
-        <v>5430</v>
+        <v>5720</v>
       </c>
       <c r="D671" t="s">
         <v>673</v>
@@ -13536,7 +13824,7 @@
         <v>95</v>
       </c>
       <c r="C672">
-        <v>5380</v>
+        <v>5630</v>
       </c>
       <c r="D672" t="s">
         <v>674</v>
@@ -13550,7 +13838,7 @@
         <v>96</v>
       </c>
       <c r="C673">
-        <v>5300</v>
+        <v>5530</v>
       </c>
       <c r="D673" t="s">
         <v>675</v>
@@ -13564,7 +13852,7 @@
         <v>1</v>
       </c>
       <c r="C674">
-        <v>5290</v>
+        <v>5440</v>
       </c>
       <c r="D674" t="s">
         <v>676</v>
@@ -13578,7 +13866,7 @@
         <v>2</v>
       </c>
       <c r="C675">
-        <v>5250</v>
+        <v>5400</v>
       </c>
       <c r="D675" t="s">
         <v>677</v>
@@ -13592,7 +13880,7 @@
         <v>3</v>
       </c>
       <c r="C676">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="D676" t="s">
         <v>678</v>
@@ -13606,7 +13894,7 @@
         <v>4</v>
       </c>
       <c r="C677">
-        <v>5220</v>
+        <v>5260</v>
       </c>
       <c r="D677" t="s">
         <v>679</v>
@@ -13620,7 +13908,7 @@
         <v>5</v>
       </c>
       <c r="C678">
-        <v>5210</v>
+        <v>5180</v>
       </c>
       <c r="D678" t="s">
         <v>680</v>
@@ -13634,7 +13922,7 @@
         <v>6</v>
       </c>
       <c r="C679">
-        <v>5150</v>
+        <v>5130</v>
       </c>
       <c r="D679" t="s">
         <v>681</v>
@@ -13648,7 +13936,7 @@
         <v>7</v>
       </c>
       <c r="C680">
-        <v>5080</v>
+        <v>5100</v>
       </c>
       <c r="D680" t="s">
         <v>682</v>
@@ -13662,7 +13950,7 @@
         <v>8</v>
       </c>
       <c r="C681">
-        <v>5010</v>
+        <v>5090</v>
       </c>
       <c r="D681" t="s">
         <v>683</v>
@@ -13676,7 +13964,7 @@
         <v>9</v>
       </c>
       <c r="C682">
-        <v>4950</v>
+        <v>5090</v>
       </c>
       <c r="D682" t="s">
         <v>684</v>
@@ -13690,7 +13978,7 @@
         <v>10</v>
       </c>
       <c r="C683">
-        <v>4920</v>
+        <v>5100</v>
       </c>
       <c r="D683" t="s">
         <v>685</v>
@@ -13704,7 +13992,7 @@
         <v>11</v>
       </c>
       <c r="C684">
-        <v>4920</v>
+        <v>5100</v>
       </c>
       <c r="D684" t="s">
         <v>686</v>
@@ -13718,7 +14006,7 @@
         <v>12</v>
       </c>
       <c r="C685">
-        <v>4940</v>
+        <v>5100</v>
       </c>
       <c r="D685" t="s">
         <v>687</v>
@@ -13732,7 +14020,7 @@
         <v>13</v>
       </c>
       <c r="C686">
-        <v>4980</v>
+        <v>5110</v>
       </c>
       <c r="D686" t="s">
         <v>688</v>
@@ -13746,7 +14034,7 @@
         <v>14</v>
       </c>
       <c r="C687">
-        <v>5030</v>
+        <v>5110</v>
       </c>
       <c r="D687" t="s">
         <v>689</v>
@@ -13760,7 +14048,7 @@
         <v>15</v>
       </c>
       <c r="C688">
-        <v>5070</v>
+        <v>5120</v>
       </c>
       <c r="D688" t="s">
         <v>690</v>
@@ -13774,7 +14062,7 @@
         <v>16</v>
       </c>
       <c r="C689">
-        <v>5100</v>
+        <v>5130</v>
       </c>
       <c r="D689" t="s">
         <v>691</v>
@@ -13788,7 +14076,7 @@
         <v>17</v>
       </c>
       <c r="C690">
-        <v>5110</v>
+        <v>5140</v>
       </c>
       <c r="D690" t="s">
         <v>692</v>
@@ -13802,7 +14090,7 @@
         <v>18</v>
       </c>
       <c r="C691">
-        <v>5110</v>
+        <v>5150</v>
       </c>
       <c r="D691" t="s">
         <v>693</v>
@@ -13816,7 +14104,7 @@
         <v>19</v>
       </c>
       <c r="C692">
-        <v>5110</v>
+        <v>5170</v>
       </c>
       <c r="D692" t="s">
         <v>694</v>
@@ -13830,7 +14118,7 @@
         <v>20</v>
       </c>
       <c r="C693">
-        <v>5120</v>
+        <v>5190</v>
       </c>
       <c r="D693" t="s">
         <v>695</v>
@@ -13844,7 +14132,7 @@
         <v>21</v>
       </c>
       <c r="C694">
-        <v>5150</v>
+        <v>5220</v>
       </c>
       <c r="D694" t="s">
         <v>696</v>
@@ -13858,7 +14146,7 @@
         <v>22</v>
       </c>
       <c r="C695">
-        <v>5210</v>
+        <v>5270</v>
       </c>
       <c r="D695" t="s">
         <v>697</v>
@@ -13872,7 +14160,7 @@
         <v>23</v>
       </c>
       <c r="C696">
-        <v>5300</v>
+        <v>5340</v>
       </c>
       <c r="D696" t="s">
         <v>698</v>
@@ -13900,7 +14188,7 @@
         <v>25</v>
       </c>
       <c r="C698">
-        <v>5580</v>
+        <v>5540</v>
       </c>
       <c r="D698" t="s">
         <v>700</v>
@@ -13914,7 +14202,7 @@
         <v>26</v>
       </c>
       <c r="C699">
-        <v>5750</v>
+        <v>5680</v>
       </c>
       <c r="D699" t="s">
         <v>701</v>
@@ -13928,7 +14216,7 @@
         <v>27</v>
       </c>
       <c r="C700">
-        <v>5930</v>
+        <v>5830</v>
       </c>
       <c r="D700" t="s">
         <v>702</v>
@@ -13942,7 +14230,7 @@
         <v>28</v>
       </c>
       <c r="C701">
-        <v>6110</v>
+        <v>5990</v>
       </c>
       <c r="D701" t="s">
         <v>703</v>
@@ -13956,7 +14244,7 @@
         <v>29</v>
       </c>
       <c r="C702">
-        <v>6260</v>
+        <v>6150</v>
       </c>
       <c r="D702" t="s">
         <v>704</v>
@@ -13970,7 +14258,7 @@
         <v>30</v>
       </c>
       <c r="C703">
-        <v>6390</v>
+        <v>6290</v>
       </c>
       <c r="D703" t="s">
         <v>705</v>
@@ -13984,7 +14272,7 @@
         <v>31</v>
       </c>
       <c r="C704">
-        <v>6480</v>
+        <v>6410</v>
       </c>
       <c r="D704" t="s">
         <v>706</v>
@@ -13998,7 +14286,7 @@
         <v>32</v>
       </c>
       <c r="C705">
-        <v>6530</v>
+        <v>6500</v>
       </c>
       <c r="D705" t="s">
         <v>707</v>
@@ -14012,7 +14300,7 @@
         <v>33</v>
       </c>
       <c r="C706">
-        <v>6530</v>
+        <v>6550</v>
       </c>
       <c r="D706" t="s">
         <v>708</v>
@@ -14026,7 +14314,7 @@
         <v>34</v>
       </c>
       <c r="C707">
-        <v>6490</v>
+        <v>6540</v>
       </c>
       <c r="D707" t="s">
         <v>709</v>
@@ -14040,7 +14328,7 @@
         <v>35</v>
       </c>
       <c r="C708">
-        <v>6410</v>
+        <v>6500</v>
       </c>
       <c r="D708" t="s">
         <v>710</v>
@@ -14054,7 +14342,7 @@
         <v>36</v>
       </c>
       <c r="C709">
-        <v>6290</v>
+        <v>6410</v>
       </c>
       <c r="D709" t="s">
         <v>711</v>
@@ -14068,7 +14356,7 @@
         <v>37</v>
       </c>
       <c r="C710">
-        <v>6150</v>
+        <v>6290</v>
       </c>
       <c r="D710" t="s">
         <v>712</v>
@@ -14082,7 +14370,7 @@
         <v>38</v>
       </c>
       <c r="C711">
-        <v>5980</v>
+        <v>6140</v>
       </c>
       <c r="D711" t="s">
         <v>713</v>
@@ -14096,7 +14384,7 @@
         <v>39</v>
       </c>
       <c r="C712">
-        <v>5810</v>
+        <v>5970</v>
       </c>
       <c r="D712" t="s">
         <v>714</v>
@@ -14110,7 +14398,7 @@
         <v>40</v>
       </c>
       <c r="C713">
-        <v>5620</v>
+        <v>5800</v>
       </c>
       <c r="D713" t="s">
         <v>715</v>
@@ -14124,7 +14412,7 @@
         <v>41</v>
       </c>
       <c r="C714">
-        <v>5430</v>
+        <v>5620</v>
       </c>
       <c r="D714" t="s">
         <v>716</v>
@@ -14138,7 +14426,7 @@
         <v>42</v>
       </c>
       <c r="C715">
-        <v>5250</v>
+        <v>5450</v>
       </c>
       <c r="D715" t="s">
         <v>717</v>
@@ -14152,7 +14440,7 @@
         <v>43</v>
       </c>
       <c r="C716">
-        <v>5070</v>
+        <v>5290</v>
       </c>
       <c r="D716" t="s">
         <v>718</v>
@@ -14166,7 +14454,7 @@
         <v>44</v>
       </c>
       <c r="C717">
-        <v>4920</v>
+        <v>5150</v>
       </c>
       <c r="D717" t="s">
         <v>719</v>
@@ -14180,7 +14468,7 @@
         <v>45</v>
       </c>
       <c r="C718">
-        <v>4780</v>
+        <v>5030</v>
       </c>
       <c r="D718" t="s">
         <v>720</v>
@@ -14194,7 +14482,7 @@
         <v>46</v>
       </c>
       <c r="C719">
-        <v>4670</v>
+        <v>4920</v>
       </c>
       <c r="D719" t="s">
         <v>721</v>
@@ -14208,7 +14496,7 @@
         <v>47</v>
       </c>
       <c r="C720">
-        <v>4580</v>
+        <v>4820</v>
       </c>
       <c r="D720" t="s">
         <v>722</v>
@@ -14222,7 +14510,7 @@
         <v>48</v>
       </c>
       <c r="C721">
-        <v>4520</v>
+        <v>4740</v>
       </c>
       <c r="D721" t="s">
         <v>723</v>
@@ -14236,7 +14524,7 @@
         <v>49</v>
       </c>
       <c r="C722">
-        <v>4490</v>
+        <v>4680</v>
       </c>
       <c r="D722" t="s">
         <v>724</v>
@@ -14250,7 +14538,7 @@
         <v>50</v>
       </c>
       <c r="C723">
-        <v>4470</v>
+        <v>4630</v>
       </c>
       <c r="D723" t="s">
         <v>725</v>
@@ -14264,7 +14552,7 @@
         <v>51</v>
       </c>
       <c r="C724">
-        <v>4470</v>
+        <v>4600</v>
       </c>
       <c r="D724" t="s">
         <v>726</v>
@@ -14278,7 +14566,7 @@
         <v>52</v>
       </c>
       <c r="C725">
-        <v>4490</v>
+        <v>4580</v>
       </c>
       <c r="D725" t="s">
         <v>727</v>
@@ -14292,7 +14580,7 @@
         <v>53</v>
       </c>
       <c r="C726">
-        <v>4510</v>
+        <v>4580</v>
       </c>
       <c r="D726" t="s">
         <v>728</v>
@@ -14306,7 +14594,7 @@
         <v>54</v>
       </c>
       <c r="C727">
-        <v>4530</v>
+        <v>4590</v>
       </c>
       <c r="D727" t="s">
         <v>729</v>
@@ -14320,7 +14608,7 @@
         <v>55</v>
       </c>
       <c r="C728">
-        <v>4560</v>
+        <v>4610</v>
       </c>
       <c r="D728" t="s">
         <v>730</v>
@@ -14334,7 +14622,7 @@
         <v>56</v>
       </c>
       <c r="C729">
-        <v>4590</v>
+        <v>4640</v>
       </c>
       <c r="D729" t="s">
         <v>731</v>
@@ -14348,7 +14636,7 @@
         <v>57</v>
       </c>
       <c r="C730">
-        <v>4610</v>
+        <v>4670</v>
       </c>
       <c r="D730" t="s">
         <v>732</v>
@@ -14362,7 +14650,7 @@
         <v>58</v>
       </c>
       <c r="C731">
-        <v>4640</v>
+        <v>4710</v>
       </c>
       <c r="D731" t="s">
         <v>733</v>
@@ -14376,7 +14664,7 @@
         <v>59</v>
       </c>
       <c r="C732">
-        <v>4670</v>
+        <v>4740</v>
       </c>
       <c r="D732" t="s">
         <v>734</v>
@@ -14390,7 +14678,7 @@
         <v>60</v>
       </c>
       <c r="C733">
-        <v>4720</v>
+        <v>4780</v>
       </c>
       <c r="D733" t="s">
         <v>735</v>
@@ -14404,7 +14692,7 @@
         <v>61</v>
       </c>
       <c r="C734">
-        <v>4770</v>
+        <v>4820</v>
       </c>
       <c r="D734" t="s">
         <v>736</v>
@@ -14418,7 +14706,7 @@
         <v>62</v>
       </c>
       <c r="C735">
-        <v>4840</v>
+        <v>4870</v>
       </c>
       <c r="D735" t="s">
         <v>737</v>
@@ -14446,7 +14734,7 @@
         <v>64</v>
       </c>
       <c r="C737">
-        <v>5030</v>
+        <v>5000</v>
       </c>
       <c r="D737" t="s">
         <v>739</v>
@@ -14460,7 +14748,7 @@
         <v>65</v>
       </c>
       <c r="C738">
-        <v>5140</v>
+        <v>5100</v>
       </c>
       <c r="D738" t="s">
         <v>740</v>
@@ -14474,7 +14762,7 @@
         <v>66</v>
       </c>
       <c r="C739">
-        <v>5270</v>
+        <v>5210</v>
       </c>
       <c r="D739" t="s">
         <v>741</v>
@@ -14488,7 +14776,7 @@
         <v>67</v>
       </c>
       <c r="C740">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="D740" t="s">
         <v>742</v>
@@ -14502,7 +14790,7 @@
         <v>68</v>
       </c>
       <c r="C741">
-        <v>5540</v>
+        <v>5480</v>
       </c>
       <c r="D741" t="s">
         <v>743</v>
@@ -14516,7 +14804,7 @@
         <v>69</v>
       </c>
       <c r="C742">
-        <v>5680</v>
+        <v>5630</v>
       </c>
       <c r="D742" t="s">
         <v>744</v>
@@ -14530,7 +14818,7 @@
         <v>70</v>
       </c>
       <c r="C743">
-        <v>5810</v>
+        <v>5780</v>
       </c>
       <c r="D743" t="s">
         <v>745</v>
@@ -14544,7 +14832,7 @@
         <v>71</v>
       </c>
       <c r="C744">
-        <v>5950</v>
+        <v>5940</v>
       </c>
       <c r="D744" t="s">
         <v>746</v>
@@ -14558,7 +14846,7 @@
         <v>72</v>
       </c>
       <c r="C745">
-        <v>6080</v>
+        <v>6090</v>
       </c>
       <c r="D745" t="s">
         <v>747</v>
@@ -14572,7 +14860,7 @@
         <v>73</v>
       </c>
       <c r="C746">
-        <v>6220</v>
+        <v>6250</v>
       </c>
       <c r="D746" t="s">
         <v>748</v>
@@ -14586,7 +14874,7 @@
         <v>74</v>
       </c>
       <c r="C747">
-        <v>6360</v>
+        <v>6410</v>
       </c>
       <c r="D747" t="s">
         <v>749</v>
@@ -14600,7 +14888,7 @@
         <v>75</v>
       </c>
       <c r="C748">
-        <v>6510</v>
+        <v>6580</v>
       </c>
       <c r="D748" t="s">
         <v>750</v>
@@ -14614,7 +14902,7 @@
         <v>76</v>
       </c>
       <c r="C749">
-        <v>6660</v>
+        <v>6740</v>
       </c>
       <c r="D749" t="s">
         <v>751</v>
@@ -14628,7 +14916,7 @@
         <v>77</v>
       </c>
       <c r="C750">
-        <v>6810</v>
+        <v>6890</v>
       </c>
       <c r="D750" t="s">
         <v>752</v>
@@ -14642,7 +14930,7 @@
         <v>78</v>
       </c>
       <c r="C751">
-        <v>6950</v>
+        <v>7020</v>
       </c>
       <c r="D751" t="s">
         <v>753</v>
@@ -14656,7 +14944,7 @@
         <v>79</v>
       </c>
       <c r="C752">
-        <v>7070</v>
+        <v>7100</v>
       </c>
       <c r="D752" t="s">
         <v>754</v>
@@ -14670,7 +14958,7 @@
         <v>80</v>
       </c>
       <c r="C753">
-        <v>7160</v>
+        <v>7100</v>
       </c>
       <c r="D753" t="s">
         <v>755</v>
@@ -14684,7 +14972,7 @@
         <v>81</v>
       </c>
       <c r="C754">
-        <v>7240</v>
+        <v>7100</v>
       </c>
       <c r="D754" t="s">
         <v>756</v>
@@ -14698,7 +14986,7 @@
         <v>82</v>
       </c>
       <c r="C755">
-        <v>7270</v>
+        <v>7100</v>
       </c>
       <c r="D755" t="s">
         <v>757</v>
@@ -14712,7 +15000,7 @@
         <v>83</v>
       </c>
       <c r="C756">
-        <v>7220</v>
+        <v>7080</v>
       </c>
       <c r="D756" t="s">
         <v>758</v>
@@ -14726,7 +15014,7 @@
         <v>84</v>
       </c>
       <c r="C757">
-        <v>7130</v>
+        <v>6980</v>
       </c>
       <c r="D757" t="s">
         <v>759</v>
@@ -14740,7 +15028,7 @@
         <v>85</v>
       </c>
       <c r="C758">
-        <v>6940</v>
+        <v>6820</v>
       </c>
       <c r="D758" t="s">
         <v>760</v>
@@ -14754,7 +15042,7 @@
         <v>86</v>
       </c>
       <c r="C759">
-        <v>6720</v>
+        <v>6650</v>
       </c>
       <c r="D759" t="s">
         <v>761</v>
@@ -14768,7 +15056,7 @@
         <v>87</v>
       </c>
       <c r="C760">
-        <v>6570</v>
+        <v>6540</v>
       </c>
       <c r="D760" t="s">
         <v>762</v>
@@ -14782,7 +15070,7 @@
         <v>88</v>
       </c>
       <c r="C761">
-        <v>6420</v>
+        <v>6450</v>
       </c>
       <c r="D761" t="s">
         <v>763</v>
@@ -14796,7 +15084,7 @@
         <v>89</v>
       </c>
       <c r="C762">
-        <v>6230</v>
+        <v>6330</v>
       </c>
       <c r="D762" t="s">
         <v>764</v>
@@ -14810,7 +15098,7 @@
         <v>90</v>
       </c>
       <c r="C763">
-        <v>6050</v>
+        <v>6220</v>
       </c>
       <c r="D763" t="s">
         <v>765</v>
@@ -14824,7 +15112,7 @@
         <v>91</v>
       </c>
       <c r="C764">
-        <v>5830</v>
+        <v>6040</v>
       </c>
       <c r="D764" t="s">
         <v>766</v>
@@ -14838,7 +15126,7 @@
         <v>92</v>
       </c>
       <c r="C765">
-        <v>5720</v>
+        <v>5920</v>
       </c>
       <c r="D765" t="s">
         <v>767</v>
@@ -14852,7 +15140,7 @@
         <v>93</v>
       </c>
       <c r="C766">
-        <v>5600</v>
+        <v>5830</v>
       </c>
       <c r="D766" t="s">
         <v>768</v>
@@ -14866,7 +15154,7 @@
         <v>94</v>
       </c>
       <c r="C767">
-        <v>5480</v>
+        <v>5670</v>
       </c>
       <c r="D767" t="s">
         <v>769</v>
@@ -14880,7 +15168,7 @@
         <v>95</v>
       </c>
       <c r="C768">
-        <v>5430</v>
+        <v>5580</v>
       </c>
       <c r="D768" t="s">
         <v>770</v>
@@ -14894,7 +15182,7 @@
         <v>96</v>
       </c>
       <c r="C769">
-        <v>5380</v>
+        <v>5470</v>
       </c>
       <c r="D769" t="s">
         <v>771</v>
@@ -14908,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="C770">
-        <v>5360</v>
+        <v>5460</v>
       </c>
       <c r="D770" t="s">
         <v>772</v>
@@ -14922,7 +15210,7 @@
         <v>2</v>
       </c>
       <c r="C771">
-        <v>5310</v>
+        <v>5420</v>
       </c>
       <c r="D771" t="s">
         <v>773</v>
@@ -14936,7 +15224,7 @@
         <v>3</v>
       </c>
       <c r="C772">
-        <v>5250</v>
+        <v>5360</v>
       </c>
       <c r="D772" t="s">
         <v>774</v>
@@ -14950,7 +15238,7 @@
         <v>4</v>
       </c>
       <c r="C773">
-        <v>5190</v>
+        <v>5280</v>
       </c>
       <c r="D773" t="s">
         <v>775</v>
@@ -14964,7 +15252,7 @@
         <v>5</v>
       </c>
       <c r="C774">
-        <v>5130</v>
+        <v>5220</v>
       </c>
       <c r="D774" t="s">
         <v>776</v>
@@ -14978,7 +15266,7 @@
         <v>6</v>
       </c>
       <c r="C775">
-        <v>5090</v>
+        <v>5180</v>
       </c>
       <c r="D775" t="s">
         <v>777</v>
@@ -14992,7 +15280,7 @@
         <v>7</v>
       </c>
       <c r="C776">
-        <v>5050</v>
+        <v>5160</v>
       </c>
       <c r="D776" t="s">
         <v>778</v>
@@ -15006,7 +15294,7 @@
         <v>8</v>
       </c>
       <c r="C777">
-        <v>5020</v>
+        <v>5140</v>
       </c>
       <c r="D777" t="s">
         <v>779</v>
@@ -15020,7 +15308,7 @@
         <v>9</v>
       </c>
       <c r="C778">
-        <v>5000</v>
+        <v>5120</v>
       </c>
       <c r="D778" t="s">
         <v>780</v>
@@ -15034,7 +15322,7 @@
         <v>10</v>
       </c>
       <c r="C779">
-        <v>4990</v>
+        <v>5100</v>
       </c>
       <c r="D779" t="s">
         <v>781</v>
@@ -15048,7 +15336,7 @@
         <v>11</v>
       </c>
       <c r="C780">
-        <v>5010</v>
+        <v>5100</v>
       </c>
       <c r="D780" t="s">
         <v>782</v>
@@ -15062,7 +15350,7 @@
         <v>12</v>
       </c>
       <c r="C781">
-        <v>5030</v>
+        <v>5120</v>
       </c>
       <c r="D781" t="s">
         <v>783</v>
@@ -15076,7 +15364,7 @@
         <v>13</v>
       </c>
       <c r="C782">
-        <v>5060</v>
+        <v>5120</v>
       </c>
       <c r="D782" t="s">
         <v>784</v>
@@ -15090,7 +15378,7 @@
         <v>14</v>
       </c>
       <c r="C783">
-        <v>5100</v>
+        <v>5140</v>
       </c>
       <c r="D783" t="s">
         <v>785</v>
@@ -15104,7 +15392,7 @@
         <v>15</v>
       </c>
       <c r="C784">
-        <v>5130</v>
+        <v>5150</v>
       </c>
       <c r="D784" t="s">
         <v>786</v>
@@ -15132,7 +15420,7 @@
         <v>17</v>
       </c>
       <c r="C786">
-        <v>5170</v>
+        <v>5180</v>
       </c>
       <c r="D786" t="s">
         <v>788</v>
@@ -15146,7 +15434,7 @@
         <v>18</v>
       </c>
       <c r="C787">
-        <v>5180</v>
+        <v>5190</v>
       </c>
       <c r="D787" t="s">
         <v>789</v>
@@ -15160,7 +15448,7 @@
         <v>19</v>
       </c>
       <c r="C788">
-        <v>5180</v>
+        <v>5210</v>
       </c>
       <c r="D788" t="s">
         <v>790</v>
@@ -15174,7 +15462,7 @@
         <v>20</v>
       </c>
       <c r="C789">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="D789" t="s">
         <v>791</v>
@@ -15188,7 +15476,7 @@
         <v>21</v>
       </c>
       <c r="C790">
-        <v>5220</v>
+        <v>5290</v>
       </c>
       <c r="D790" t="s">
         <v>792</v>
@@ -15202,7 +15490,7 @@
         <v>22</v>
       </c>
       <c r="C791">
-        <v>5280</v>
+        <v>5360</v>
       </c>
       <c r="D791" t="s">
         <v>793</v>
@@ -15216,7 +15504,7 @@
         <v>23</v>
       </c>
       <c r="C792">
-        <v>5350</v>
+        <v>5450</v>
       </c>
       <c r="D792" t="s">
         <v>794</v>
@@ -15230,7 +15518,7 @@
         <v>24</v>
       </c>
       <c r="C793">
-        <v>5450</v>
+        <v>5560</v>
       </c>
       <c r="D793" t="s">
         <v>795</v>
@@ -15244,7 +15532,7 @@
         <v>25</v>
       </c>
       <c r="C794">
-        <v>5580</v>
+        <v>5690</v>
       </c>
       <c r="D794" t="s">
         <v>796</v>
@@ -15258,7 +15546,7 @@
         <v>26</v>
       </c>
       <c r="C795">
-        <v>5720</v>
+        <v>5830</v>
       </c>
       <c r="D795" t="s">
         <v>797</v>
@@ -15272,7 +15560,7 @@
         <v>27</v>
       </c>
       <c r="C796">
-        <v>5860</v>
+        <v>5980</v>
       </c>
       <c r="D796" t="s">
         <v>798</v>
@@ -15286,7 +15574,7 @@
         <v>28</v>
       </c>
       <c r="C797">
-        <v>6000</v>
+        <v>6140</v>
       </c>
       <c r="D797" t="s">
         <v>799</v>
@@ -15300,7 +15588,7 @@
         <v>29</v>
       </c>
       <c r="C798">
-        <v>6120</v>
+        <v>6290</v>
       </c>
       <c r="D798" t="s">
         <v>800</v>
@@ -15314,7 +15602,7 @@
         <v>30</v>
       </c>
       <c r="C799">
-        <v>6210</v>
+        <v>6420</v>
       </c>
       <c r="D799" t="s">
         <v>801</v>
@@ -15328,7 +15616,7 @@
         <v>31</v>
       </c>
       <c r="C800">
-        <v>6280</v>
+        <v>6530</v>
       </c>
       <c r="D800" t="s">
         <v>802</v>
@@ -15342,7 +15630,7 @@
         <v>32</v>
       </c>
       <c r="C801">
-        <v>6300</v>
+        <v>6610</v>
       </c>
       <c r="D801" t="s">
         <v>803</v>
@@ -15356,7 +15644,7 @@
         <v>33</v>
       </c>
       <c r="C802">
-        <v>6290</v>
+        <v>6650</v>
       </c>
       <c r="D802" t="s">
         <v>804</v>
@@ -15370,7 +15658,7 @@
         <v>34</v>
       </c>
       <c r="C803">
-        <v>6240</v>
+        <v>6650</v>
       </c>
       <c r="D803" t="s">
         <v>805</v>
@@ -15384,7 +15672,7 @@
         <v>35</v>
       </c>
       <c r="C804">
-        <v>6150</v>
+        <v>6650</v>
       </c>
       <c r="D804" t="s">
         <v>806</v>
@@ -15398,7 +15686,7 @@
         <v>36</v>
       </c>
       <c r="C805">
-        <v>6040</v>
+        <v>6630</v>
       </c>
       <c r="D805" t="s">
         <v>807</v>
@@ -15412,7 +15700,7 @@
         <v>37</v>
       </c>
       <c r="C806">
-        <v>5900</v>
+        <v>6560</v>
       </c>
       <c r="D806" t="s">
         <v>808</v>
@@ -15426,7 +15714,7 @@
         <v>38</v>
       </c>
       <c r="C807">
-        <v>5750</v>
+        <v>6490</v>
       </c>
       <c r="D807" t="s">
         <v>809</v>
@@ -15440,7 +15728,7 @@
         <v>39</v>
       </c>
       <c r="C808">
-        <v>5580</v>
+        <v>6400</v>
       </c>
       <c r="D808" t="s">
         <v>810</v>
@@ -15454,7 +15742,7 @@
         <v>40</v>
       </c>
       <c r="C809">
-        <v>5410</v>
+        <v>6310</v>
       </c>
       <c r="D809" t="s">
         <v>811</v>
@@ -15468,7 +15756,7 @@
         <v>41</v>
       </c>
       <c r="C810">
-        <v>5240</v>
+        <v>6220</v>
       </c>
       <c r="D810" t="s">
         <v>812</v>
@@ -15482,7 +15770,7 @@
         <v>42</v>
       </c>
       <c r="C811">
-        <v>5070</v>
+        <v>6130</v>
       </c>
       <c r="D811" t="s">
         <v>813</v>
@@ -15496,7 +15784,7 @@
         <v>43</v>
       </c>
       <c r="C812">
-        <v>4910</v>
+        <v>6050</v>
       </c>
       <c r="D812" t="s">
         <v>814</v>
@@ -15510,7 +15798,7 @@
         <v>44</v>
       </c>
       <c r="C813">
-        <v>4750</v>
+        <v>5980</v>
       </c>
       <c r="D813" t="s">
         <v>815</v>
@@ -15524,7 +15812,7 @@
         <v>45</v>
       </c>
       <c r="C814">
-        <v>4610</v>
+        <v>5910</v>
       </c>
       <c r="D814" t="s">
         <v>816</v>
@@ -15538,7 +15826,7 @@
         <v>46</v>
       </c>
       <c r="C815">
-        <v>4480</v>
+        <v>5860</v>
       </c>
       <c r="D815" t="s">
         <v>817</v>
@@ -15552,7 +15840,7 @@
         <v>47</v>
       </c>
       <c r="C816">
-        <v>4370</v>
+        <v>5800</v>
       </c>
       <c r="D816" t="s">
         <v>818</v>
@@ -15566,7 +15854,7 @@
         <v>48</v>
       </c>
       <c r="C817">
-        <v>4280</v>
+        <v>5750</v>
       </c>
       <c r="D817" t="s">
         <v>819</v>
@@ -15580,7 +15868,7 @@
         <v>49</v>
       </c>
       <c r="C818">
-        <v>4210</v>
+        <v>5710</v>
       </c>
       <c r="D818" t="s">
         <v>820</v>
@@ -15594,7 +15882,7 @@
         <v>50</v>
       </c>
       <c r="C819">
-        <v>4150</v>
+        <v>5670</v>
       </c>
       <c r="D819" t="s">
         <v>821</v>
@@ -15608,7 +15896,7 @@
         <v>51</v>
       </c>
       <c r="C820">
-        <v>4120</v>
+        <v>5640</v>
       </c>
       <c r="D820" t="s">
         <v>822</v>
@@ -15622,7 +15910,7 @@
         <v>52</v>
       </c>
       <c r="C821">
-        <v>4100</v>
+        <v>5620</v>
       </c>
       <c r="D821" t="s">
         <v>823</v>
@@ -15636,7 +15924,7 @@
         <v>53</v>
       </c>
       <c r="C822">
-        <v>4110</v>
+        <v>5600</v>
       </c>
       <c r="D822" t="s">
         <v>824</v>
@@ -15650,7 +15938,7 @@
         <v>54</v>
       </c>
       <c r="C823">
-        <v>4120</v>
+        <v>5600</v>
       </c>
       <c r="D823" t="s">
         <v>825</v>
@@ -15664,7 +15952,7 @@
         <v>55</v>
       </c>
       <c r="C824">
-        <v>4140</v>
+        <v>5600</v>
       </c>
       <c r="D824" t="s">
         <v>826</v>
@@ -15678,7 +15966,7 @@
         <v>56</v>
       </c>
       <c r="C825">
-        <v>4180</v>
+        <v>5600</v>
       </c>
       <c r="D825" t="s">
         <v>827</v>
@@ -15692,7 +15980,7 @@
         <v>57</v>
       </c>
       <c r="C826">
-        <v>4220</v>
+        <v>5610</v>
       </c>
       <c r="D826" t="s">
         <v>828</v>
@@ -15706,7 +15994,7 @@
         <v>58</v>
       </c>
       <c r="C827">
-        <v>4260</v>
+        <v>5620</v>
       </c>
       <c r="D827" t="s">
         <v>829</v>
@@ -15720,7 +16008,7 @@
         <v>59</v>
       </c>
       <c r="C828">
-        <v>4310</v>
+        <v>5630</v>
       </c>
       <c r="D828" t="s">
         <v>830</v>
@@ -15734,7 +16022,7 @@
         <v>60</v>
       </c>
       <c r="C829">
-        <v>4370</v>
+        <v>5650</v>
       </c>
       <c r="D829" t="s">
         <v>831</v>
@@ -15748,7 +16036,7 @@
         <v>61</v>
       </c>
       <c r="C830">
-        <v>4430</v>
+        <v>5660</v>
       </c>
       <c r="D830" t="s">
         <v>832</v>
@@ -15762,7 +16050,7 @@
         <v>62</v>
       </c>
       <c r="C831">
-        <v>4510</v>
+        <v>5680</v>
       </c>
       <c r="D831" t="s">
         <v>833</v>
@@ -15776,7 +16064,7 @@
         <v>63</v>
       </c>
       <c r="C832">
-        <v>4610</v>
+        <v>5710</v>
       </c>
       <c r="D832" t="s">
         <v>834</v>
@@ -15790,7 +16078,7 @@
         <v>64</v>
       </c>
       <c r="C833">
-        <v>4710</v>
+        <v>5760</v>
       </c>
       <c r="D833" t="s">
         <v>835</v>
@@ -15804,7 +16092,7 @@
         <v>65</v>
       </c>
       <c r="C834">
-        <v>4840</v>
+        <v>5810</v>
       </c>
       <c r="D834" t="s">
         <v>836</v>
@@ -15818,7 +16106,7 @@
         <v>66</v>
       </c>
       <c r="C835">
-        <v>4980</v>
+        <v>5880</v>
       </c>
       <c r="D835" t="s">
         <v>837</v>
@@ -15832,7 +16120,7 @@
         <v>67</v>
       </c>
       <c r="C836">
-        <v>5130</v>
+        <v>5950</v>
       </c>
       <c r="D836" t="s">
         <v>838</v>
@@ -15846,7 +16134,7 @@
         <v>68</v>
       </c>
       <c r="C837">
-        <v>5300</v>
+        <v>6040</v>
       </c>
       <c r="D837" t="s">
         <v>839</v>
@@ -15860,7 +16148,7 @@
         <v>69</v>
       </c>
       <c r="C838">
-        <v>5460</v>
+        <v>6130</v>
       </c>
       <c r="D838" t="s">
         <v>840</v>
@@ -15874,7 +16162,7 @@
         <v>70</v>
       </c>
       <c r="C839">
-        <v>5630</v>
+        <v>6220</v>
       </c>
       <c r="D839" t="s">
         <v>841</v>
@@ -15888,7 +16176,7 @@
         <v>71</v>
       </c>
       <c r="C840">
-        <v>5800</v>
+        <v>6310</v>
       </c>
       <c r="D840" t="s">
         <v>842</v>
@@ -15902,7 +16190,7 @@
         <v>72</v>
       </c>
       <c r="C841">
-        <v>5960</v>
+        <v>6400</v>
       </c>
       <c r="D841" t="s">
         <v>843</v>
@@ -15916,7 +16204,7 @@
         <v>73</v>
       </c>
       <c r="C842">
-        <v>6120</v>
+        <v>6490</v>
       </c>
       <c r="D842" t="s">
         <v>844</v>
@@ -15930,7 +16218,7 @@
         <v>74</v>
       </c>
       <c r="C843">
-        <v>6260</v>
+        <v>6590</v>
       </c>
       <c r="D843" t="s">
         <v>845</v>
@@ -15944,7 +16232,7 @@
         <v>75</v>
       </c>
       <c r="C844">
-        <v>6400</v>
+        <v>6710</v>
       </c>
       <c r="D844" t="s">
         <v>846</v>
@@ -15958,7 +16246,7 @@
         <v>76</v>
       </c>
       <c r="C845">
-        <v>6540</v>
+        <v>6830</v>
       </c>
       <c r="D845" t="s">
         <v>847</v>
@@ -15972,7 +16260,7 @@
         <v>77</v>
       </c>
       <c r="C846">
-        <v>6670</v>
+        <v>6950</v>
       </c>
       <c r="D846" t="s">
         <v>848</v>
@@ -15986,7 +16274,7 @@
         <v>78</v>
       </c>
       <c r="C847">
-        <v>6800</v>
+        <v>7050</v>
       </c>
       <c r="D847" t="s">
         <v>849</v>
@@ -16000,7 +16288,7 @@
         <v>79</v>
       </c>
       <c r="C848">
-        <v>6920</v>
+        <v>7100</v>
       </c>
       <c r="D848" t="s">
         <v>850</v>
@@ -16014,7 +16302,7 @@
         <v>80</v>
       </c>
       <c r="C849">
-        <v>7020</v>
+        <v>7100</v>
       </c>
       <c r="D849" t="s">
         <v>851</v>
@@ -16028,7 +16316,7 @@
         <v>81</v>
       </c>
       <c r="C850">
-        <v>7120</v>
+        <v>7100</v>
       </c>
       <c r="D850" t="s">
         <v>852</v>
@@ -16042,7 +16330,7 @@
         <v>82</v>
       </c>
       <c r="C851">
-        <v>7170</v>
+        <v>7100</v>
       </c>
       <c r="D851" t="s">
         <v>853</v>
@@ -16056,7 +16344,7 @@
         <v>83</v>
       </c>
       <c r="C852">
-        <v>7130</v>
+        <v>7080</v>
       </c>
       <c r="D852" t="s">
         <v>854</v>
@@ -16070,7 +16358,7 @@
         <v>84</v>
       </c>
       <c r="C853">
-        <v>7020</v>
+        <v>7000</v>
       </c>
       <c r="D853" t="s">
         <v>855</v>
@@ -16084,7 +16372,7 @@
         <v>85</v>
       </c>
       <c r="C854">
-        <v>6810</v>
+        <v>6860</v>
       </c>
       <c r="D854" t="s">
         <v>856</v>
@@ -16098,7 +16386,7 @@
         <v>86</v>
       </c>
       <c r="C855">
-        <v>6560</v>
+        <v>6690</v>
       </c>
       <c r="D855" t="s">
         <v>857</v>
@@ -16112,7 +16400,7 @@
         <v>87</v>
       </c>
       <c r="C856">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="D856" t="s">
         <v>858</v>
@@ -16126,7 +16414,7 @@
         <v>88</v>
       </c>
       <c r="C857">
-        <v>6280</v>
+        <v>6500</v>
       </c>
       <c r="D857" t="s">
         <v>859</v>
@@ -16140,7 +16428,7 @@
         <v>89</v>
       </c>
       <c r="C858">
-        <v>6120</v>
+        <v>6360</v>
       </c>
       <c r="D858" t="s">
         <v>860</v>
@@ -16154,7 +16442,7 @@
         <v>90</v>
       </c>
       <c r="C859">
-        <v>5960</v>
+        <v>6230</v>
       </c>
       <c r="D859" t="s">
         <v>861</v>
@@ -16168,7 +16456,7 @@
         <v>91</v>
       </c>
       <c r="C860">
-        <v>5730</v>
+        <v>6060</v>
       </c>
       <c r="D860" t="s">
         <v>862</v>
@@ -16182,7 +16470,7 @@
         <v>92</v>
       </c>
       <c r="C861">
-        <v>5600</v>
+        <v>5950</v>
       </c>
       <c r="D861" t="s">
         <v>863</v>
@@ -16196,7 +16484,7 @@
         <v>93</v>
       </c>
       <c r="C862">
-        <v>5470</v>
+        <v>5870</v>
       </c>
       <c r="D862" t="s">
         <v>864</v>
@@ -16210,7 +16498,7 @@
         <v>94</v>
       </c>
       <c r="C863">
-        <v>5350</v>
+        <v>5720</v>
       </c>
       <c r="D863" t="s">
         <v>865</v>
@@ -16224,7 +16512,7 @@
         <v>95</v>
       </c>
       <c r="C864">
-        <v>5280</v>
+        <v>5630</v>
       </c>
       <c r="D864" t="s">
         <v>866</v>
@@ -16238,7 +16526,7 @@
         <v>96</v>
       </c>
       <c r="C865">
-        <v>5200</v>
+        <v>5520</v>
       </c>
       <c r="D865" t="s">
         <v>867</v>
@@ -21618,6 +21906,1350 @@
       </c>
       <c r="D1249" t="s">
         <v>1251</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4">
+      <c r="A1250" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1250">
+        <v>1</v>
+      </c>
+      <c r="C1250">
+        <v>5510</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4">
+      <c r="A1251" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1251">
+        <v>2</v>
+      </c>
+      <c r="C1251">
+        <v>5470</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4">
+      <c r="A1252" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1252">
+        <v>3</v>
+      </c>
+      <c r="C1252">
+        <v>5410</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4">
+      <c r="A1253" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1253">
+        <v>4</v>
+      </c>
+      <c r="C1253">
+        <v>5340</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4">
+      <c r="A1254" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1254">
+        <v>5</v>
+      </c>
+      <c r="C1254">
+        <v>5290</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4">
+      <c r="A1255" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1255">
+        <v>6</v>
+      </c>
+      <c r="C1255">
+        <v>5250</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4">
+      <c r="A1256" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1256">
+        <v>7</v>
+      </c>
+      <c r="C1256">
+        <v>5220</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4">
+      <c r="A1257" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1257">
+        <v>8</v>
+      </c>
+      <c r="C1257">
+        <v>5200</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4">
+      <c r="A1258" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1258">
+        <v>9</v>
+      </c>
+      <c r="C1258">
+        <v>5180</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4">
+      <c r="A1259" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1259">
+        <v>10</v>
+      </c>
+      <c r="C1259">
+        <v>5170</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4">
+      <c r="A1260" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1260">
+        <v>11</v>
+      </c>
+      <c r="C1260">
+        <v>5160</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4">
+      <c r="A1261" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1261">
+        <v>12</v>
+      </c>
+      <c r="C1261">
+        <v>5170</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4">
+      <c r="A1262" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1262">
+        <v>13</v>
+      </c>
+      <c r="C1262">
+        <v>5170</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4">
+      <c r="A1263" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1263">
+        <v>14</v>
+      </c>
+      <c r="C1263">
+        <v>5180</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4">
+      <c r="A1264" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1264">
+        <v>15</v>
+      </c>
+      <c r="C1264">
+        <v>5190</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4">
+      <c r="A1265" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1265">
+        <v>16</v>
+      </c>
+      <c r="C1265">
+        <v>5200</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4">
+      <c r="A1266" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1266">
+        <v>17</v>
+      </c>
+      <c r="C1266">
+        <v>5210</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4">
+      <c r="A1267" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1267">
+        <v>18</v>
+      </c>
+      <c r="C1267">
+        <v>5220</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4">
+      <c r="A1268" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1268">
+        <v>19</v>
+      </c>
+      <c r="C1268">
+        <v>5230</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4">
+      <c r="A1269" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1269">
+        <v>20</v>
+      </c>
+      <c r="C1269">
+        <v>5250</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4">
+      <c r="A1270" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1270">
+        <v>21</v>
+      </c>
+      <c r="C1270">
+        <v>5280</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4">
+      <c r="A1271" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1271">
+        <v>22</v>
+      </c>
+      <c r="C1271">
+        <v>5340</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4">
+      <c r="A1272" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1272">
+        <v>23</v>
+      </c>
+      <c r="C1272">
+        <v>5410</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4">
+      <c r="A1273" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1273">
+        <v>24</v>
+      </c>
+      <c r="C1273">
+        <v>5520</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4">
+      <c r="A1274" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1274">
+        <v>25</v>
+      </c>
+      <c r="C1274">
+        <v>5650</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4">
+      <c r="A1275" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1275">
+        <v>26</v>
+      </c>
+      <c r="C1275">
+        <v>5790</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4">
+      <c r="A1276" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1276">
+        <v>27</v>
+      </c>
+      <c r="C1276">
+        <v>5960</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4">
+      <c r="A1277" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1277">
+        <v>28</v>
+      </c>
+      <c r="C1277">
+        <v>6130</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4">
+      <c r="A1278" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1278">
+        <v>29</v>
+      </c>
+      <c r="C1278">
+        <v>6290</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4">
+      <c r="A1279" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1279">
+        <v>30</v>
+      </c>
+      <c r="C1279">
+        <v>6440</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4">
+      <c r="A1280" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1280">
+        <v>31</v>
+      </c>
+      <c r="C1280">
+        <v>6560</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4">
+      <c r="A1281" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1281">
+        <v>32</v>
+      </c>
+      <c r="C1281">
+        <v>6660</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4">
+      <c r="A1282" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1282">
+        <v>33</v>
+      </c>
+      <c r="C1282">
+        <v>6720</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4">
+      <c r="A1283" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1283">
+        <v>34</v>
+      </c>
+      <c r="C1283">
+        <v>6740</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4">
+      <c r="A1284" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1284">
+        <v>35</v>
+      </c>
+      <c r="C1284">
+        <v>6730</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4">
+      <c r="A1285" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1285">
+        <v>36</v>
+      </c>
+      <c r="C1285">
+        <v>6690</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4">
+      <c r="A1286" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1286">
+        <v>37</v>
+      </c>
+      <c r="C1286">
+        <v>6630</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4">
+      <c r="A1287" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1287">
+        <v>38</v>
+      </c>
+      <c r="C1287">
+        <v>6560</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4">
+      <c r="A1288" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1288">
+        <v>39</v>
+      </c>
+      <c r="C1288">
+        <v>6480</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4">
+      <c r="A1289" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1289">
+        <v>40</v>
+      </c>
+      <c r="C1289">
+        <v>6390</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4">
+      <c r="A1290" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1290">
+        <v>41</v>
+      </c>
+      <c r="C1290">
+        <v>6320</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4">
+      <c r="A1291" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1291">
+        <v>42</v>
+      </c>
+      <c r="C1291">
+        <v>6250</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4">
+      <c r="A1292" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1292">
+        <v>43</v>
+      </c>
+      <c r="C1292">
+        <v>6190</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4">
+      <c r="A1293" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1293">
+        <v>44</v>
+      </c>
+      <c r="C1293">
+        <v>6140</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4">
+      <c r="A1294" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1294">
+        <v>45</v>
+      </c>
+      <c r="C1294">
+        <v>6090</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4">
+      <c r="A1295" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1295">
+        <v>46</v>
+      </c>
+      <c r="C1295">
+        <v>6050</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4">
+      <c r="A1296" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1296">
+        <v>47</v>
+      </c>
+      <c r="C1296">
+        <v>6010</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4">
+      <c r="A1297" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1297">
+        <v>48</v>
+      </c>
+      <c r="C1297">
+        <v>5970</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4">
+      <c r="A1298" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1298">
+        <v>49</v>
+      </c>
+      <c r="C1298">
+        <v>5930</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4">
+      <c r="A1299" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1299">
+        <v>50</v>
+      </c>
+      <c r="C1299">
+        <v>5890</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4">
+      <c r="A1300" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1300">
+        <v>51</v>
+      </c>
+      <c r="C1300">
+        <v>5860</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4">
+      <c r="A1301" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1301">
+        <v>52</v>
+      </c>
+      <c r="C1301">
+        <v>5830</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4">
+      <c r="A1302" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1302">
+        <v>53</v>
+      </c>
+      <c r="C1302">
+        <v>5810</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4">
+      <c r="A1303" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1303">
+        <v>54</v>
+      </c>
+      <c r="C1303">
+        <v>5800</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4">
+      <c r="A1304" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1304">
+        <v>55</v>
+      </c>
+      <c r="C1304">
+        <v>5810</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4">
+      <c r="A1305" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1305">
+        <v>56</v>
+      </c>
+      <c r="C1305">
+        <v>5820</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4">
+      <c r="A1306" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1306">
+        <v>57</v>
+      </c>
+      <c r="C1306">
+        <v>5830</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4">
+      <c r="A1307" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1307">
+        <v>58</v>
+      </c>
+      <c r="C1307">
+        <v>5840</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4">
+      <c r="A1308" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1308">
+        <v>59</v>
+      </c>
+      <c r="C1308">
+        <v>5860</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4">
+      <c r="A1309" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1309">
+        <v>60</v>
+      </c>
+      <c r="C1309">
+        <v>5870</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4">
+      <c r="A1310" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1310">
+        <v>61</v>
+      </c>
+      <c r="C1310">
+        <v>5890</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4">
+      <c r="A1311" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1311">
+        <v>62</v>
+      </c>
+      <c r="C1311">
+        <v>5900</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4">
+      <c r="A1312" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1312">
+        <v>63</v>
+      </c>
+      <c r="C1312">
+        <v>5930</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4">
+      <c r="A1313" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1313">
+        <v>64</v>
+      </c>
+      <c r="C1313">
+        <v>5970</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4">
+      <c r="A1314" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1314">
+        <v>65</v>
+      </c>
+      <c r="C1314">
+        <v>6020</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4">
+      <c r="A1315" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1315">
+        <v>66</v>
+      </c>
+      <c r="C1315">
+        <v>6090</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4">
+      <c r="A1316" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1316">
+        <v>67</v>
+      </c>
+      <c r="C1316">
+        <v>6180</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4">
+      <c r="A1317" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1317">
+        <v>68</v>
+      </c>
+      <c r="C1317">
+        <v>6270</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4">
+      <c r="A1318" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1318">
+        <v>69</v>
+      </c>
+      <c r="C1318">
+        <v>6360</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4">
+      <c r="A1319" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1319">
+        <v>70</v>
+      </c>
+      <c r="C1319">
+        <v>6440</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4">
+      <c r="A1320" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1320">
+        <v>71</v>
+      </c>
+      <c r="C1320">
+        <v>6520</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4">
+      <c r="A1321" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1321">
+        <v>72</v>
+      </c>
+      <c r="C1321">
+        <v>6590</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4">
+      <c r="A1322" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1322">
+        <v>73</v>
+      </c>
+      <c r="C1322">
+        <v>6670</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4">
+      <c r="A1323" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1323">
+        <v>74</v>
+      </c>
+      <c r="C1323">
+        <v>6770</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4">
+      <c r="A1324" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1324">
+        <v>75</v>
+      </c>
+      <c r="C1324">
+        <v>6880</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4">
+      <c r="A1325" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1325">
+        <v>76</v>
+      </c>
+      <c r="C1325">
+        <v>7010</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4">
+      <c r="A1326" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1326">
+        <v>77</v>
+      </c>
+      <c r="C1326">
+        <v>7150</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4">
+      <c r="A1327" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1327">
+        <v>78</v>
+      </c>
+      <c r="C1327">
+        <v>7270</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4">
+      <c r="A1328" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1328">
+        <v>79</v>
+      </c>
+      <c r="C1328">
+        <v>7360</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4">
+      <c r="A1329" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1329">
+        <v>80</v>
+      </c>
+      <c r="C1329">
+        <v>7390</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4">
+      <c r="A1330" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1330">
+        <v>81</v>
+      </c>
+      <c r="C1330">
+        <v>7390</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4">
+      <c r="A1331" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1331">
+        <v>82</v>
+      </c>
+      <c r="C1331">
+        <v>7370</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4">
+      <c r="A1332" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1332">
+        <v>83</v>
+      </c>
+      <c r="C1332">
+        <v>7300</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4">
+      <c r="A1333" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1333">
+        <v>84</v>
+      </c>
+      <c r="C1333">
+        <v>7230</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4">
+      <c r="A1334" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1334">
+        <v>85</v>
+      </c>
+      <c r="C1334">
+        <v>7110</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4">
+      <c r="A1335" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1335">
+        <v>86</v>
+      </c>
+      <c r="C1335">
+        <v>6970</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4">
+      <c r="A1336" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1336">
+        <v>87</v>
+      </c>
+      <c r="C1336">
+        <v>6880</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4">
+      <c r="A1337" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1337">
+        <v>88</v>
+      </c>
+      <c r="C1337">
+        <v>6770</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4">
+      <c r="A1338" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1338">
+        <v>89</v>
+      </c>
+      <c r="C1338">
+        <v>6620</v>
+      </c>
+      <c r="D1338" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4">
+      <c r="A1339" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1339">
+        <v>90</v>
+      </c>
+      <c r="C1339">
+        <v>6500</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4">
+      <c r="A1340" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1340">
+        <v>91</v>
+      </c>
+      <c r="C1340">
+        <v>6340</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4">
+      <c r="A1341" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1341">
+        <v>92</v>
+      </c>
+      <c r="C1341">
+        <v>6200</v>
+      </c>
+      <c r="D1341" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4">
+      <c r="A1342" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1342">
+        <v>93</v>
+      </c>
+      <c r="C1342">
+        <v>6050</v>
+      </c>
+      <c r="D1342" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4">
+      <c r="A1343" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1343">
+        <v>94</v>
+      </c>
+      <c r="C1343">
+        <v>5890</v>
+      </c>
+      <c r="D1343" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4">
+      <c r="A1344" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1344">
+        <v>95</v>
+      </c>
+      <c r="C1344">
+        <v>5800</v>
+      </c>
+      <c r="D1344" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4">
+      <c r="A1345" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1345">
+        <v>96</v>
+      </c>
+      <c r="C1345">
+        <v>5690</v>
+      </c>
+      <c r="D1345" t="s">
+        <v>1347</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -13852,7 +13852,7 @@
         <v>1</v>
       </c>
       <c r="C674">
-        <v>5440</v>
+        <v>5220</v>
       </c>
       <c r="D674" t="s">
         <v>676</v>
@@ -13866,7 +13866,7 @@
         <v>2</v>
       </c>
       <c r="C675">
-        <v>5400</v>
+        <v>5170</v>
       </c>
       <c r="D675" t="s">
         <v>677</v>
@@ -13880,7 +13880,7 @@
         <v>3</v>
       </c>
       <c r="C676">
-        <v>5350</v>
+        <v>5130</v>
       </c>
       <c r="D676" t="s">
         <v>678</v>
@@ -13894,7 +13894,7 @@
         <v>4</v>
       </c>
       <c r="C677">
-        <v>5260</v>
+        <v>5120</v>
       </c>
       <c r="D677" t="s">
         <v>679</v>
@@ -13908,7 +13908,7 @@
         <v>5</v>
       </c>
       <c r="C678">
-        <v>5180</v>
+        <v>5100</v>
       </c>
       <c r="D678" t="s">
         <v>680</v>
@@ -13922,7 +13922,7 @@
         <v>6</v>
       </c>
       <c r="C679">
-        <v>5130</v>
+        <v>5100</v>
       </c>
       <c r="D679" t="s">
         <v>681</v>
@@ -13950,7 +13950,7 @@
         <v>8</v>
       </c>
       <c r="C681">
-        <v>5090</v>
+        <v>5100</v>
       </c>
       <c r="D681" t="s">
         <v>683</v>
@@ -14006,7 +14006,7 @@
         <v>12</v>
       </c>
       <c r="C685">
-        <v>5100</v>
+        <v>5110</v>
       </c>
       <c r="D685" t="s">
         <v>687</v>
@@ -14020,7 +14020,7 @@
         <v>13</v>
       </c>
       <c r="C686">
-        <v>5110</v>
+        <v>5120</v>
       </c>
       <c r="D686" t="s">
         <v>688</v>
@@ -14034,7 +14034,7 @@
         <v>14</v>
       </c>
       <c r="C687">
-        <v>5110</v>
+        <v>5150</v>
       </c>
       <c r="D687" t="s">
         <v>689</v>
@@ -14048,7 +14048,7 @@
         <v>15</v>
       </c>
       <c r="C688">
-        <v>5120</v>
+        <v>5150</v>
       </c>
       <c r="D688" t="s">
         <v>690</v>
@@ -14062,7 +14062,7 @@
         <v>16</v>
       </c>
       <c r="C689">
-        <v>5130</v>
+        <v>5150</v>
       </c>
       <c r="D689" t="s">
         <v>691</v>
@@ -14076,7 +14076,7 @@
         <v>17</v>
       </c>
       <c r="C690">
-        <v>5140</v>
+        <v>5150</v>
       </c>
       <c r="D690" t="s">
         <v>692</v>
@@ -14104,7 +14104,7 @@
         <v>19</v>
       </c>
       <c r="C692">
-        <v>5170</v>
+        <v>5150</v>
       </c>
       <c r="D692" t="s">
         <v>694</v>
@@ -14118,7 +14118,7 @@
         <v>20</v>
       </c>
       <c r="C693">
-        <v>5190</v>
+        <v>5150</v>
       </c>
       <c r="D693" t="s">
         <v>695</v>
@@ -14132,7 +14132,7 @@
         <v>21</v>
       </c>
       <c r="C694">
-        <v>5220</v>
+        <v>5140</v>
       </c>
       <c r="D694" t="s">
         <v>696</v>
@@ -14146,7 +14146,7 @@
         <v>22</v>
       </c>
       <c r="C695">
-        <v>5270</v>
+        <v>5140</v>
       </c>
       <c r="D695" t="s">
         <v>697</v>
@@ -14160,7 +14160,7 @@
         <v>23</v>
       </c>
       <c r="C696">
-        <v>5340</v>
+        <v>5150</v>
       </c>
       <c r="D696" t="s">
         <v>698</v>
@@ -14174,7 +14174,7 @@
         <v>24</v>
       </c>
       <c r="C697">
-        <v>5430</v>
+        <v>5150</v>
       </c>
       <c r="D697" t="s">
         <v>699</v>
@@ -14188,7 +14188,7 @@
         <v>25</v>
       </c>
       <c r="C698">
-        <v>5540</v>
+        <v>5490</v>
       </c>
       <c r="D698" t="s">
         <v>700</v>
@@ -14202,7 +14202,7 @@
         <v>26</v>
       </c>
       <c r="C699">
-        <v>5680</v>
+        <v>5690</v>
       </c>
       <c r="D699" t="s">
         <v>701</v>
@@ -14230,7 +14230,7 @@
         <v>28</v>
       </c>
       <c r="C701">
-        <v>5990</v>
+        <v>6000</v>
       </c>
       <c r="D701" t="s">
         <v>703</v>
@@ -14244,7 +14244,7 @@
         <v>29</v>
       </c>
       <c r="C702">
-        <v>6150</v>
+        <v>6160</v>
       </c>
       <c r="D702" t="s">
         <v>704</v>
@@ -14272,7 +14272,7 @@
         <v>31</v>
       </c>
       <c r="C704">
-        <v>6410</v>
+        <v>6390</v>
       </c>
       <c r="D704" t="s">
         <v>706</v>
@@ -14286,7 +14286,7 @@
         <v>32</v>
       </c>
       <c r="C705">
-        <v>6500</v>
+        <v>6440</v>
       </c>
       <c r="D705" t="s">
         <v>707</v>
@@ -14300,7 +14300,7 @@
         <v>33</v>
       </c>
       <c r="C706">
-        <v>6550</v>
+        <v>6450</v>
       </c>
       <c r="D706" t="s">
         <v>708</v>
@@ -14314,7 +14314,7 @@
         <v>34</v>
       </c>
       <c r="C707">
-        <v>6540</v>
+        <v>6440</v>
       </c>
       <c r="D707" t="s">
         <v>709</v>
@@ -14328,7 +14328,7 @@
         <v>35</v>
       </c>
       <c r="C708">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="D708" t="s">
         <v>710</v>
@@ -14342,7 +14342,7 @@
         <v>36</v>
       </c>
       <c r="C709">
-        <v>6410</v>
+        <v>6340</v>
       </c>
       <c r="D709" t="s">
         <v>711</v>
@@ -14356,7 +14356,7 @@
         <v>37</v>
       </c>
       <c r="C710">
-        <v>6290</v>
+        <v>6230</v>
       </c>
       <c r="D710" t="s">
         <v>712</v>
@@ -14370,7 +14370,7 @@
         <v>38</v>
       </c>
       <c r="C711">
-        <v>6140</v>
+        <v>6100</v>
       </c>
       <c r="D711" t="s">
         <v>713</v>
@@ -14384,7 +14384,7 @@
         <v>39</v>
       </c>
       <c r="C712">
-        <v>5970</v>
+        <v>5930</v>
       </c>
       <c r="D712" t="s">
         <v>714</v>
@@ -14398,7 +14398,7 @@
         <v>40</v>
       </c>
       <c r="C713">
-        <v>5800</v>
+        <v>5730</v>
       </c>
       <c r="D713" t="s">
         <v>715</v>
@@ -14412,7 +14412,7 @@
         <v>41</v>
       </c>
       <c r="C714">
-        <v>5620</v>
+        <v>5470</v>
       </c>
       <c r="D714" t="s">
         <v>716</v>
@@ -14426,7 +14426,7 @@
         <v>42</v>
       </c>
       <c r="C715">
-        <v>5450</v>
+        <v>5260</v>
       </c>
       <c r="D715" t="s">
         <v>717</v>
@@ -14440,7 +14440,7 @@
         <v>43</v>
       </c>
       <c r="C716">
-        <v>5290</v>
+        <v>5070</v>
       </c>
       <c r="D716" t="s">
         <v>718</v>
@@ -14454,7 +14454,7 @@
         <v>44</v>
       </c>
       <c r="C717">
-        <v>5150</v>
+        <v>4890</v>
       </c>
       <c r="D717" t="s">
         <v>719</v>
@@ -14468,7 +14468,7 @@
         <v>45</v>
       </c>
       <c r="C718">
-        <v>5030</v>
+        <v>4750</v>
       </c>
       <c r="D718" t="s">
         <v>720</v>
@@ -14482,7 +14482,7 @@
         <v>46</v>
       </c>
       <c r="C719">
-        <v>4920</v>
+        <v>4640</v>
       </c>
       <c r="D719" t="s">
         <v>721</v>
@@ -14496,7 +14496,7 @@
         <v>47</v>
       </c>
       <c r="C720">
-        <v>4820</v>
+        <v>4540</v>
       </c>
       <c r="D720" t="s">
         <v>722</v>
@@ -14510,7 +14510,7 @@
         <v>48</v>
       </c>
       <c r="C721">
-        <v>4740</v>
+        <v>4470</v>
       </c>
       <c r="D721" t="s">
         <v>723</v>
@@ -14524,7 +14524,7 @@
         <v>49</v>
       </c>
       <c r="C722">
-        <v>4680</v>
+        <v>4430</v>
       </c>
       <c r="D722" t="s">
         <v>724</v>
@@ -14538,7 +14538,7 @@
         <v>50</v>
       </c>
       <c r="C723">
-        <v>4630</v>
+        <v>4420</v>
       </c>
       <c r="D723" t="s">
         <v>725</v>
@@ -14552,7 +14552,7 @@
         <v>51</v>
       </c>
       <c r="C724">
-        <v>4600</v>
+        <v>4420</v>
       </c>
       <c r="D724" t="s">
         <v>726</v>
@@ -14566,7 +14566,7 @@
         <v>52</v>
       </c>
       <c r="C725">
-        <v>4580</v>
+        <v>4420</v>
       </c>
       <c r="D725" t="s">
         <v>727</v>
@@ -14580,7 +14580,7 @@
         <v>53</v>
       </c>
       <c r="C726">
-        <v>4580</v>
+        <v>4500</v>
       </c>
       <c r="D726" t="s">
         <v>728</v>
@@ -14594,7 +14594,7 @@
         <v>54</v>
       </c>
       <c r="C727">
-        <v>4590</v>
+        <v>4520</v>
       </c>
       <c r="D727" t="s">
         <v>729</v>
@@ -14608,7 +14608,7 @@
         <v>55</v>
       </c>
       <c r="C728">
-        <v>4610</v>
+        <v>4530</v>
       </c>
       <c r="D728" t="s">
         <v>730</v>
@@ -14622,7 +14622,7 @@
         <v>56</v>
       </c>
       <c r="C729">
-        <v>4640</v>
+        <v>4540</v>
       </c>
       <c r="D729" t="s">
         <v>731</v>
@@ -14636,7 +14636,7 @@
         <v>57</v>
       </c>
       <c r="C730">
-        <v>4670</v>
+        <v>4550</v>
       </c>
       <c r="D730" t="s">
         <v>732</v>
@@ -14650,7 +14650,7 @@
         <v>58</v>
       </c>
       <c r="C731">
-        <v>4710</v>
+        <v>4550</v>
       </c>
       <c r="D731" t="s">
         <v>733</v>
@@ -14664,7 +14664,7 @@
         <v>59</v>
       </c>
       <c r="C732">
-        <v>4740</v>
+        <v>4550</v>
       </c>
       <c r="D732" t="s">
         <v>734</v>
@@ -14678,7 +14678,7 @@
         <v>60</v>
       </c>
       <c r="C733">
-        <v>4780</v>
+        <v>4570</v>
       </c>
       <c r="D733" t="s">
         <v>735</v>
@@ -14692,7 +14692,7 @@
         <v>61</v>
       </c>
       <c r="C734">
-        <v>4820</v>
+        <v>4630</v>
       </c>
       <c r="D734" t="s">
         <v>736</v>
@@ -14706,7 +14706,7 @@
         <v>62</v>
       </c>
       <c r="C735">
-        <v>4870</v>
+        <v>4710</v>
       </c>
       <c r="D735" t="s">
         <v>737</v>
@@ -14720,7 +14720,7 @@
         <v>63</v>
       </c>
       <c r="C736">
-        <v>4930</v>
+        <v>4780</v>
       </c>
       <c r="D736" t="s">
         <v>738</v>
@@ -14734,7 +14734,7 @@
         <v>64</v>
       </c>
       <c r="C737">
-        <v>5000</v>
+        <v>4880</v>
       </c>
       <c r="D737" t="s">
         <v>739</v>
@@ -14748,7 +14748,7 @@
         <v>65</v>
       </c>
       <c r="C738">
-        <v>5100</v>
+        <v>4990</v>
       </c>
       <c r="D738" t="s">
         <v>740</v>
@@ -14762,7 +14762,7 @@
         <v>66</v>
       </c>
       <c r="C739">
-        <v>5210</v>
+        <v>5120</v>
       </c>
       <c r="D739" t="s">
         <v>741</v>
@@ -14776,7 +14776,7 @@
         <v>67</v>
       </c>
       <c r="C740">
-        <v>5340</v>
+        <v>5270</v>
       </c>
       <c r="D740" t="s">
         <v>742</v>
@@ -14790,7 +14790,7 @@
         <v>68</v>
       </c>
       <c r="C741">
-        <v>5480</v>
+        <v>5430</v>
       </c>
       <c r="D741" t="s">
         <v>743</v>
@@ -14804,7 +14804,7 @@
         <v>69</v>
       </c>
       <c r="C742">
-        <v>5630</v>
+        <v>5610</v>
       </c>
       <c r="D742" t="s">
         <v>744</v>
@@ -14832,7 +14832,7 @@
         <v>71</v>
       </c>
       <c r="C744">
-        <v>5940</v>
+        <v>5930</v>
       </c>
       <c r="D744" t="s">
         <v>746</v>
@@ -14846,7 +14846,7 @@
         <v>72</v>
       </c>
       <c r="C745">
-        <v>6090</v>
+        <v>6080</v>
       </c>
       <c r="D745" t="s">
         <v>747</v>
@@ -14860,7 +14860,7 @@
         <v>73</v>
       </c>
       <c r="C746">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="D746" t="s">
         <v>748</v>
@@ -14874,7 +14874,7 @@
         <v>74</v>
       </c>
       <c r="C747">
-        <v>6410</v>
+        <v>6380</v>
       </c>
       <c r="D747" t="s">
         <v>749</v>
@@ -14888,7 +14888,7 @@
         <v>75</v>
       </c>
       <c r="C748">
-        <v>6580</v>
+        <v>6520</v>
       </c>
       <c r="D748" t="s">
         <v>750</v>
@@ -14902,7 +14902,7 @@
         <v>76</v>
       </c>
       <c r="C749">
-        <v>6740</v>
+        <v>6660</v>
       </c>
       <c r="D749" t="s">
         <v>751</v>
@@ -14916,7 +14916,7 @@
         <v>77</v>
       </c>
       <c r="C750">
-        <v>6890</v>
+        <v>6820</v>
       </c>
       <c r="D750" t="s">
         <v>752</v>
@@ -14930,7 +14930,7 @@
         <v>78</v>
       </c>
       <c r="C751">
-        <v>7020</v>
+        <v>6930</v>
       </c>
       <c r="D751" t="s">
         <v>753</v>
@@ -14944,7 +14944,7 @@
         <v>79</v>
       </c>
       <c r="C752">
-        <v>7100</v>
+        <v>7010</v>
       </c>
       <c r="D752" t="s">
         <v>754</v>
@@ -14958,7 +14958,7 @@
         <v>80</v>
       </c>
       <c r="C753">
-        <v>7100</v>
+        <v>7040</v>
       </c>
       <c r="D753" t="s">
         <v>755</v>
@@ -14972,7 +14972,7 @@
         <v>81</v>
       </c>
       <c r="C754">
-        <v>7100</v>
+        <v>7030</v>
       </c>
       <c r="D754" t="s">
         <v>756</v>
@@ -14986,7 +14986,7 @@
         <v>82</v>
       </c>
       <c r="C755">
-        <v>7100</v>
+        <v>6990</v>
       </c>
       <c r="D755" t="s">
         <v>757</v>
@@ -15000,7 +15000,7 @@
         <v>83</v>
       </c>
       <c r="C756">
-        <v>7080</v>
+        <v>6930</v>
       </c>
       <c r="D756" t="s">
         <v>758</v>
@@ -15014,7 +15014,7 @@
         <v>84</v>
       </c>
       <c r="C757">
-        <v>6980</v>
+        <v>6850</v>
       </c>
       <c r="D757" t="s">
         <v>759</v>
@@ -15028,7 +15028,7 @@
         <v>85</v>
       </c>
       <c r="C758">
-        <v>6820</v>
+        <v>6730</v>
       </c>
       <c r="D758" t="s">
         <v>760</v>
@@ -15042,7 +15042,7 @@
         <v>86</v>
       </c>
       <c r="C759">
-        <v>6650</v>
+        <v>6610</v>
       </c>
       <c r="D759" t="s">
         <v>761</v>
@@ -15056,7 +15056,7 @@
         <v>87</v>
       </c>
       <c r="C760">
-        <v>6540</v>
+        <v>6500</v>
       </c>
       <c r="D760" t="s">
         <v>762</v>
@@ -15070,7 +15070,7 @@
         <v>88</v>
       </c>
       <c r="C761">
-        <v>6450</v>
+        <v>6360</v>
       </c>
       <c r="D761" t="s">
         <v>763</v>
@@ -15084,7 +15084,7 @@
         <v>89</v>
       </c>
       <c r="C762">
-        <v>6330</v>
+        <v>6180</v>
       </c>
       <c r="D762" t="s">
         <v>764</v>
@@ -15098,7 +15098,7 @@
         <v>90</v>
       </c>
       <c r="C763">
-        <v>6220</v>
+        <v>6030</v>
       </c>
       <c r="D763" t="s">
         <v>765</v>
@@ -15112,7 +15112,7 @@
         <v>91</v>
       </c>
       <c r="C764">
-        <v>6040</v>
+        <v>5890</v>
       </c>
       <c r="D764" t="s">
         <v>766</v>
@@ -15126,7 +15126,7 @@
         <v>92</v>
       </c>
       <c r="C765">
-        <v>5920</v>
+        <v>5780</v>
       </c>
       <c r="D765" t="s">
         <v>767</v>
@@ -15140,7 +15140,7 @@
         <v>93</v>
       </c>
       <c r="C766">
-        <v>5830</v>
+        <v>5680</v>
       </c>
       <c r="D766" t="s">
         <v>768</v>
@@ -15154,7 +15154,7 @@
         <v>94</v>
       </c>
       <c r="C767">
-        <v>5670</v>
+        <v>5570</v>
       </c>
       <c r="D767" t="s">
         <v>769</v>
@@ -15168,7 +15168,7 @@
         <v>95</v>
       </c>
       <c r="C768">
-        <v>5580</v>
+        <v>5450</v>
       </c>
       <c r="D768" t="s">
         <v>770</v>
@@ -15182,7 +15182,7 @@
         <v>96</v>
       </c>
       <c r="C769">
-        <v>5470</v>
+        <v>5340</v>
       </c>
       <c r="D769" t="s">
         <v>771</v>
@@ -15196,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="C770">
-        <v>5460</v>
+        <v>5350</v>
       </c>
       <c r="D770" t="s">
         <v>772</v>
@@ -15210,7 +15210,7 @@
         <v>2</v>
       </c>
       <c r="C771">
-        <v>5420</v>
+        <v>5300</v>
       </c>
       <c r="D771" t="s">
         <v>773</v>
@@ -15224,7 +15224,7 @@
         <v>3</v>
       </c>
       <c r="C772">
-        <v>5360</v>
+        <v>5240</v>
       </c>
       <c r="D772" t="s">
         <v>774</v>
@@ -15238,7 +15238,7 @@
         <v>4</v>
       </c>
       <c r="C773">
-        <v>5280</v>
+        <v>5170</v>
       </c>
       <c r="D773" t="s">
         <v>775</v>
@@ -15252,7 +15252,7 @@
         <v>5</v>
       </c>
       <c r="C774">
-        <v>5220</v>
+        <v>5100</v>
       </c>
       <c r="D774" t="s">
         <v>776</v>
@@ -15266,7 +15266,7 @@
         <v>6</v>
       </c>
       <c r="C775">
-        <v>5180</v>
+        <v>5070</v>
       </c>
       <c r="D775" t="s">
         <v>777</v>
@@ -15280,7 +15280,7 @@
         <v>7</v>
       </c>
       <c r="C776">
-        <v>5160</v>
+        <v>5050</v>
       </c>
       <c r="D776" t="s">
         <v>778</v>
@@ -15294,7 +15294,7 @@
         <v>8</v>
       </c>
       <c r="C777">
-        <v>5140</v>
+        <v>5050</v>
       </c>
       <c r="D777" t="s">
         <v>779</v>
@@ -15308,7 +15308,7 @@
         <v>9</v>
       </c>
       <c r="C778">
-        <v>5120</v>
+        <v>5050</v>
       </c>
       <c r="D778" t="s">
         <v>780</v>
@@ -15322,7 +15322,7 @@
         <v>10</v>
       </c>
       <c r="C779">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="D779" t="s">
         <v>781</v>
@@ -15336,7 +15336,7 @@
         <v>11</v>
       </c>
       <c r="C780">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="D780" t="s">
         <v>782</v>
@@ -15350,7 +15350,7 @@
         <v>12</v>
       </c>
       <c r="C781">
-        <v>5120</v>
+        <v>5080</v>
       </c>
       <c r="D781" t="s">
         <v>783</v>
@@ -15364,7 +15364,7 @@
         <v>13</v>
       </c>
       <c r="C782">
-        <v>5120</v>
+        <v>5110</v>
       </c>
       <c r="D782" t="s">
         <v>784</v>
@@ -15378,7 +15378,7 @@
         <v>14</v>
       </c>
       <c r="C783">
-        <v>5140</v>
+        <v>5130</v>
       </c>
       <c r="D783" t="s">
         <v>785</v>
@@ -15420,7 +15420,7 @@
         <v>17</v>
       </c>
       <c r="C786">
-        <v>5180</v>
+        <v>5160</v>
       </c>
       <c r="D786" t="s">
         <v>788</v>
@@ -15434,7 +15434,7 @@
         <v>18</v>
       </c>
       <c r="C787">
-        <v>5190</v>
+        <v>5160</v>
       </c>
       <c r="D787" t="s">
         <v>789</v>
@@ -15448,7 +15448,7 @@
         <v>19</v>
       </c>
       <c r="C788">
-        <v>5210</v>
+        <v>5170</v>
       </c>
       <c r="D788" t="s">
         <v>790</v>
@@ -15462,7 +15462,7 @@
         <v>20</v>
       </c>
       <c r="C789">
-        <v>5250</v>
+        <v>5180</v>
       </c>
       <c r="D789" t="s">
         <v>791</v>
@@ -15476,7 +15476,7 @@
         <v>21</v>
       </c>
       <c r="C790">
-        <v>5290</v>
+        <v>5200</v>
       </c>
       <c r="D790" t="s">
         <v>792</v>
@@ -15490,7 +15490,7 @@
         <v>22</v>
       </c>
       <c r="C791">
-        <v>5360</v>
+        <v>5250</v>
       </c>
       <c r="D791" t="s">
         <v>793</v>
@@ -15504,7 +15504,7 @@
         <v>23</v>
       </c>
       <c r="C792">
-        <v>5450</v>
+        <v>5330</v>
       </c>
       <c r="D792" t="s">
         <v>794</v>
@@ -15518,7 +15518,7 @@
         <v>24</v>
       </c>
       <c r="C793">
-        <v>5560</v>
+        <v>5420</v>
       </c>
       <c r="D793" t="s">
         <v>795</v>
@@ -15532,7 +15532,7 @@
         <v>25</v>
       </c>
       <c r="C794">
-        <v>5690</v>
+        <v>5540</v>
       </c>
       <c r="D794" t="s">
         <v>796</v>
@@ -15546,7 +15546,7 @@
         <v>26</v>
       </c>
       <c r="C795">
-        <v>5830</v>
+        <v>5670</v>
       </c>
       <c r="D795" t="s">
         <v>797</v>
@@ -15560,7 +15560,7 @@
         <v>27</v>
       </c>
       <c r="C796">
-        <v>5980</v>
+        <v>5800</v>
       </c>
       <c r="D796" t="s">
         <v>798</v>
@@ -15574,7 +15574,7 @@
         <v>28</v>
       </c>
       <c r="C797">
-        <v>6140</v>
+        <v>5940</v>
       </c>
       <c r="D797" t="s">
         <v>799</v>
@@ -15588,7 +15588,7 @@
         <v>29</v>
       </c>
       <c r="C798">
-        <v>6290</v>
+        <v>6080</v>
       </c>
       <c r="D798" t="s">
         <v>800</v>
@@ -15602,7 +15602,7 @@
         <v>30</v>
       </c>
       <c r="C799">
-        <v>6420</v>
+        <v>6200</v>
       </c>
       <c r="D799" t="s">
         <v>801</v>
@@ -15616,7 +15616,7 @@
         <v>31</v>
       </c>
       <c r="C800">
-        <v>6530</v>
+        <v>6300</v>
       </c>
       <c r="D800" t="s">
         <v>802</v>
@@ -15630,7 +15630,7 @@
         <v>32</v>
       </c>
       <c r="C801">
-        <v>6610</v>
+        <v>6380</v>
       </c>
       <c r="D801" t="s">
         <v>803</v>
@@ -15644,7 +15644,7 @@
         <v>33</v>
       </c>
       <c r="C802">
-        <v>6650</v>
+        <v>6440</v>
       </c>
       <c r="D802" t="s">
         <v>804</v>
@@ -15658,7 +15658,7 @@
         <v>34</v>
       </c>
       <c r="C803">
-        <v>6650</v>
+        <v>6480</v>
       </c>
       <c r="D803" t="s">
         <v>805</v>
@@ -15672,7 +15672,7 @@
         <v>35</v>
       </c>
       <c r="C804">
-        <v>6650</v>
+        <v>6500</v>
       </c>
       <c r="D804" t="s">
         <v>806</v>
@@ -15686,7 +15686,7 @@
         <v>36</v>
       </c>
       <c r="C805">
-        <v>6630</v>
+        <v>6500</v>
       </c>
       <c r="D805" t="s">
         <v>807</v>
@@ -15700,7 +15700,7 @@
         <v>37</v>
       </c>
       <c r="C806">
-        <v>6560</v>
+        <v>6460</v>
       </c>
       <c r="D806" t="s">
         <v>808</v>
@@ -15714,7 +15714,7 @@
         <v>38</v>
       </c>
       <c r="C807">
-        <v>6490</v>
+        <v>6400</v>
       </c>
       <c r="D807" t="s">
         <v>809</v>
@@ -15728,7 +15728,7 @@
         <v>39</v>
       </c>
       <c r="C808">
-        <v>6400</v>
+        <v>6330</v>
       </c>
       <c r="D808" t="s">
         <v>810</v>
@@ -15742,7 +15742,7 @@
         <v>40</v>
       </c>
       <c r="C809">
-        <v>6310</v>
+        <v>6240</v>
       </c>
       <c r="D809" t="s">
         <v>811</v>
@@ -15756,7 +15756,7 @@
         <v>41</v>
       </c>
       <c r="C810">
-        <v>6220</v>
+        <v>6120</v>
       </c>
       <c r="D810" t="s">
         <v>812</v>
@@ -15770,7 +15770,7 @@
         <v>42</v>
       </c>
       <c r="C811">
-        <v>6130</v>
+        <v>6010</v>
       </c>
       <c r="D811" t="s">
         <v>813</v>
@@ -15784,7 +15784,7 @@
         <v>43</v>
       </c>
       <c r="C812">
-        <v>6050</v>
+        <v>5900</v>
       </c>
       <c r="D812" t="s">
         <v>814</v>
@@ -15798,7 +15798,7 @@
         <v>44</v>
       </c>
       <c r="C813">
-        <v>5980</v>
+        <v>5790</v>
       </c>
       <c r="D813" t="s">
         <v>815</v>
@@ -15812,7 +15812,7 @@
         <v>45</v>
       </c>
       <c r="C814">
-        <v>5910</v>
+        <v>5680</v>
       </c>
       <c r="D814" t="s">
         <v>816</v>
@@ -15826,7 +15826,7 @@
         <v>46</v>
       </c>
       <c r="C815">
-        <v>5860</v>
+        <v>5570</v>
       </c>
       <c r="D815" t="s">
         <v>817</v>
@@ -15840,7 +15840,7 @@
         <v>47</v>
       </c>
       <c r="C816">
-        <v>5800</v>
+        <v>5470</v>
       </c>
       <c r="D816" t="s">
         <v>818</v>
@@ -15854,7 +15854,7 @@
         <v>48</v>
       </c>
       <c r="C817">
-        <v>5750</v>
+        <v>5380</v>
       </c>
       <c r="D817" t="s">
         <v>819</v>
@@ -15868,7 +15868,7 @@
         <v>49</v>
       </c>
       <c r="C818">
-        <v>5710</v>
+        <v>5300</v>
       </c>
       <c r="D818" t="s">
         <v>820</v>
@@ -15882,7 +15882,7 @@
         <v>50</v>
       </c>
       <c r="C819">
-        <v>5670</v>
+        <v>5230</v>
       </c>
       <c r="D819" t="s">
         <v>821</v>
@@ -15896,7 +15896,7 @@
         <v>51</v>
       </c>
       <c r="C820">
-        <v>5640</v>
+        <v>5170</v>
       </c>
       <c r="D820" t="s">
         <v>822</v>
@@ -15910,7 +15910,7 @@
         <v>52</v>
       </c>
       <c r="C821">
-        <v>5620</v>
+        <v>5130</v>
       </c>
       <c r="D821" t="s">
         <v>823</v>
@@ -15924,7 +15924,7 @@
         <v>53</v>
       </c>
       <c r="C822">
-        <v>5600</v>
+        <v>5100</v>
       </c>
       <c r="D822" t="s">
         <v>824</v>
@@ -15938,7 +15938,7 @@
         <v>54</v>
       </c>
       <c r="C823">
-        <v>5600</v>
+        <v>5090</v>
       </c>
       <c r="D823" t="s">
         <v>825</v>
@@ -15952,7 +15952,7 @@
         <v>55</v>
       </c>
       <c r="C824">
-        <v>5600</v>
+        <v>5090</v>
       </c>
       <c r="D824" t="s">
         <v>826</v>
@@ -15966,7 +15966,7 @@
         <v>56</v>
       </c>
       <c r="C825">
-        <v>5600</v>
+        <v>5110</v>
       </c>
       <c r="D825" t="s">
         <v>827</v>
@@ -15980,7 +15980,7 @@
         <v>57</v>
       </c>
       <c r="C826">
-        <v>5610</v>
+        <v>5130</v>
       </c>
       <c r="D826" t="s">
         <v>828</v>
@@ -15994,7 +15994,7 @@
         <v>58</v>
       </c>
       <c r="C827">
-        <v>5620</v>
+        <v>5160</v>
       </c>
       <c r="D827" t="s">
         <v>829</v>
@@ -16008,7 +16008,7 @@
         <v>59</v>
       </c>
       <c r="C828">
-        <v>5630</v>
+        <v>5200</v>
       </c>
       <c r="D828" t="s">
         <v>830</v>
@@ -16022,7 +16022,7 @@
         <v>60</v>
       </c>
       <c r="C829">
-        <v>5650</v>
+        <v>5250</v>
       </c>
       <c r="D829" t="s">
         <v>831</v>
@@ -16036,7 +16036,7 @@
         <v>61</v>
       </c>
       <c r="C830">
-        <v>5660</v>
+        <v>5290</v>
       </c>
       <c r="D830" t="s">
         <v>832</v>
@@ -16050,7 +16050,7 @@
         <v>62</v>
       </c>
       <c r="C831">
-        <v>5680</v>
+        <v>5350</v>
       </c>
       <c r="D831" t="s">
         <v>833</v>
@@ -16064,7 +16064,7 @@
         <v>63</v>
       </c>
       <c r="C832">
-        <v>5710</v>
+        <v>5410</v>
       </c>
       <c r="D832" t="s">
         <v>834</v>
@@ -16078,7 +16078,7 @@
         <v>64</v>
       </c>
       <c r="C833">
-        <v>5760</v>
+        <v>5480</v>
       </c>
       <c r="D833" t="s">
         <v>835</v>
@@ -16092,7 +16092,7 @@
         <v>65</v>
       </c>
       <c r="C834">
-        <v>5810</v>
+        <v>5570</v>
       </c>
       <c r="D834" t="s">
         <v>836</v>
@@ -16106,7 +16106,7 @@
         <v>66</v>
       </c>
       <c r="C835">
-        <v>5880</v>
+        <v>5660</v>
       </c>
       <c r="D835" t="s">
         <v>837</v>
@@ -16120,7 +16120,7 @@
         <v>67</v>
       </c>
       <c r="C836">
-        <v>5950</v>
+        <v>5760</v>
       </c>
       <c r="D836" t="s">
         <v>838</v>
@@ -16134,7 +16134,7 @@
         <v>68</v>
       </c>
       <c r="C837">
-        <v>6040</v>
+        <v>5860</v>
       </c>
       <c r="D837" t="s">
         <v>839</v>
@@ -16148,7 +16148,7 @@
         <v>69</v>
       </c>
       <c r="C838">
-        <v>6130</v>
+        <v>5960</v>
       </c>
       <c r="D838" t="s">
         <v>840</v>
@@ -16162,7 +16162,7 @@
         <v>70</v>
       </c>
       <c r="C839">
-        <v>6220</v>
+        <v>6070</v>
       </c>
       <c r="D839" t="s">
         <v>841</v>
@@ -16176,7 +16176,7 @@
         <v>71</v>
       </c>
       <c r="C840">
-        <v>6310</v>
+        <v>6160</v>
       </c>
       <c r="D840" t="s">
         <v>842</v>
@@ -16190,7 +16190,7 @@
         <v>72</v>
       </c>
       <c r="C841">
-        <v>6400</v>
+        <v>6260</v>
       </c>
       <c r="D841" t="s">
         <v>843</v>
@@ -16204,7 +16204,7 @@
         <v>73</v>
       </c>
       <c r="C842">
-        <v>6490</v>
+        <v>6360</v>
       </c>
       <c r="D842" t="s">
         <v>844</v>
@@ -16218,7 +16218,7 @@
         <v>74</v>
       </c>
       <c r="C843">
-        <v>6590</v>
+        <v>6470</v>
       </c>
       <c r="D843" t="s">
         <v>845</v>
@@ -16232,7 +16232,7 @@
         <v>75</v>
       </c>
       <c r="C844">
-        <v>6710</v>
+        <v>6580</v>
       </c>
       <c r="D844" t="s">
         <v>846</v>
@@ -16246,7 +16246,7 @@
         <v>76</v>
       </c>
       <c r="C845">
-        <v>6830</v>
+        <v>6700</v>
       </c>
       <c r="D845" t="s">
         <v>847</v>
@@ -16260,7 +16260,7 @@
         <v>77</v>
       </c>
       <c r="C846">
-        <v>6950</v>
+        <v>6820</v>
       </c>
       <c r="D846" t="s">
         <v>848</v>
@@ -16274,7 +16274,7 @@
         <v>78</v>
       </c>
       <c r="C847">
-        <v>7050</v>
+        <v>6910</v>
       </c>
       <c r="D847" t="s">
         <v>849</v>
@@ -16288,7 +16288,7 @@
         <v>79</v>
       </c>
       <c r="C848">
-        <v>7100</v>
+        <v>6940</v>
       </c>
       <c r="D848" t="s">
         <v>850</v>
@@ -16302,7 +16302,7 @@
         <v>80</v>
       </c>
       <c r="C849">
-        <v>7100</v>
+        <v>6950</v>
       </c>
       <c r="D849" t="s">
         <v>851</v>
@@ -16316,7 +16316,7 @@
         <v>81</v>
       </c>
       <c r="C850">
-        <v>7100</v>
+        <v>6950</v>
       </c>
       <c r="D850" t="s">
         <v>852</v>
@@ -16330,7 +16330,7 @@
         <v>82</v>
       </c>
       <c r="C851">
-        <v>7100</v>
+        <v>6940</v>
       </c>
       <c r="D851" t="s">
         <v>853</v>
@@ -16344,7 +16344,7 @@
         <v>83</v>
       </c>
       <c r="C852">
-        <v>7080</v>
+        <v>6930</v>
       </c>
       <c r="D852" t="s">
         <v>854</v>
@@ -16358,7 +16358,7 @@
         <v>84</v>
       </c>
       <c r="C853">
-        <v>7000</v>
+        <v>6880</v>
       </c>
       <c r="D853" t="s">
         <v>855</v>
@@ -16372,7 +16372,7 @@
         <v>85</v>
       </c>
       <c r="C854">
-        <v>6860</v>
+        <v>6780</v>
       </c>
       <c r="D854" t="s">
         <v>856</v>
@@ -16386,7 +16386,7 @@
         <v>86</v>
       </c>
       <c r="C855">
-        <v>6690</v>
+        <v>6680</v>
       </c>
       <c r="D855" t="s">
         <v>857</v>
@@ -16400,7 +16400,7 @@
         <v>87</v>
       </c>
       <c r="C856">
-        <v>6600</v>
+        <v>6560</v>
       </c>
       <c r="D856" t="s">
         <v>858</v>
@@ -16414,7 +16414,7 @@
         <v>88</v>
       </c>
       <c r="C857">
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="D857" t="s">
         <v>859</v>
@@ -16428,7 +16428,7 @@
         <v>89</v>
       </c>
       <c r="C858">
-        <v>6360</v>
+        <v>6300</v>
       </c>
       <c r="D858" t="s">
         <v>860</v>
@@ -16442,7 +16442,7 @@
         <v>90</v>
       </c>
       <c r="C859">
-        <v>6230</v>
+        <v>6170</v>
       </c>
       <c r="D859" t="s">
         <v>861</v>
@@ -16456,7 +16456,7 @@
         <v>91</v>
       </c>
       <c r="C860">
-        <v>6060</v>
+        <v>6020</v>
       </c>
       <c r="D860" t="s">
         <v>862</v>
@@ -16470,7 +16470,7 @@
         <v>92</v>
       </c>
       <c r="C861">
-        <v>5950</v>
+        <v>5890</v>
       </c>
       <c r="D861" t="s">
         <v>863</v>
@@ -16484,7 +16484,7 @@
         <v>93</v>
       </c>
       <c r="C862">
-        <v>5870</v>
+        <v>5730</v>
       </c>
       <c r="D862" t="s">
         <v>864</v>
@@ -16498,7 +16498,7 @@
         <v>94</v>
       </c>
       <c r="C863">
-        <v>5720</v>
+        <v>5590</v>
       </c>
       <c r="D863" t="s">
         <v>865</v>
@@ -16512,7 +16512,7 @@
         <v>95</v>
       </c>
       <c r="C864">
-        <v>5630</v>
+        <v>5480</v>
       </c>
       <c r="D864" t="s">
         <v>866</v>
@@ -16526,7 +16526,7 @@
         <v>96</v>
       </c>
       <c r="C865">
-        <v>5520</v>
+        <v>5370</v>
       </c>
       <c r="D865" t="s">
         <v>867</v>
@@ -16540,7 +16540,7 @@
         <v>1</v>
       </c>
       <c r="C866">
-        <v>5180</v>
+        <v>5350</v>
       </c>
       <c r="D866" t="s">
         <v>868</v>
@@ -16554,7 +16554,7 @@
         <v>2</v>
       </c>
       <c r="C867">
-        <v>5160</v>
+        <v>5280</v>
       </c>
       <c r="D867" t="s">
         <v>869</v>
@@ -16568,7 +16568,7 @@
         <v>3</v>
       </c>
       <c r="C868">
-        <v>5150</v>
+        <v>5240</v>
       </c>
       <c r="D868" t="s">
         <v>870</v>
@@ -16582,7 +16582,7 @@
         <v>4</v>
       </c>
       <c r="C869">
-        <v>5140</v>
+        <v>5190</v>
       </c>
       <c r="D869" t="s">
         <v>871</v>
@@ -16596,7 +16596,7 @@
         <v>5</v>
       </c>
       <c r="C870">
-        <v>5120</v>
+        <v>5130</v>
       </c>
       <c r="D870" t="s">
         <v>872</v>
@@ -16610,7 +16610,7 @@
         <v>6</v>
       </c>
       <c r="C871">
-        <v>5110</v>
+        <v>5080</v>
       </c>
       <c r="D871" t="s">
         <v>873</v>
@@ -16624,7 +16624,7 @@
         <v>7</v>
       </c>
       <c r="C872">
-        <v>5100</v>
+        <v>5040</v>
       </c>
       <c r="D872" t="s">
         <v>874</v>
@@ -16638,7 +16638,7 @@
         <v>8</v>
       </c>
       <c r="C873">
-        <v>5080</v>
+        <v>5000</v>
       </c>
       <c r="D873" t="s">
         <v>875</v>
@@ -16652,7 +16652,7 @@
         <v>9</v>
       </c>
       <c r="C874">
-        <v>5070</v>
+        <v>4980</v>
       </c>
       <c r="D874" t="s">
         <v>876</v>
@@ -16666,7 +16666,7 @@
         <v>10</v>
       </c>
       <c r="C875">
-        <v>5060</v>
+        <v>4960</v>
       </c>
       <c r="D875" t="s">
         <v>877</v>
@@ -16680,7 +16680,7 @@
         <v>11</v>
       </c>
       <c r="C876">
-        <v>5060</v>
+        <v>4960</v>
       </c>
       <c r="D876" t="s">
         <v>878</v>
@@ -16694,7 +16694,7 @@
         <v>12</v>
       </c>
       <c r="C877">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="D877" t="s">
         <v>879</v>
@@ -16708,7 +16708,7 @@
         <v>13</v>
       </c>
       <c r="C878">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="D878" t="s">
         <v>880</v>
@@ -16722,7 +16722,7 @@
         <v>14</v>
       </c>
       <c r="C879">
-        <v>5050</v>
+        <v>4960</v>
       </c>
       <c r="D879" t="s">
         <v>881</v>
@@ -16736,7 +16736,7 @@
         <v>15</v>
       </c>
       <c r="C880">
-        <v>5060</v>
+        <v>4960</v>
       </c>
       <c r="D880" t="s">
         <v>882</v>
@@ -16750,7 +16750,7 @@
         <v>16</v>
       </c>
       <c r="C881">
-        <v>5070</v>
+        <v>4970</v>
       </c>
       <c r="D881" t="s">
         <v>883</v>
@@ -16764,7 +16764,7 @@
         <v>17</v>
       </c>
       <c r="C882">
-        <v>5090</v>
+        <v>4980</v>
       </c>
       <c r="D882" t="s">
         <v>884</v>
@@ -16778,7 +16778,7 @@
         <v>18</v>
       </c>
       <c r="C883">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="D883" t="s">
         <v>885</v>
@@ -16792,7 +16792,7 @@
         <v>19</v>
       </c>
       <c r="C884">
-        <v>5120</v>
+        <v>5020</v>
       </c>
       <c r="D884" t="s">
         <v>886</v>
@@ -16806,7 +16806,7 @@
         <v>20</v>
       </c>
       <c r="C885">
-        <v>5130</v>
+        <v>5050</v>
       </c>
       <c r="D885" t="s">
         <v>887</v>
@@ -16820,7 +16820,7 @@
         <v>21</v>
       </c>
       <c r="C886">
-        <v>5140</v>
+        <v>5080</v>
       </c>
       <c r="D886" t="s">
         <v>888</v>
@@ -16834,7 +16834,7 @@
         <v>22</v>
       </c>
       <c r="C887">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="D887" t="s">
         <v>889</v>
@@ -16848,7 +16848,7 @@
         <v>23</v>
       </c>
       <c r="C888">
-        <v>5150</v>
+        <v>5160</v>
       </c>
       <c r="D888" t="s">
         <v>890</v>
@@ -16862,7 +16862,7 @@
         <v>24</v>
       </c>
       <c r="C889">
-        <v>5160</v>
+        <v>5200</v>
       </c>
       <c r="D889" t="s">
         <v>891</v>
@@ -16876,7 +16876,7 @@
         <v>25</v>
       </c>
       <c r="C890">
-        <v>5170</v>
+        <v>5240</v>
       </c>
       <c r="D890" t="s">
         <v>892</v>
@@ -16890,7 +16890,7 @@
         <v>26</v>
       </c>
       <c r="C891">
-        <v>5190</v>
+        <v>5290</v>
       </c>
       <c r="D891" t="s">
         <v>893</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="C892">
-        <v>5220</v>
+        <v>5330</v>
       </c>
       <c r="D892" t="s">
         <v>894</v>
@@ -16918,7 +16918,7 @@
         <v>28</v>
       </c>
       <c r="C893">
-        <v>5250</v>
+        <v>5370</v>
       </c>
       <c r="D893" t="s">
         <v>895</v>
@@ -16932,7 +16932,7 @@
         <v>29</v>
       </c>
       <c r="C894">
-        <v>5280</v>
+        <v>5420</v>
       </c>
       <c r="D894" t="s">
         <v>896</v>
@@ -16946,7 +16946,7 @@
         <v>30</v>
       </c>
       <c r="C895">
-        <v>5310</v>
+        <v>5460</v>
       </c>
       <c r="D895" t="s">
         <v>897</v>
@@ -16960,7 +16960,7 @@
         <v>31</v>
       </c>
       <c r="C896">
-        <v>5330</v>
+        <v>5490</v>
       </c>
       <c r="D896" t="s">
         <v>898</v>
@@ -16974,7 +16974,7 @@
         <v>32</v>
       </c>
       <c r="C897">
-        <v>5350</v>
+        <v>5500</v>
       </c>
       <c r="D897" t="s">
         <v>899</v>
@@ -16988,7 +16988,7 @@
         <v>33</v>
       </c>
       <c r="C898">
-        <v>5350</v>
+        <v>5500</v>
       </c>
       <c r="D898" t="s">
         <v>900</v>
@@ -17002,7 +17002,7 @@
         <v>34</v>
       </c>
       <c r="C899">
-        <v>5320</v>
+        <v>5500</v>
       </c>
       <c r="D899" t="s">
         <v>901</v>
@@ -17016,7 +17016,7 @@
         <v>35</v>
       </c>
       <c r="C900">
-        <v>5280</v>
+        <v>5500</v>
       </c>
       <c r="D900" t="s">
         <v>902</v>
@@ -17030,7 +17030,7 @@
         <v>36</v>
       </c>
       <c r="C901">
-        <v>5210</v>
+        <v>5500</v>
       </c>
       <c r="D901" t="s">
         <v>903</v>
@@ -17044,7 +17044,7 @@
         <v>37</v>
       </c>
       <c r="C902">
-        <v>5110</v>
+        <v>5460</v>
       </c>
       <c r="D902" t="s">
         <v>904</v>
@@ -17058,7 +17058,7 @@
         <v>38</v>
       </c>
       <c r="C903">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="D903" t="s">
         <v>905</v>
@@ -17072,7 +17072,7 @@
         <v>39</v>
       </c>
       <c r="C904">
-        <v>4870</v>
+        <v>5330</v>
       </c>
       <c r="D904" t="s">
         <v>906</v>
@@ -17086,7 +17086,7 @@
         <v>40</v>
       </c>
       <c r="C905">
-        <v>4730</v>
+        <v>5250</v>
       </c>
       <c r="D905" t="s">
         <v>907</v>
@@ -17100,7 +17100,7 @@
         <v>41</v>
       </c>
       <c r="C906">
-        <v>4590</v>
+        <v>5170</v>
       </c>
       <c r="D906" t="s">
         <v>908</v>
@@ -17114,7 +17114,7 @@
         <v>42</v>
       </c>
       <c r="C907">
-        <v>4460</v>
+        <v>5080</v>
       </c>
       <c r="D907" t="s">
         <v>909</v>
@@ -17128,7 +17128,7 @@
         <v>43</v>
       </c>
       <c r="C908">
-        <v>4330</v>
+        <v>5000</v>
       </c>
       <c r="D908" t="s">
         <v>910</v>
@@ -17142,7 +17142,7 @@
         <v>44</v>
       </c>
       <c r="C909">
-        <v>4220</v>
+        <v>4920</v>
       </c>
       <c r="D909" t="s">
         <v>911</v>
@@ -17156,7 +17156,7 @@
         <v>45</v>
       </c>
       <c r="C910">
-        <v>4120</v>
+        <v>4860</v>
       </c>
       <c r="D910" t="s">
         <v>912</v>
@@ -17170,7 +17170,7 @@
         <v>46</v>
       </c>
       <c r="C911">
-        <v>4050</v>
+        <v>4800</v>
       </c>
       <c r="D911" t="s">
         <v>913</v>
@@ -17184,7 +17184,7 @@
         <v>47</v>
       </c>
       <c r="C912">
-        <v>3980</v>
+        <v>4740</v>
       </c>
       <c r="D912" t="s">
         <v>914</v>
@@ -17198,7 +17198,7 @@
         <v>48</v>
       </c>
       <c r="C913">
-        <v>3940</v>
+        <v>4700</v>
       </c>
       <c r="D913" t="s">
         <v>915</v>
@@ -17212,7 +17212,7 @@
         <v>49</v>
       </c>
       <c r="C914">
-        <v>3910</v>
+        <v>4660</v>
       </c>
       <c r="D914" t="s">
         <v>916</v>
@@ -17226,7 +17226,7 @@
         <v>50</v>
       </c>
       <c r="C915">
-        <v>3890</v>
+        <v>4630</v>
       </c>
       <c r="D915" t="s">
         <v>917</v>
@@ -17240,7 +17240,7 @@
         <v>51</v>
       </c>
       <c r="C916">
-        <v>3870</v>
+        <v>4600</v>
       </c>
       <c r="D916" t="s">
         <v>918</v>
@@ -17254,7 +17254,7 @@
         <v>52</v>
       </c>
       <c r="C917">
-        <v>3870</v>
+        <v>4570</v>
       </c>
       <c r="D917" t="s">
         <v>919</v>
@@ -17268,7 +17268,7 @@
         <v>53</v>
       </c>
       <c r="C918">
-        <v>3870</v>
+        <v>4560</v>
       </c>
       <c r="D918" t="s">
         <v>920</v>
@@ -17282,7 +17282,7 @@
         <v>54</v>
       </c>
       <c r="C919">
-        <v>3880</v>
+        <v>4550</v>
       </c>
       <c r="D919" t="s">
         <v>921</v>
@@ -17296,7 +17296,7 @@
         <v>55</v>
       </c>
       <c r="C920">
-        <v>3900</v>
+        <v>4560</v>
       </c>
       <c r="D920" t="s">
         <v>922</v>
@@ -17310,7 +17310,7 @@
         <v>56</v>
       </c>
       <c r="C921">
-        <v>3920</v>
+        <v>4580</v>
       </c>
       <c r="D921" t="s">
         <v>923</v>
@@ -17324,7 +17324,7 @@
         <v>57</v>
       </c>
       <c r="C922">
-        <v>3960</v>
+        <v>4600</v>
       </c>
       <c r="D922" t="s">
         <v>924</v>
@@ -17338,7 +17338,7 @@
         <v>58</v>
       </c>
       <c r="C923">
-        <v>3990</v>
+        <v>4640</v>
       </c>
       <c r="D923" t="s">
         <v>925</v>
@@ -17352,7 +17352,7 @@
         <v>59</v>
       </c>
       <c r="C924">
-        <v>4040</v>
+        <v>4680</v>
       </c>
       <c r="D924" t="s">
         <v>926</v>
@@ -17366,7 +17366,7 @@
         <v>60</v>
       </c>
       <c r="C925">
-        <v>4090</v>
+        <v>4730</v>
       </c>
       <c r="D925" t="s">
         <v>927</v>
@@ -17380,7 +17380,7 @@
         <v>61</v>
       </c>
       <c r="C926">
-        <v>4160</v>
+        <v>4780</v>
       </c>
       <c r="D926" t="s">
         <v>928</v>
@@ -17394,7 +17394,7 @@
         <v>62</v>
       </c>
       <c r="C927">
-        <v>4230</v>
+        <v>4830</v>
       </c>
       <c r="D927" t="s">
         <v>929</v>
@@ -17408,7 +17408,7 @@
         <v>63</v>
       </c>
       <c r="C928">
-        <v>4310</v>
+        <v>4890</v>
       </c>
       <c r="D928" t="s">
         <v>930</v>
@@ -17422,7 +17422,7 @@
         <v>64</v>
       </c>
       <c r="C929">
-        <v>4410</v>
+        <v>4950</v>
       </c>
       <c r="D929" t="s">
         <v>931</v>
@@ -17436,7 +17436,7 @@
         <v>65</v>
       </c>
       <c r="C930">
-        <v>4510</v>
+        <v>5020</v>
       </c>
       <c r="D930" t="s">
         <v>932</v>
@@ -17450,7 +17450,7 @@
         <v>66</v>
       </c>
       <c r="C931">
-        <v>4630</v>
+        <v>5110</v>
       </c>
       <c r="D931" t="s">
         <v>933</v>
@@ -17464,7 +17464,7 @@
         <v>67</v>
       </c>
       <c r="C932">
-        <v>4760</v>
+        <v>5200</v>
       </c>
       <c r="D932" t="s">
         <v>934</v>
@@ -17478,7 +17478,7 @@
         <v>68</v>
       </c>
       <c r="C933">
-        <v>4900</v>
+        <v>5310</v>
       </c>
       <c r="D933" t="s">
         <v>935</v>
@@ -17492,7 +17492,7 @@
         <v>69</v>
       </c>
       <c r="C934">
-        <v>5050</v>
+        <v>5430</v>
       </c>
       <c r="D934" t="s">
         <v>936</v>
@@ -17506,7 +17506,7 @@
         <v>70</v>
       </c>
       <c r="C935">
-        <v>5200</v>
+        <v>5560</v>
       </c>
       <c r="D935" t="s">
         <v>937</v>
@@ -17520,7 +17520,7 @@
         <v>71</v>
       </c>
       <c r="C936">
-        <v>5340</v>
+        <v>5680</v>
       </c>
       <c r="D936" t="s">
         <v>938</v>
@@ -17534,7 +17534,7 @@
         <v>72</v>
       </c>
       <c r="C937">
-        <v>5490</v>
+        <v>5800</v>
       </c>
       <c r="D937" t="s">
         <v>939</v>
@@ -17548,7 +17548,7 @@
         <v>73</v>
       </c>
       <c r="C938">
-        <v>5630</v>
+        <v>5930</v>
       </c>
       <c r="D938" t="s">
         <v>940</v>
@@ -17562,7 +17562,7 @@
         <v>74</v>
       </c>
       <c r="C939">
-        <v>5770</v>
+        <v>6050</v>
       </c>
       <c r="D939" t="s">
         <v>941</v>
@@ -17576,7 +17576,7 @@
         <v>75</v>
       </c>
       <c r="C940">
-        <v>5910</v>
+        <v>6170</v>
       </c>
       <c r="D940" t="s">
         <v>942</v>
@@ -17590,7 +17590,7 @@
         <v>76</v>
       </c>
       <c r="C941">
-        <v>6050</v>
+        <v>6300</v>
       </c>
       <c r="D941" t="s">
         <v>943</v>
@@ -17604,7 +17604,7 @@
         <v>77</v>
       </c>
       <c r="C942">
-        <v>6180</v>
+        <v>6410</v>
       </c>
       <c r="D942" t="s">
         <v>944</v>
@@ -17618,7 +17618,7 @@
         <v>78</v>
       </c>
       <c r="C943">
-        <v>6300</v>
+        <v>6510</v>
       </c>
       <c r="D943" t="s">
         <v>945</v>
@@ -17632,7 +17632,7 @@
         <v>79</v>
       </c>
       <c r="C944">
-        <v>6400</v>
+        <v>6550</v>
       </c>
       <c r="D944" t="s">
         <v>946</v>
@@ -17646,7 +17646,7 @@
         <v>80</v>
       </c>
       <c r="C945">
-        <v>6470</v>
+        <v>6550</v>
       </c>
       <c r="D945" t="s">
         <v>947</v>
@@ -17660,7 +17660,7 @@
         <v>81</v>
       </c>
       <c r="C946">
-        <v>6520</v>
+        <v>6550</v>
       </c>
       <c r="D946" t="s">
         <v>948</v>
@@ -17674,7 +17674,7 @@
         <v>82</v>
       </c>
       <c r="C947">
-        <v>6530</v>
+        <v>6550</v>
       </c>
       <c r="D947" t="s">
         <v>949</v>
@@ -17688,7 +17688,7 @@
         <v>83</v>
       </c>
       <c r="C948">
-        <v>6490</v>
+        <v>6540</v>
       </c>
       <c r="D948" t="s">
         <v>950</v>
@@ -17702,7 +17702,7 @@
         <v>84</v>
       </c>
       <c r="C949">
-        <v>6410</v>
+        <v>6490</v>
       </c>
       <c r="D949" t="s">
         <v>951</v>
@@ -17716,7 +17716,7 @@
         <v>85</v>
       </c>
       <c r="C950">
-        <v>6260</v>
+        <v>6400</v>
       </c>
       <c r="D950" t="s">
         <v>952</v>
@@ -17730,7 +17730,7 @@
         <v>86</v>
       </c>
       <c r="C951">
-        <v>6090</v>
+        <v>6280</v>
       </c>
       <c r="D951" t="s">
         <v>953</v>
@@ -17744,7 +17744,7 @@
         <v>87</v>
       </c>
       <c r="C952">
-        <v>6000</v>
+        <v>6220</v>
       </c>
       <c r="D952" t="s">
         <v>954</v>
@@ -17758,7 +17758,7 @@
         <v>88</v>
       </c>
       <c r="C953">
-        <v>5910</v>
+        <v>6140</v>
       </c>
       <c r="D953" t="s">
         <v>955</v>
@@ -17772,7 +17772,7 @@
         <v>89</v>
       </c>
       <c r="C954">
-        <v>5790</v>
+        <v>6010</v>
       </c>
       <c r="D954" t="s">
         <v>956</v>
@@ -17786,7 +17786,7 @@
         <v>90</v>
       </c>
       <c r="C955">
-        <v>5690</v>
+        <v>5920</v>
       </c>
       <c r="D955" t="s">
         <v>957</v>
@@ -17800,7 +17800,7 @@
         <v>91</v>
       </c>
       <c r="C956">
-        <v>5510</v>
+        <v>5780</v>
       </c>
       <c r="D956" t="s">
         <v>958</v>
@@ -17814,7 +17814,7 @@
         <v>92</v>
       </c>
       <c r="C957">
-        <v>5400</v>
+        <v>5650</v>
       </c>
       <c r="D957" t="s">
         <v>959</v>
@@ -17828,7 +17828,7 @@
         <v>93</v>
       </c>
       <c r="C958">
-        <v>5320</v>
+        <v>5510</v>
       </c>
       <c r="D958" t="s">
         <v>960</v>
@@ -17842,7 +17842,7 @@
         <v>94</v>
       </c>
       <c r="C959">
-        <v>5170</v>
+        <v>5380</v>
       </c>
       <c r="D959" t="s">
         <v>961</v>
@@ -17856,7 +17856,7 @@
         <v>95</v>
       </c>
       <c r="C960">
-        <v>5150</v>
+        <v>5270</v>
       </c>
       <c r="D960" t="s">
         <v>962</v>
@@ -17870,7 +17870,7 @@
         <v>96</v>
       </c>
       <c r="C961">
-        <v>5120</v>
+        <v>5170</v>
       </c>
       <c r="D961" t="s">
         <v>963</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1540">
   <si>
     <t>Date</t>
   </si>
@@ -4058,6 +4058,582 @@
   </si>
   <si>
     <t>14.10.202696.0</t>
+  </si>
+  <si>
+    <t>15.10.20261.0</t>
+  </si>
+  <si>
+    <t>15.10.20262.0</t>
+  </si>
+  <si>
+    <t>15.10.20263.0</t>
+  </si>
+  <si>
+    <t>15.10.20264.0</t>
+  </si>
+  <si>
+    <t>15.10.20265.0</t>
+  </si>
+  <si>
+    <t>15.10.20266.0</t>
+  </si>
+  <si>
+    <t>15.10.20267.0</t>
+  </si>
+  <si>
+    <t>15.10.20268.0</t>
+  </si>
+  <si>
+    <t>15.10.20269.0</t>
+  </si>
+  <si>
+    <t>15.10.202610.0</t>
+  </si>
+  <si>
+    <t>15.10.202611.0</t>
+  </si>
+  <si>
+    <t>15.10.202612.0</t>
+  </si>
+  <si>
+    <t>15.10.202613.0</t>
+  </si>
+  <si>
+    <t>15.10.202614.0</t>
+  </si>
+  <si>
+    <t>15.10.202615.0</t>
+  </si>
+  <si>
+    <t>15.10.202616.0</t>
+  </si>
+  <si>
+    <t>15.10.202617.0</t>
+  </si>
+  <si>
+    <t>15.10.202618.0</t>
+  </si>
+  <si>
+    <t>15.10.202619.0</t>
+  </si>
+  <si>
+    <t>15.10.202620.0</t>
+  </si>
+  <si>
+    <t>15.10.202621.0</t>
+  </si>
+  <si>
+    <t>15.10.202622.0</t>
+  </si>
+  <si>
+    <t>15.10.202623.0</t>
+  </si>
+  <si>
+    <t>15.10.202624.0</t>
+  </si>
+  <si>
+    <t>15.10.202625.0</t>
+  </si>
+  <si>
+    <t>15.10.202626.0</t>
+  </si>
+  <si>
+    <t>15.10.202627.0</t>
+  </si>
+  <si>
+    <t>15.10.202628.0</t>
+  </si>
+  <si>
+    <t>15.10.202629.0</t>
+  </si>
+  <si>
+    <t>15.10.202630.0</t>
+  </si>
+  <si>
+    <t>15.10.202631.0</t>
+  </si>
+  <si>
+    <t>15.10.202632.0</t>
+  </si>
+  <si>
+    <t>15.10.202633.0</t>
+  </si>
+  <si>
+    <t>15.10.202634.0</t>
+  </si>
+  <si>
+    <t>15.10.202635.0</t>
+  </si>
+  <si>
+    <t>15.10.202636.0</t>
+  </si>
+  <si>
+    <t>15.10.202637.0</t>
+  </si>
+  <si>
+    <t>15.10.202638.0</t>
+  </si>
+  <si>
+    <t>15.10.202639.0</t>
+  </si>
+  <si>
+    <t>15.10.202640.0</t>
+  </si>
+  <si>
+    <t>15.10.202641.0</t>
+  </si>
+  <si>
+    <t>15.10.202642.0</t>
+  </si>
+  <si>
+    <t>15.10.202643.0</t>
+  </si>
+  <si>
+    <t>15.10.202644.0</t>
+  </si>
+  <si>
+    <t>15.10.202645.0</t>
+  </si>
+  <si>
+    <t>15.10.202646.0</t>
+  </si>
+  <si>
+    <t>15.10.202647.0</t>
+  </si>
+  <si>
+    <t>15.10.202648.0</t>
+  </si>
+  <si>
+    <t>15.10.202649.0</t>
+  </si>
+  <si>
+    <t>15.10.202650.0</t>
+  </si>
+  <si>
+    <t>15.10.202651.0</t>
+  </si>
+  <si>
+    <t>15.10.202652.0</t>
+  </si>
+  <si>
+    <t>15.10.202653.0</t>
+  </si>
+  <si>
+    <t>15.10.202654.0</t>
+  </si>
+  <si>
+    <t>15.10.202655.0</t>
+  </si>
+  <si>
+    <t>15.10.202656.0</t>
+  </si>
+  <si>
+    <t>15.10.202657.0</t>
+  </si>
+  <si>
+    <t>15.10.202658.0</t>
+  </si>
+  <si>
+    <t>15.10.202659.0</t>
+  </si>
+  <si>
+    <t>15.10.202660.0</t>
+  </si>
+  <si>
+    <t>15.10.202661.0</t>
+  </si>
+  <si>
+    <t>15.10.202662.0</t>
+  </si>
+  <si>
+    <t>15.10.202663.0</t>
+  </si>
+  <si>
+    <t>15.10.202664.0</t>
+  </si>
+  <si>
+    <t>15.10.202665.0</t>
+  </si>
+  <si>
+    <t>15.10.202666.0</t>
+  </si>
+  <si>
+    <t>15.10.202667.0</t>
+  </si>
+  <si>
+    <t>15.10.202668.0</t>
+  </si>
+  <si>
+    <t>15.10.202669.0</t>
+  </si>
+  <si>
+    <t>15.10.202670.0</t>
+  </si>
+  <si>
+    <t>15.10.202671.0</t>
+  </si>
+  <si>
+    <t>15.10.202672.0</t>
+  </si>
+  <si>
+    <t>15.10.202673.0</t>
+  </si>
+  <si>
+    <t>15.10.202674.0</t>
+  </si>
+  <si>
+    <t>15.10.202675.0</t>
+  </si>
+  <si>
+    <t>15.10.202676.0</t>
+  </si>
+  <si>
+    <t>15.10.202677.0</t>
+  </si>
+  <si>
+    <t>15.10.202678.0</t>
+  </si>
+  <si>
+    <t>15.10.202679.0</t>
+  </si>
+  <si>
+    <t>15.10.202680.0</t>
+  </si>
+  <si>
+    <t>15.10.202681.0</t>
+  </si>
+  <si>
+    <t>15.10.202682.0</t>
+  </si>
+  <si>
+    <t>15.10.202683.0</t>
+  </si>
+  <si>
+    <t>15.10.202684.0</t>
+  </si>
+  <si>
+    <t>15.10.202685.0</t>
+  </si>
+  <si>
+    <t>15.10.202686.0</t>
+  </si>
+  <si>
+    <t>15.10.202687.0</t>
+  </si>
+  <si>
+    <t>15.10.202688.0</t>
+  </si>
+  <si>
+    <t>15.10.202689.0</t>
+  </si>
+  <si>
+    <t>15.10.202690.0</t>
+  </si>
+  <si>
+    <t>15.10.202691.0</t>
+  </si>
+  <si>
+    <t>15.10.202692.0</t>
+  </si>
+  <si>
+    <t>15.10.202693.0</t>
+  </si>
+  <si>
+    <t>15.10.202694.0</t>
+  </si>
+  <si>
+    <t>15.10.202695.0</t>
+  </si>
+  <si>
+    <t>15.10.202696.0</t>
+  </si>
+  <si>
+    <t>16.10.20261.0</t>
+  </si>
+  <si>
+    <t>16.10.20262.0</t>
+  </si>
+  <si>
+    <t>16.10.20263.0</t>
+  </si>
+  <si>
+    <t>16.10.20264.0</t>
+  </si>
+  <si>
+    <t>16.10.20265.0</t>
+  </si>
+  <si>
+    <t>16.10.20266.0</t>
+  </si>
+  <si>
+    <t>16.10.20267.0</t>
+  </si>
+  <si>
+    <t>16.10.20268.0</t>
+  </si>
+  <si>
+    <t>16.10.20269.0</t>
+  </si>
+  <si>
+    <t>16.10.202610.0</t>
+  </si>
+  <si>
+    <t>16.10.202611.0</t>
+  </si>
+  <si>
+    <t>16.10.202612.0</t>
+  </si>
+  <si>
+    <t>16.10.202613.0</t>
+  </si>
+  <si>
+    <t>16.10.202614.0</t>
+  </si>
+  <si>
+    <t>16.10.202615.0</t>
+  </si>
+  <si>
+    <t>16.10.202616.0</t>
+  </si>
+  <si>
+    <t>16.10.202617.0</t>
+  </si>
+  <si>
+    <t>16.10.202618.0</t>
+  </si>
+  <si>
+    <t>16.10.202619.0</t>
+  </si>
+  <si>
+    <t>16.10.202620.0</t>
+  </si>
+  <si>
+    <t>16.10.202621.0</t>
+  </si>
+  <si>
+    <t>16.10.202622.0</t>
+  </si>
+  <si>
+    <t>16.10.202623.0</t>
+  </si>
+  <si>
+    <t>16.10.202624.0</t>
+  </si>
+  <si>
+    <t>16.10.202625.0</t>
+  </si>
+  <si>
+    <t>16.10.202626.0</t>
+  </si>
+  <si>
+    <t>16.10.202627.0</t>
+  </si>
+  <si>
+    <t>16.10.202628.0</t>
+  </si>
+  <si>
+    <t>16.10.202629.0</t>
+  </si>
+  <si>
+    <t>16.10.202630.0</t>
+  </si>
+  <si>
+    <t>16.10.202631.0</t>
+  </si>
+  <si>
+    <t>16.10.202632.0</t>
+  </si>
+  <si>
+    <t>16.10.202633.0</t>
+  </si>
+  <si>
+    <t>16.10.202634.0</t>
+  </si>
+  <si>
+    <t>16.10.202635.0</t>
+  </si>
+  <si>
+    <t>16.10.202636.0</t>
+  </si>
+  <si>
+    <t>16.10.202637.0</t>
+  </si>
+  <si>
+    <t>16.10.202638.0</t>
+  </si>
+  <si>
+    <t>16.10.202639.0</t>
+  </si>
+  <si>
+    <t>16.10.202640.0</t>
+  </si>
+  <si>
+    <t>16.10.202641.0</t>
+  </si>
+  <si>
+    <t>16.10.202642.0</t>
+  </si>
+  <si>
+    <t>16.10.202643.0</t>
+  </si>
+  <si>
+    <t>16.10.202644.0</t>
+  </si>
+  <si>
+    <t>16.10.202645.0</t>
+  </si>
+  <si>
+    <t>16.10.202646.0</t>
+  </si>
+  <si>
+    <t>16.10.202647.0</t>
+  </si>
+  <si>
+    <t>16.10.202648.0</t>
+  </si>
+  <si>
+    <t>16.10.202649.0</t>
+  </si>
+  <si>
+    <t>16.10.202650.0</t>
+  </si>
+  <si>
+    <t>16.10.202651.0</t>
+  </si>
+  <si>
+    <t>16.10.202652.0</t>
+  </si>
+  <si>
+    <t>16.10.202653.0</t>
+  </si>
+  <si>
+    <t>16.10.202654.0</t>
+  </si>
+  <si>
+    <t>16.10.202655.0</t>
+  </si>
+  <si>
+    <t>16.10.202656.0</t>
+  </si>
+  <si>
+    <t>16.10.202657.0</t>
+  </si>
+  <si>
+    <t>16.10.202658.0</t>
+  </si>
+  <si>
+    <t>16.10.202659.0</t>
+  </si>
+  <si>
+    <t>16.10.202660.0</t>
+  </si>
+  <si>
+    <t>16.10.202661.0</t>
+  </si>
+  <si>
+    <t>16.10.202662.0</t>
+  </si>
+  <si>
+    <t>16.10.202663.0</t>
+  </si>
+  <si>
+    <t>16.10.202664.0</t>
+  </si>
+  <si>
+    <t>16.10.202665.0</t>
+  </si>
+  <si>
+    <t>16.10.202666.0</t>
+  </si>
+  <si>
+    <t>16.10.202667.0</t>
+  </si>
+  <si>
+    <t>16.10.202668.0</t>
+  </si>
+  <si>
+    <t>16.10.202669.0</t>
+  </si>
+  <si>
+    <t>16.10.202670.0</t>
+  </si>
+  <si>
+    <t>16.10.202671.0</t>
+  </si>
+  <si>
+    <t>16.10.202672.0</t>
+  </si>
+  <si>
+    <t>16.10.202673.0</t>
+  </si>
+  <si>
+    <t>16.10.202674.0</t>
+  </si>
+  <si>
+    <t>16.10.202675.0</t>
+  </si>
+  <si>
+    <t>16.10.202676.0</t>
+  </si>
+  <si>
+    <t>16.10.202677.0</t>
+  </si>
+  <si>
+    <t>16.10.202678.0</t>
+  </si>
+  <si>
+    <t>16.10.202679.0</t>
+  </si>
+  <si>
+    <t>16.10.202680.0</t>
+  </si>
+  <si>
+    <t>16.10.202681.0</t>
+  </si>
+  <si>
+    <t>16.10.202682.0</t>
+  </si>
+  <si>
+    <t>16.10.202683.0</t>
+  </si>
+  <si>
+    <t>16.10.202684.0</t>
+  </si>
+  <si>
+    <t>16.10.202685.0</t>
+  </si>
+  <si>
+    <t>16.10.202686.0</t>
+  </si>
+  <si>
+    <t>16.10.202687.0</t>
+  </si>
+  <si>
+    <t>16.10.202688.0</t>
+  </si>
+  <si>
+    <t>16.10.202689.0</t>
+  </si>
+  <si>
+    <t>16.10.202690.0</t>
+  </si>
+  <si>
+    <t>16.10.202691.0</t>
+  </si>
+  <si>
+    <t>16.10.202692.0</t>
+  </si>
+  <si>
+    <t>16.10.202693.0</t>
+  </si>
+  <si>
+    <t>16.10.202694.0</t>
+  </si>
+  <si>
+    <t>16.10.202695.0</t>
+  </si>
+  <si>
+    <t>16.10.202696.0</t>
   </si>
 </sst>
 </file>
@@ -4419,7 +4995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1345"/>
+  <dimension ref="A1:D1537"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -15196,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="C770">
-        <v>5350</v>
+        <v>5260</v>
       </c>
       <c r="D770" t="s">
         <v>772</v>
@@ -15210,7 +15786,7 @@
         <v>2</v>
       </c>
       <c r="C771">
-        <v>5300</v>
+        <v>5190</v>
       </c>
       <c r="D771" t="s">
         <v>773</v>
@@ -15224,7 +15800,7 @@
         <v>3</v>
       </c>
       <c r="C772">
-        <v>5240</v>
+        <v>5150</v>
       </c>
       <c r="D772" t="s">
         <v>774</v>
@@ -15238,7 +15814,7 @@
         <v>4</v>
       </c>
       <c r="C773">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="D773" t="s">
         <v>775</v>
@@ -15252,7 +15828,7 @@
         <v>5</v>
       </c>
       <c r="C774">
-        <v>5100</v>
+        <v>5090</v>
       </c>
       <c r="D774" t="s">
         <v>776</v>
@@ -15294,7 +15870,7 @@
         <v>8</v>
       </c>
       <c r="C777">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="D777" t="s">
         <v>779</v>
@@ -15308,7 +15884,7 @@
         <v>9</v>
       </c>
       <c r="C778">
-        <v>5050</v>
+        <v>4980</v>
       </c>
       <c r="D778" t="s">
         <v>780</v>
@@ -15322,7 +15898,7 @@
         <v>10</v>
       </c>
       <c r="C779">
-        <v>5050</v>
+        <v>4980</v>
       </c>
       <c r="D779" t="s">
         <v>781</v>
@@ -15336,7 +15912,7 @@
         <v>11</v>
       </c>
       <c r="C780">
-        <v>5050</v>
+        <v>4980</v>
       </c>
       <c r="D780" t="s">
         <v>782</v>
@@ -15350,7 +15926,7 @@
         <v>12</v>
       </c>
       <c r="C781">
-        <v>5080</v>
+        <v>4980</v>
       </c>
       <c r="D781" t="s">
         <v>783</v>
@@ -15364,7 +15940,7 @@
         <v>13</v>
       </c>
       <c r="C782">
-        <v>5110</v>
+        <v>5030</v>
       </c>
       <c r="D782" t="s">
         <v>784</v>
@@ -15378,7 +15954,7 @@
         <v>14</v>
       </c>
       <c r="C783">
-        <v>5130</v>
+        <v>5050</v>
       </c>
       <c r="D783" t="s">
         <v>785</v>
@@ -15392,7 +15968,7 @@
         <v>15</v>
       </c>
       <c r="C784">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="D784" t="s">
         <v>786</v>
@@ -15406,7 +15982,7 @@
         <v>16</v>
       </c>
       <c r="C785">
-        <v>5160</v>
+        <v>5050</v>
       </c>
       <c r="D785" t="s">
         <v>787</v>
@@ -15420,7 +15996,7 @@
         <v>17</v>
       </c>
       <c r="C786">
-        <v>5160</v>
+        <v>5020</v>
       </c>
       <c r="D786" t="s">
         <v>788</v>
@@ -15434,7 +16010,7 @@
         <v>18</v>
       </c>
       <c r="C787">
-        <v>5160</v>
+        <v>5000</v>
       </c>
       <c r="D787" t="s">
         <v>789</v>
@@ -15448,7 +16024,7 @@
         <v>19</v>
       </c>
       <c r="C788">
-        <v>5170</v>
+        <v>5000</v>
       </c>
       <c r="D788" t="s">
         <v>790</v>
@@ -15462,7 +16038,7 @@
         <v>20</v>
       </c>
       <c r="C789">
-        <v>5180</v>
+        <v>5010</v>
       </c>
       <c r="D789" t="s">
         <v>791</v>
@@ -15476,7 +16052,7 @@
         <v>21</v>
       </c>
       <c r="C790">
-        <v>5200</v>
+        <v>5080</v>
       </c>
       <c r="D790" t="s">
         <v>792</v>
@@ -15490,7 +16066,7 @@
         <v>22</v>
       </c>
       <c r="C791">
-        <v>5250</v>
+        <v>5140</v>
       </c>
       <c r="D791" t="s">
         <v>793</v>
@@ -15504,7 +16080,7 @@
         <v>23</v>
       </c>
       <c r="C792">
-        <v>5330</v>
+        <v>5230</v>
       </c>
       <c r="D792" t="s">
         <v>794</v>
@@ -15518,7 +16094,7 @@
         <v>24</v>
       </c>
       <c r="C793">
-        <v>5420</v>
+        <v>5350</v>
       </c>
       <c r="D793" t="s">
         <v>795</v>
@@ -15532,7 +16108,7 @@
         <v>25</v>
       </c>
       <c r="C794">
-        <v>5540</v>
+        <v>5470</v>
       </c>
       <c r="D794" t="s">
         <v>796</v>
@@ -15546,7 +16122,7 @@
         <v>26</v>
       </c>
       <c r="C795">
-        <v>5670</v>
+        <v>5610</v>
       </c>
       <c r="D795" t="s">
         <v>797</v>
@@ -15560,7 +16136,7 @@
         <v>27</v>
       </c>
       <c r="C796">
-        <v>5800</v>
+        <v>5750</v>
       </c>
       <c r="D796" t="s">
         <v>798</v>
@@ -15574,7 +16150,7 @@
         <v>28</v>
       </c>
       <c r="C797">
-        <v>5940</v>
+        <v>5920</v>
       </c>
       <c r="D797" t="s">
         <v>799</v>
@@ -15588,7 +16164,7 @@
         <v>29</v>
       </c>
       <c r="C798">
-        <v>6080</v>
+        <v>6150</v>
       </c>
       <c r="D798" t="s">
         <v>800</v>
@@ -15602,7 +16178,7 @@
         <v>30</v>
       </c>
       <c r="C799">
-        <v>6200</v>
+        <v>6310</v>
       </c>
       <c r="D799" t="s">
         <v>801</v>
@@ -15616,7 +16192,7 @@
         <v>31</v>
       </c>
       <c r="C800">
-        <v>6300</v>
+        <v>6390</v>
       </c>
       <c r="D800" t="s">
         <v>802</v>
@@ -15630,7 +16206,7 @@
         <v>32</v>
       </c>
       <c r="C801">
-        <v>6380</v>
+        <v>6460</v>
       </c>
       <c r="D801" t="s">
         <v>803</v>
@@ -15644,7 +16220,7 @@
         <v>33</v>
       </c>
       <c r="C802">
-        <v>6440</v>
+        <v>6500</v>
       </c>
       <c r="D802" t="s">
         <v>804</v>
@@ -15658,7 +16234,7 @@
         <v>34</v>
       </c>
       <c r="C803">
-        <v>6480</v>
+        <v>6520</v>
       </c>
       <c r="D803" t="s">
         <v>805</v>
@@ -15672,7 +16248,7 @@
         <v>35</v>
       </c>
       <c r="C804">
-        <v>6500</v>
+        <v>6510</v>
       </c>
       <c r="D804" t="s">
         <v>806</v>
@@ -15686,7 +16262,7 @@
         <v>36</v>
       </c>
       <c r="C805">
-        <v>6500</v>
+        <v>6470</v>
       </c>
       <c r="D805" t="s">
         <v>807</v>
@@ -15700,7 +16276,7 @@
         <v>37</v>
       </c>
       <c r="C806">
-        <v>6460</v>
+        <v>6370</v>
       </c>
       <c r="D806" t="s">
         <v>808</v>
@@ -15714,7 +16290,7 @@
         <v>38</v>
       </c>
       <c r="C807">
-        <v>6400</v>
+        <v>6250</v>
       </c>
       <c r="D807" t="s">
         <v>809</v>
@@ -15728,7 +16304,7 @@
         <v>39</v>
       </c>
       <c r="C808">
-        <v>6330</v>
+        <v>6120</v>
       </c>
       <c r="D808" t="s">
         <v>810</v>
@@ -15742,7 +16318,7 @@
         <v>40</v>
       </c>
       <c r="C809">
-        <v>6240</v>
+        <v>5980</v>
       </c>
       <c r="D809" t="s">
         <v>811</v>
@@ -15756,7 +16332,7 @@
         <v>41</v>
       </c>
       <c r="C810">
-        <v>6120</v>
+        <v>5850</v>
       </c>
       <c r="D810" t="s">
         <v>812</v>
@@ -15770,7 +16346,7 @@
         <v>42</v>
       </c>
       <c r="C811">
-        <v>6010</v>
+        <v>5700</v>
       </c>
       <c r="D811" t="s">
         <v>813</v>
@@ -15784,7 +16360,7 @@
         <v>43</v>
       </c>
       <c r="C812">
-        <v>5900</v>
+        <v>5550</v>
       </c>
       <c r="D812" t="s">
         <v>814</v>
@@ -15798,7 +16374,7 @@
         <v>44</v>
       </c>
       <c r="C813">
-        <v>5790</v>
+        <v>5410</v>
       </c>
       <c r="D813" t="s">
         <v>815</v>
@@ -15812,7 +16388,7 @@
         <v>45</v>
       </c>
       <c r="C814">
-        <v>5680</v>
+        <v>5250</v>
       </c>
       <c r="D814" t="s">
         <v>816</v>
@@ -15826,7 +16402,7 @@
         <v>46</v>
       </c>
       <c r="C815">
-        <v>5570</v>
+        <v>5140</v>
       </c>
       <c r="D815" t="s">
         <v>817</v>
@@ -15840,7 +16416,7 @@
         <v>47</v>
       </c>
       <c r="C816">
-        <v>5470</v>
+        <v>5050</v>
       </c>
       <c r="D816" t="s">
         <v>818</v>
@@ -15854,7 +16430,7 @@
         <v>48</v>
       </c>
       <c r="C817">
-        <v>5380</v>
+        <v>4980</v>
       </c>
       <c r="D817" t="s">
         <v>819</v>
@@ -15868,7 +16444,7 @@
         <v>49</v>
       </c>
       <c r="C818">
-        <v>5300</v>
+        <v>4930</v>
       </c>
       <c r="D818" t="s">
         <v>820</v>
@@ -15882,7 +16458,7 @@
         <v>50</v>
       </c>
       <c r="C819">
-        <v>5230</v>
+        <v>4920</v>
       </c>
       <c r="D819" t="s">
         <v>821</v>
@@ -15896,7 +16472,7 @@
         <v>51</v>
       </c>
       <c r="C820">
-        <v>5170</v>
+        <v>4920</v>
       </c>
       <c r="D820" t="s">
         <v>822</v>
@@ -15910,7 +16486,7 @@
         <v>52</v>
       </c>
       <c r="C821">
-        <v>5130</v>
+        <v>4920</v>
       </c>
       <c r="D821" t="s">
         <v>823</v>
@@ -15924,7 +16500,7 @@
         <v>53</v>
       </c>
       <c r="C822">
-        <v>5100</v>
+        <v>4980</v>
       </c>
       <c r="D822" t="s">
         <v>824</v>
@@ -15938,7 +16514,7 @@
         <v>54</v>
       </c>
       <c r="C823">
-        <v>5090</v>
+        <v>5000</v>
       </c>
       <c r="D823" t="s">
         <v>825</v>
@@ -15952,7 +16528,7 @@
         <v>55</v>
       </c>
       <c r="C824">
-        <v>5090</v>
+        <v>5010</v>
       </c>
       <c r="D824" t="s">
         <v>826</v>
@@ -15966,7 +16542,7 @@
         <v>56</v>
       </c>
       <c r="C825">
-        <v>5110</v>
+        <v>5020</v>
       </c>
       <c r="D825" t="s">
         <v>827</v>
@@ -15980,7 +16556,7 @@
         <v>57</v>
       </c>
       <c r="C826">
-        <v>5130</v>
+        <v>5020</v>
       </c>
       <c r="D826" t="s">
         <v>828</v>
@@ -15994,7 +16570,7 @@
         <v>58</v>
       </c>
       <c r="C827">
-        <v>5160</v>
+        <v>5020</v>
       </c>
       <c r="D827" t="s">
         <v>829</v>
@@ -16008,7 +16584,7 @@
         <v>59</v>
       </c>
       <c r="C828">
-        <v>5200</v>
+        <v>5020</v>
       </c>
       <c r="D828" t="s">
         <v>830</v>
@@ -16022,7 +16598,7 @@
         <v>60</v>
       </c>
       <c r="C829">
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="D829" t="s">
         <v>831</v>
@@ -16036,7 +16612,7 @@
         <v>61</v>
       </c>
       <c r="C830">
-        <v>5290</v>
+        <v>5070</v>
       </c>
       <c r="D830" t="s">
         <v>832</v>
@@ -16050,7 +16626,7 @@
         <v>62</v>
       </c>
       <c r="C831">
-        <v>5350</v>
+        <v>5110</v>
       </c>
       <c r="D831" t="s">
         <v>833</v>
@@ -16064,7 +16640,7 @@
         <v>63</v>
       </c>
       <c r="C832">
-        <v>5410</v>
+        <v>5140</v>
       </c>
       <c r="D832" t="s">
         <v>834</v>
@@ -16078,7 +16654,7 @@
         <v>64</v>
       </c>
       <c r="C833">
-        <v>5480</v>
+        <v>5200</v>
       </c>
       <c r="D833" t="s">
         <v>835</v>
@@ -16092,7 +16668,7 @@
         <v>65</v>
       </c>
       <c r="C834">
-        <v>5570</v>
+        <v>5300</v>
       </c>
       <c r="D834" t="s">
         <v>836</v>
@@ -16106,7 +16682,7 @@
         <v>66</v>
       </c>
       <c r="C835">
-        <v>5660</v>
+        <v>5400</v>
       </c>
       <c r="D835" t="s">
         <v>837</v>
@@ -16120,7 +16696,7 @@
         <v>67</v>
       </c>
       <c r="C836">
-        <v>5760</v>
+        <v>5510</v>
       </c>
       <c r="D836" t="s">
         <v>838</v>
@@ -16134,7 +16710,7 @@
         <v>68</v>
       </c>
       <c r="C837">
-        <v>5860</v>
+        <v>5630</v>
       </c>
       <c r="D837" t="s">
         <v>839</v>
@@ -16148,7 +16724,7 @@
         <v>69</v>
       </c>
       <c r="C838">
-        <v>5960</v>
+        <v>5750</v>
       </c>
       <c r="D838" t="s">
         <v>840</v>
@@ -16162,7 +16738,7 @@
         <v>70</v>
       </c>
       <c r="C839">
-        <v>6070</v>
+        <v>5890</v>
       </c>
       <c r="D839" t="s">
         <v>841</v>
@@ -16176,7 +16752,7 @@
         <v>71</v>
       </c>
       <c r="C840">
-        <v>6160</v>
+        <v>6020</v>
       </c>
       <c r="D840" t="s">
         <v>842</v>
@@ -16190,7 +16766,7 @@
         <v>72</v>
       </c>
       <c r="C841">
-        <v>6260</v>
+        <v>6150</v>
       </c>
       <c r="D841" t="s">
         <v>843</v>
@@ -16204,7 +16780,7 @@
         <v>73</v>
       </c>
       <c r="C842">
-        <v>6360</v>
+        <v>6300</v>
       </c>
       <c r="D842" t="s">
         <v>844</v>
@@ -16218,7 +16794,7 @@
         <v>74</v>
       </c>
       <c r="C843">
-        <v>6470</v>
+        <v>6430</v>
       </c>
       <c r="D843" t="s">
         <v>845</v>
@@ -16232,7 +16808,7 @@
         <v>75</v>
       </c>
       <c r="C844">
-        <v>6580</v>
+        <v>6560</v>
       </c>
       <c r="D844" t="s">
         <v>846</v>
@@ -16246,7 +16822,7 @@
         <v>76</v>
       </c>
       <c r="C845">
-        <v>6700</v>
+        <v>6690</v>
       </c>
       <c r="D845" t="s">
         <v>847</v>
@@ -16274,7 +16850,7 @@
         <v>78</v>
       </c>
       <c r="C847">
-        <v>6910</v>
+        <v>6920</v>
       </c>
       <c r="D847" t="s">
         <v>849</v>
@@ -16288,7 +16864,7 @@
         <v>79</v>
       </c>
       <c r="C848">
-        <v>6940</v>
+        <v>6980</v>
       </c>
       <c r="D848" t="s">
         <v>850</v>
@@ -16302,7 +16878,7 @@
         <v>80</v>
       </c>
       <c r="C849">
-        <v>6950</v>
+        <v>7000</v>
       </c>
       <c r="D849" t="s">
         <v>851</v>
@@ -16316,7 +16892,7 @@
         <v>81</v>
       </c>
       <c r="C850">
-        <v>6950</v>
+        <v>7000</v>
       </c>
       <c r="D850" t="s">
         <v>852</v>
@@ -16330,7 +16906,7 @@
         <v>82</v>
       </c>
       <c r="C851">
-        <v>6940</v>
+        <v>6980</v>
       </c>
       <c r="D851" t="s">
         <v>853</v>
@@ -16344,7 +16920,7 @@
         <v>83</v>
       </c>
       <c r="C852">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="D852" t="s">
         <v>854</v>
@@ -16358,7 +16934,7 @@
         <v>84</v>
       </c>
       <c r="C853">
-        <v>6880</v>
+        <v>6860</v>
       </c>
       <c r="D853" t="s">
         <v>855</v>
@@ -16372,7 +16948,7 @@
         <v>85</v>
       </c>
       <c r="C854">
-        <v>6780</v>
+        <v>6730</v>
       </c>
       <c r="D854" t="s">
         <v>856</v>
@@ -16386,7 +16962,7 @@
         <v>86</v>
       </c>
       <c r="C855">
-        <v>6680</v>
+        <v>6600</v>
       </c>
       <c r="D855" t="s">
         <v>857</v>
@@ -16400,7 +16976,7 @@
         <v>87</v>
       </c>
       <c r="C856">
-        <v>6560</v>
+        <v>6490</v>
       </c>
       <c r="D856" t="s">
         <v>858</v>
@@ -16414,7 +16990,7 @@
         <v>88</v>
       </c>
       <c r="C857">
-        <v>6450</v>
+        <v>6370</v>
       </c>
       <c r="D857" t="s">
         <v>859</v>
@@ -16428,7 +17004,7 @@
         <v>89</v>
       </c>
       <c r="C858">
-        <v>6300</v>
+        <v>6210</v>
       </c>
       <c r="D858" t="s">
         <v>860</v>
@@ -16442,7 +17018,7 @@
         <v>90</v>
       </c>
       <c r="C859">
-        <v>6170</v>
+        <v>6080</v>
       </c>
       <c r="D859" t="s">
         <v>861</v>
@@ -16456,7 +17032,7 @@
         <v>91</v>
       </c>
       <c r="C860">
-        <v>6020</v>
+        <v>5930</v>
       </c>
       <c r="D860" t="s">
         <v>862</v>
@@ -16470,7 +17046,7 @@
         <v>92</v>
       </c>
       <c r="C861">
-        <v>5890</v>
+        <v>5800</v>
       </c>
       <c r="D861" t="s">
         <v>863</v>
@@ -16484,7 +17060,7 @@
         <v>93</v>
       </c>
       <c r="C862">
-        <v>5730</v>
+        <v>5700</v>
       </c>
       <c r="D862" t="s">
         <v>864</v>
@@ -16498,7 +17074,7 @@
         <v>94</v>
       </c>
       <c r="C863">
-        <v>5590</v>
+        <v>5580</v>
       </c>
       <c r="D863" t="s">
         <v>865</v>
@@ -16512,7 +17088,7 @@
         <v>95</v>
       </c>
       <c r="C864">
-        <v>5480</v>
+        <v>5470</v>
       </c>
       <c r="D864" t="s">
         <v>866</v>
@@ -16526,7 +17102,7 @@
         <v>96</v>
       </c>
       <c r="C865">
-        <v>5370</v>
+        <v>5360</v>
       </c>
       <c r="D865" t="s">
         <v>867</v>
@@ -16540,7 +17116,7 @@
         <v>1</v>
       </c>
       <c r="C866">
-        <v>5350</v>
+        <v>5290</v>
       </c>
       <c r="D866" t="s">
         <v>868</v>
@@ -16554,7 +17130,7 @@
         <v>2</v>
       </c>
       <c r="C867">
-        <v>5280</v>
+        <v>5240</v>
       </c>
       <c r="D867" t="s">
         <v>869</v>
@@ -16568,7 +17144,7 @@
         <v>3</v>
       </c>
       <c r="C868">
-        <v>5240</v>
+        <v>5190</v>
       </c>
       <c r="D868" t="s">
         <v>870</v>
@@ -16582,7 +17158,7 @@
         <v>4</v>
       </c>
       <c r="C869">
-        <v>5190</v>
+        <v>5120</v>
       </c>
       <c r="D869" t="s">
         <v>871</v>
@@ -16596,7 +17172,7 @@
         <v>5</v>
       </c>
       <c r="C870">
-        <v>5130</v>
+        <v>5060</v>
       </c>
       <c r="D870" t="s">
         <v>872</v>
@@ -16610,7 +17186,7 @@
         <v>6</v>
       </c>
       <c r="C871">
-        <v>5080</v>
+        <v>5000</v>
       </c>
       <c r="D871" t="s">
         <v>873</v>
@@ -16624,7 +17200,7 @@
         <v>7</v>
       </c>
       <c r="C872">
-        <v>5040</v>
+        <v>4960</v>
       </c>
       <c r="D872" t="s">
         <v>874</v>
@@ -16638,7 +17214,7 @@
         <v>8</v>
       </c>
       <c r="C873">
-        <v>5000</v>
+        <v>4930</v>
       </c>
       <c r="D873" t="s">
         <v>875</v>
@@ -16652,7 +17228,7 @@
         <v>9</v>
       </c>
       <c r="C874">
-        <v>4980</v>
+        <v>4920</v>
       </c>
       <c r="D874" t="s">
         <v>876</v>
@@ -16666,7 +17242,7 @@
         <v>10</v>
       </c>
       <c r="C875">
-        <v>4960</v>
+        <v>4910</v>
       </c>
       <c r="D875" t="s">
         <v>877</v>
@@ -16680,7 +17256,7 @@
         <v>11</v>
       </c>
       <c r="C876">
-        <v>4960</v>
+        <v>4900</v>
       </c>
       <c r="D876" t="s">
         <v>878</v>
@@ -16694,7 +17270,7 @@
         <v>12</v>
       </c>
       <c r="C877">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="D877" t="s">
         <v>879</v>
@@ -16708,7 +17284,7 @@
         <v>13</v>
       </c>
       <c r="C878">
-        <v>4950</v>
+        <v>4910</v>
       </c>
       <c r="D878" t="s">
         <v>880</v>
@@ -16722,7 +17298,7 @@
         <v>14</v>
       </c>
       <c r="C879">
-        <v>4960</v>
+        <v>4910</v>
       </c>
       <c r="D879" t="s">
         <v>881</v>
@@ -16736,7 +17312,7 @@
         <v>15</v>
       </c>
       <c r="C880">
-        <v>4960</v>
+        <v>4920</v>
       </c>
       <c r="D880" t="s">
         <v>882</v>
@@ -16750,7 +17326,7 @@
         <v>16</v>
       </c>
       <c r="C881">
-        <v>4970</v>
+        <v>4920</v>
       </c>
       <c r="D881" t="s">
         <v>883</v>
@@ -16764,7 +17340,7 @@
         <v>17</v>
       </c>
       <c r="C882">
-        <v>4980</v>
+        <v>4930</v>
       </c>
       <c r="D882" t="s">
         <v>884</v>
@@ -16778,7 +17354,7 @@
         <v>18</v>
       </c>
       <c r="C883">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="D883" t="s">
         <v>885</v>
@@ -16792,7 +17368,7 @@
         <v>19</v>
       </c>
       <c r="C884">
-        <v>5020</v>
+        <v>4970</v>
       </c>
       <c r="D884" t="s">
         <v>886</v>
@@ -16806,7 +17382,7 @@
         <v>20</v>
       </c>
       <c r="C885">
-        <v>5050</v>
+        <v>4990</v>
       </c>
       <c r="D885" t="s">
         <v>887</v>
@@ -16820,7 +17396,7 @@
         <v>21</v>
       </c>
       <c r="C886">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="D886" t="s">
         <v>888</v>
@@ -16834,7 +17410,7 @@
         <v>22</v>
       </c>
       <c r="C887">
-        <v>5120</v>
+        <v>5060</v>
       </c>
       <c r="D887" t="s">
         <v>889</v>
@@ -16848,7 +17424,7 @@
         <v>23</v>
       </c>
       <c r="C888">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D888" t="s">
         <v>890</v>
@@ -16862,7 +17438,7 @@
         <v>24</v>
       </c>
       <c r="C889">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="D889" t="s">
         <v>891</v>
@@ -16876,7 +17452,7 @@
         <v>25</v>
       </c>
       <c r="C890">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="D890" t="s">
         <v>892</v>
@@ -16890,7 +17466,7 @@
         <v>26</v>
       </c>
       <c r="C891">
-        <v>5290</v>
+        <v>5240</v>
       </c>
       <c r="D891" t="s">
         <v>893</v>
@@ -16904,7 +17480,7 @@
         <v>27</v>
       </c>
       <c r="C892">
-        <v>5330</v>
+        <v>5290</v>
       </c>
       <c r="D892" t="s">
         <v>894</v>
@@ -16918,7 +17494,7 @@
         <v>28</v>
       </c>
       <c r="C893">
-        <v>5370</v>
+        <v>5340</v>
       </c>
       <c r="D893" t="s">
         <v>895</v>
@@ -16932,7 +17508,7 @@
         <v>29</v>
       </c>
       <c r="C894">
-        <v>5420</v>
+        <v>5380</v>
       </c>
       <c r="D894" t="s">
         <v>896</v>
@@ -16946,7 +17522,7 @@
         <v>30</v>
       </c>
       <c r="C895">
-        <v>5460</v>
+        <v>5420</v>
       </c>
       <c r="D895" t="s">
         <v>897</v>
@@ -16960,7 +17536,7 @@
         <v>31</v>
       </c>
       <c r="C896">
-        <v>5490</v>
+        <v>5450</v>
       </c>
       <c r="D896" t="s">
         <v>898</v>
@@ -16974,7 +17550,7 @@
         <v>32</v>
       </c>
       <c r="C897">
-        <v>5500</v>
+        <v>5480</v>
       </c>
       <c r="D897" t="s">
         <v>899</v>
@@ -17030,7 +17606,7 @@
         <v>36</v>
       </c>
       <c r="C901">
-        <v>5500</v>
+        <v>5480</v>
       </c>
       <c r="D901" t="s">
         <v>903</v>
@@ -17044,7 +17620,7 @@
         <v>37</v>
       </c>
       <c r="C902">
-        <v>5460</v>
+        <v>5440</v>
       </c>
       <c r="D902" t="s">
         <v>904</v>
@@ -17058,7 +17634,7 @@
         <v>38</v>
       </c>
       <c r="C903">
-        <v>5400</v>
+        <v>5390</v>
       </c>
       <c r="D903" t="s">
         <v>905</v>
@@ -17072,7 +17648,7 @@
         <v>39</v>
       </c>
       <c r="C904">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="D904" t="s">
         <v>906</v>
@@ -17142,7 +17718,7 @@
         <v>44</v>
       </c>
       <c r="C909">
-        <v>4920</v>
+        <v>4930</v>
       </c>
       <c r="D909" t="s">
         <v>911</v>
@@ -17226,7 +17802,7 @@
         <v>50</v>
       </c>
       <c r="C915">
-        <v>4630</v>
+        <v>4620</v>
       </c>
       <c r="D915" t="s">
         <v>917</v>
@@ -17548,7 +18124,7 @@
         <v>73</v>
       </c>
       <c r="C938">
-        <v>5930</v>
+        <v>5920</v>
       </c>
       <c r="D938" t="s">
         <v>940</v>
@@ -17562,7 +18138,7 @@
         <v>74</v>
       </c>
       <c r="C939">
-        <v>6050</v>
+        <v>6030</v>
       </c>
       <c r="D939" t="s">
         <v>941</v>
@@ -17576,7 +18152,7 @@
         <v>75</v>
       </c>
       <c r="C940">
-        <v>6170</v>
+        <v>6140</v>
       </c>
       <c r="D940" t="s">
         <v>942</v>
@@ -17590,7 +18166,7 @@
         <v>76</v>
       </c>
       <c r="C941">
-        <v>6300</v>
+        <v>6250</v>
       </c>
       <c r="D941" t="s">
         <v>943</v>
@@ -17604,7 +18180,7 @@
         <v>77</v>
       </c>
       <c r="C942">
-        <v>6410</v>
+        <v>6350</v>
       </c>
       <c r="D942" t="s">
         <v>944</v>
@@ -17618,7 +18194,7 @@
         <v>78</v>
       </c>
       <c r="C943">
-        <v>6510</v>
+        <v>6430</v>
       </c>
       <c r="D943" t="s">
         <v>945</v>
@@ -17632,7 +18208,7 @@
         <v>79</v>
       </c>
       <c r="C944">
-        <v>6550</v>
+        <v>6450</v>
       </c>
       <c r="D944" t="s">
         <v>946</v>
@@ -17646,7 +18222,7 @@
         <v>80</v>
       </c>
       <c r="C945">
-        <v>6550</v>
+        <v>6450</v>
       </c>
       <c r="D945" t="s">
         <v>947</v>
@@ -17660,7 +18236,7 @@
         <v>81</v>
       </c>
       <c r="C946">
-        <v>6550</v>
+        <v>6450</v>
       </c>
       <c r="D946" t="s">
         <v>948</v>
@@ -17674,7 +18250,7 @@
         <v>82</v>
       </c>
       <c r="C947">
-        <v>6550</v>
+        <v>6450</v>
       </c>
       <c r="D947" t="s">
         <v>949</v>
@@ -17688,7 +18264,7 @@
         <v>83</v>
       </c>
       <c r="C948">
-        <v>6540</v>
+        <v>6450</v>
       </c>
       <c r="D948" t="s">
         <v>950</v>
@@ -17702,7 +18278,7 @@
         <v>84</v>
       </c>
       <c r="C949">
-        <v>6490</v>
+        <v>6420</v>
       </c>
       <c r="D949" t="s">
         <v>951</v>
@@ -17716,7 +18292,7 @@
         <v>85</v>
       </c>
       <c r="C950">
-        <v>6400</v>
+        <v>6330</v>
       </c>
       <c r="D950" t="s">
         <v>952</v>
@@ -17730,7 +18306,7 @@
         <v>86</v>
       </c>
       <c r="C951">
-        <v>6280</v>
+        <v>6250</v>
       </c>
       <c r="D951" t="s">
         <v>953</v>
@@ -17744,7 +18320,7 @@
         <v>87</v>
       </c>
       <c r="C952">
-        <v>6220</v>
+        <v>6170</v>
       </c>
       <c r="D952" t="s">
         <v>954</v>
@@ -17758,7 +18334,7 @@
         <v>88</v>
       </c>
       <c r="C953">
-        <v>6140</v>
+        <v>6090</v>
       </c>
       <c r="D953" t="s">
         <v>955</v>
@@ -17772,7 +18348,7 @@
         <v>89</v>
       </c>
       <c r="C954">
-        <v>6010</v>
+        <v>5970</v>
       </c>
       <c r="D954" t="s">
         <v>956</v>
@@ -17786,7 +18362,7 @@
         <v>90</v>
       </c>
       <c r="C955">
-        <v>5920</v>
+        <v>5870</v>
       </c>
       <c r="D955" t="s">
         <v>957</v>
@@ -17800,7 +18376,7 @@
         <v>91</v>
       </c>
       <c r="C956">
-        <v>5780</v>
+        <v>5730</v>
       </c>
       <c r="D956" t="s">
         <v>958</v>
@@ -17814,7 +18390,7 @@
         <v>92</v>
       </c>
       <c r="C957">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="D957" t="s">
         <v>959</v>
@@ -17828,7 +18404,7 @@
         <v>93</v>
       </c>
       <c r="C958">
-        <v>5510</v>
+        <v>5460</v>
       </c>
       <c r="D958" t="s">
         <v>960</v>
@@ -17842,7 +18418,7 @@
         <v>94</v>
       </c>
       <c r="C959">
-        <v>5380</v>
+        <v>5330</v>
       </c>
       <c r="D959" t="s">
         <v>961</v>
@@ -17856,7 +18432,7 @@
         <v>95</v>
       </c>
       <c r="C960">
-        <v>5270</v>
+        <v>5230</v>
       </c>
       <c r="D960" t="s">
         <v>962</v>
@@ -17870,7 +18446,7 @@
         <v>96</v>
       </c>
       <c r="C961">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="D961" t="s">
         <v>963</v>
@@ -17884,7 +18460,7 @@
         <v>1</v>
       </c>
       <c r="C962">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="D962" t="s">
         <v>964</v>
@@ -17898,7 +18474,7 @@
         <v>2</v>
       </c>
       <c r="C963">
-        <v>5020</v>
+        <v>4940</v>
       </c>
       <c r="D963" t="s">
         <v>965</v>
@@ -17912,7 +18488,7 @@
         <v>3</v>
       </c>
       <c r="C964">
-        <v>5000</v>
+        <v>4890</v>
       </c>
       <c r="D964" t="s">
         <v>966</v>
@@ -17926,7 +18502,7 @@
         <v>4</v>
       </c>
       <c r="C965">
-        <v>4940</v>
+        <v>4830</v>
       </c>
       <c r="D965" t="s">
         <v>967</v>
@@ -17940,7 +18516,7 @@
         <v>5</v>
       </c>
       <c r="C966">
-        <v>4870</v>
+        <v>4780</v>
       </c>
       <c r="D966" t="s">
         <v>968</v>
@@ -17954,7 +18530,7 @@
         <v>6</v>
       </c>
       <c r="C967">
-        <v>4820</v>
+        <v>4730</v>
       </c>
       <c r="D967" t="s">
         <v>969</v>
@@ -17968,7 +18544,7 @@
         <v>7</v>
       </c>
       <c r="C968">
-        <v>4790</v>
+        <v>4690</v>
       </c>
       <c r="D968" t="s">
         <v>970</v>
@@ -17982,7 +18558,7 @@
         <v>8</v>
       </c>
       <c r="C969">
-        <v>4780</v>
+        <v>4640</v>
       </c>
       <c r="D969" t="s">
         <v>971</v>
@@ -17996,7 +18572,7 @@
         <v>9</v>
       </c>
       <c r="C970">
-        <v>4790</v>
+        <v>4600</v>
       </c>
       <c r="D970" t="s">
         <v>972</v>
@@ -18010,7 +18586,7 @@
         <v>10</v>
       </c>
       <c r="C971">
-        <v>4790</v>
+        <v>4570</v>
       </c>
       <c r="D971" t="s">
         <v>973</v>
@@ -18024,7 +18600,7 @@
         <v>11</v>
       </c>
       <c r="C972">
-        <v>4790</v>
+        <v>4540</v>
       </c>
       <c r="D972" t="s">
         <v>974</v>
@@ -18038,7 +18614,7 @@
         <v>12</v>
       </c>
       <c r="C973">
-        <v>4780</v>
+        <v>4530</v>
       </c>
       <c r="D973" t="s">
         <v>975</v>
@@ -18052,7 +18628,7 @@
         <v>13</v>
       </c>
       <c r="C974">
-        <v>4770</v>
+        <v>4520</v>
       </c>
       <c r="D974" t="s">
         <v>976</v>
@@ -18066,7 +18642,7 @@
         <v>14</v>
       </c>
       <c r="C975">
-        <v>4760</v>
+        <v>4500</v>
       </c>
       <c r="D975" t="s">
         <v>977</v>
@@ -18080,7 +18656,7 @@
         <v>15</v>
       </c>
       <c r="C976">
-        <v>4750</v>
+        <v>4500</v>
       </c>
       <c r="D976" t="s">
         <v>978</v>
@@ -18094,7 +18670,7 @@
         <v>16</v>
       </c>
       <c r="C977">
-        <v>4740</v>
+        <v>4500</v>
       </c>
       <c r="D977" t="s">
         <v>979</v>
@@ -18108,7 +18684,7 @@
         <v>17</v>
       </c>
       <c r="C978">
-        <v>4740</v>
+        <v>4510</v>
       </c>
       <c r="D978" t="s">
         <v>980</v>
@@ -18122,7 +18698,7 @@
         <v>18</v>
       </c>
       <c r="C979">
-        <v>4750</v>
+        <v>4530</v>
       </c>
       <c r="D979" t="s">
         <v>981</v>
@@ -18136,7 +18712,7 @@
         <v>19</v>
       </c>
       <c r="C980">
-        <v>4770</v>
+        <v>4540</v>
       </c>
       <c r="D980" t="s">
         <v>982</v>
@@ -18150,7 +18726,7 @@
         <v>20</v>
       </c>
       <c r="C981">
-        <v>4780</v>
+        <v>4550</v>
       </c>
       <c r="D981" t="s">
         <v>983</v>
@@ -18164,7 +18740,7 @@
         <v>21</v>
       </c>
       <c r="C982">
-        <v>4790</v>
+        <v>4570</v>
       </c>
       <c r="D982" t="s">
         <v>984</v>
@@ -18178,7 +18754,7 @@
         <v>22</v>
       </c>
       <c r="C983">
-        <v>4800</v>
+        <v>4590</v>
       </c>
       <c r="D983" t="s">
         <v>985</v>
@@ -18192,7 +18768,7 @@
         <v>23</v>
       </c>
       <c r="C984">
-        <v>4810</v>
+        <v>4620</v>
       </c>
       <c r="D984" t="s">
         <v>986</v>
@@ -18206,7 +18782,7 @@
         <v>24</v>
       </c>
       <c r="C985">
-        <v>4820</v>
+        <v>4650</v>
       </c>
       <c r="D985" t="s">
         <v>987</v>
@@ -18220,7 +18796,7 @@
         <v>25</v>
       </c>
       <c r="C986">
-        <v>4820</v>
+        <v>4680</v>
       </c>
       <c r="D986" t="s">
         <v>988</v>
@@ -18234,7 +18810,7 @@
         <v>26</v>
       </c>
       <c r="C987">
-        <v>4840</v>
+        <v>4710</v>
       </c>
       <c r="D987" t="s">
         <v>989</v>
@@ -18248,7 +18824,7 @@
         <v>27</v>
       </c>
       <c r="C988">
-        <v>4850</v>
+        <v>4740</v>
       </c>
       <c r="D988" t="s">
         <v>990</v>
@@ -18262,7 +18838,7 @@
         <v>28</v>
       </c>
       <c r="C989">
-        <v>4870</v>
+        <v>4770</v>
       </c>
       <c r="D989" t="s">
         <v>991</v>
@@ -18276,7 +18852,7 @@
         <v>29</v>
       </c>
       <c r="C990">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="D990" t="s">
         <v>992</v>
@@ -18290,7 +18866,7 @@
         <v>30</v>
       </c>
       <c r="C991">
-        <v>4920</v>
+        <v>4820</v>
       </c>
       <c r="D991" t="s">
         <v>993</v>
@@ -18304,7 +18880,7 @@
         <v>31</v>
       </c>
       <c r="C992">
-        <v>4940</v>
+        <v>4840</v>
       </c>
       <c r="D992" t="s">
         <v>994</v>
@@ -18318,7 +18894,7 @@
         <v>32</v>
       </c>
       <c r="C993">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="D993" t="s">
         <v>995</v>
@@ -18332,7 +18908,7 @@
         <v>33</v>
       </c>
       <c r="C994">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="D994" t="s">
         <v>996</v>
@@ -18346,7 +18922,7 @@
         <v>34</v>
       </c>
       <c r="C995">
-        <v>4920</v>
+        <v>4850</v>
       </c>
       <c r="D995" t="s">
         <v>997</v>
@@ -18360,7 +18936,7 @@
         <v>35</v>
       </c>
       <c r="C996">
-        <v>4870</v>
+        <v>4840</v>
       </c>
       <c r="D996" t="s">
         <v>998</v>
@@ -18374,7 +18950,7 @@
         <v>36</v>
       </c>
       <c r="C997">
-        <v>4790</v>
+        <v>4810</v>
       </c>
       <c r="D997" t="s">
         <v>999</v>
@@ -18388,7 +18964,7 @@
         <v>37</v>
       </c>
       <c r="C998">
-        <v>4680</v>
+        <v>4780</v>
       </c>
       <c r="D998" t="s">
         <v>1000</v>
@@ -18402,7 +18978,7 @@
         <v>38</v>
       </c>
       <c r="C999">
-        <v>4560</v>
+        <v>4740</v>
       </c>
       <c r="D999" t="s">
         <v>1001</v>
@@ -18416,7 +18992,7 @@
         <v>39</v>
       </c>
       <c r="C1000">
-        <v>4410</v>
+        <v>4690</v>
       </c>
       <c r="D1000" t="s">
         <v>1002</v>
@@ -18430,7 +19006,7 @@
         <v>40</v>
       </c>
       <c r="C1001">
-        <v>4260</v>
+        <v>4630</v>
       </c>
       <c r="D1001" t="s">
         <v>1003</v>
@@ -18444,7 +19020,7 @@
         <v>41</v>
       </c>
       <c r="C1002">
-        <v>4110</v>
+        <v>4580</v>
       </c>
       <c r="D1002" t="s">
         <v>1004</v>
@@ -18458,7 +19034,7 @@
         <v>42</v>
       </c>
       <c r="C1003">
-        <v>3960</v>
+        <v>4520</v>
       </c>
       <c r="D1003" t="s">
         <v>1005</v>
@@ -18472,7 +19048,7 @@
         <v>43</v>
       </c>
       <c r="C1004">
-        <v>3820</v>
+        <v>4470</v>
       </c>
       <c r="D1004" t="s">
         <v>1006</v>
@@ -18486,7 +19062,7 @@
         <v>44</v>
       </c>
       <c r="C1005">
-        <v>3700</v>
+        <v>4420</v>
       </c>
       <c r="D1005" t="s">
         <v>1007</v>
@@ -18500,7 +19076,7 @@
         <v>45</v>
       </c>
       <c r="C1006">
-        <v>3590</v>
+        <v>4380</v>
       </c>
       <c r="D1006" t="s">
         <v>1008</v>
@@ -18514,7 +19090,7 @@
         <v>46</v>
       </c>
       <c r="C1007">
-        <v>3510</v>
+        <v>4350</v>
       </c>
       <c r="D1007" t="s">
         <v>1009</v>
@@ -18528,7 +19104,7 @@
         <v>47</v>
       </c>
       <c r="C1008">
-        <v>3440</v>
+        <v>4310</v>
       </c>
       <c r="D1008" t="s">
         <v>1010</v>
@@ -18542,7 +19118,7 @@
         <v>48</v>
       </c>
       <c r="C1009">
-        <v>3390</v>
+        <v>4280</v>
       </c>
       <c r="D1009" t="s">
         <v>1011</v>
@@ -18556,7 +19132,7 @@
         <v>49</v>
       </c>
       <c r="C1010">
-        <v>3350</v>
+        <v>4250</v>
       </c>
       <c r="D1010" t="s">
         <v>1012</v>
@@ -18570,7 +19146,7 @@
         <v>50</v>
       </c>
       <c r="C1011">
-        <v>3330</v>
+        <v>4230</v>
       </c>
       <c r="D1011" t="s">
         <v>1013</v>
@@ -18584,7 +19160,7 @@
         <v>51</v>
       </c>
       <c r="C1012">
-        <v>3320</v>
+        <v>4200</v>
       </c>
       <c r="D1012" t="s">
         <v>1014</v>
@@ -18598,7 +19174,7 @@
         <v>52</v>
       </c>
       <c r="C1013">
-        <v>3310</v>
+        <v>4180</v>
       </c>
       <c r="D1013" t="s">
         <v>1015</v>
@@ -18612,7 +19188,7 @@
         <v>53</v>
       </c>
       <c r="C1014">
-        <v>3320</v>
+        <v>4160</v>
       </c>
       <c r="D1014" t="s">
         <v>1016</v>
@@ -18626,7 +19202,7 @@
         <v>54</v>
       </c>
       <c r="C1015">
-        <v>3330</v>
+        <v>4150</v>
       </c>
       <c r="D1015" t="s">
         <v>1017</v>
@@ -18640,7 +19216,7 @@
         <v>55</v>
       </c>
       <c r="C1016">
-        <v>3350</v>
+        <v>4150</v>
       </c>
       <c r="D1016" t="s">
         <v>1018</v>
@@ -18654,7 +19230,7 @@
         <v>56</v>
       </c>
       <c r="C1017">
-        <v>3380</v>
+        <v>4150</v>
       </c>
       <c r="D1017" t="s">
         <v>1019</v>
@@ -18668,7 +19244,7 @@
         <v>57</v>
       </c>
       <c r="C1018">
-        <v>3410</v>
+        <v>4170</v>
       </c>
       <c r="D1018" t="s">
         <v>1020</v>
@@ -18682,7 +19258,7 @@
         <v>58</v>
       </c>
       <c r="C1019">
-        <v>3450</v>
+        <v>4200</v>
       </c>
       <c r="D1019" t="s">
         <v>1021</v>
@@ -18696,7 +19272,7 @@
         <v>59</v>
       </c>
       <c r="C1020">
-        <v>3500</v>
+        <v>4240</v>
       </c>
       <c r="D1020" t="s">
         <v>1022</v>
@@ -18710,7 +19286,7 @@
         <v>60</v>
       </c>
       <c r="C1021">
-        <v>3550</v>
+        <v>4280</v>
       </c>
       <c r="D1021" t="s">
         <v>1023</v>
@@ -18724,7 +19300,7 @@
         <v>61</v>
       </c>
       <c r="C1022">
-        <v>3600</v>
+        <v>4330</v>
       </c>
       <c r="D1022" t="s">
         <v>1024</v>
@@ -18738,7 +19314,7 @@
         <v>62</v>
       </c>
       <c r="C1023">
-        <v>3670</v>
+        <v>4380</v>
       </c>
       <c r="D1023" t="s">
         <v>1025</v>
@@ -18752,7 +19328,7 @@
         <v>63</v>
       </c>
       <c r="C1024">
-        <v>3750</v>
+        <v>4440</v>
       </c>
       <c r="D1024" t="s">
         <v>1026</v>
@@ -18766,7 +19342,7 @@
         <v>64</v>
       </c>
       <c r="C1025">
-        <v>3840</v>
+        <v>4500</v>
       </c>
       <c r="D1025" t="s">
         <v>1027</v>
@@ -18780,7 +19356,7 @@
         <v>65</v>
       </c>
       <c r="C1026">
-        <v>3960</v>
+        <v>4580</v>
       </c>
       <c r="D1026" t="s">
         <v>1028</v>
@@ -18794,7 +19370,7 @@
         <v>66</v>
       </c>
       <c r="C1027">
-        <v>4090</v>
+        <v>4660</v>
       </c>
       <c r="D1027" t="s">
         <v>1029</v>
@@ -18808,7 +19384,7 @@
         <v>67</v>
       </c>
       <c r="C1028">
-        <v>4250</v>
+        <v>4750</v>
       </c>
       <c r="D1028" t="s">
         <v>1030</v>
@@ -18822,7 +19398,7 @@
         <v>68</v>
       </c>
       <c r="C1029">
-        <v>4410</v>
+        <v>4850</v>
       </c>
       <c r="D1029" t="s">
         <v>1031</v>
@@ -18836,7 +19412,7 @@
         <v>69</v>
       </c>
       <c r="C1030">
-        <v>4590</v>
+        <v>4960</v>
       </c>
       <c r="D1030" t="s">
         <v>1032</v>
@@ -18850,7 +19426,7 @@
         <v>70</v>
       </c>
       <c r="C1031">
-        <v>4760</v>
+        <v>5080</v>
       </c>
       <c r="D1031" t="s">
         <v>1033</v>
@@ -18864,7 +19440,7 @@
         <v>71</v>
       </c>
       <c r="C1032">
-        <v>4930</v>
+        <v>5200</v>
       </c>
       <c r="D1032" t="s">
         <v>1034</v>
@@ -18878,7 +19454,7 @@
         <v>72</v>
       </c>
       <c r="C1033">
-        <v>5090</v>
+        <v>5330</v>
       </c>
       <c r="D1033" t="s">
         <v>1035</v>
@@ -18892,7 +19468,7 @@
         <v>73</v>
       </c>
       <c r="C1034">
-        <v>5240</v>
+        <v>5450</v>
       </c>
       <c r="D1034" t="s">
         <v>1036</v>
@@ -18906,7 +19482,7 @@
         <v>74</v>
       </c>
       <c r="C1035">
-        <v>5380</v>
+        <v>5570</v>
       </c>
       <c r="D1035" t="s">
         <v>1037</v>
@@ -18920,7 +19496,7 @@
         <v>75</v>
       </c>
       <c r="C1036">
-        <v>5520</v>
+        <v>5700</v>
       </c>
       <c r="D1036" t="s">
         <v>1038</v>
@@ -18934,7 +19510,7 @@
         <v>76</v>
       </c>
       <c r="C1037">
-        <v>5660</v>
+        <v>5820</v>
       </c>
       <c r="D1037" t="s">
         <v>1039</v>
@@ -18948,7 +19524,7 @@
         <v>77</v>
       </c>
       <c r="C1038">
-        <v>5800</v>
+        <v>5930</v>
       </c>
       <c r="D1038" t="s">
         <v>1040</v>
@@ -18962,7 +19538,7 @@
         <v>78</v>
       </c>
       <c r="C1039">
-        <v>5930</v>
+        <v>6020</v>
       </c>
       <c r="D1039" t="s">
         <v>1041</v>
@@ -18990,7 +19566,7 @@
         <v>80</v>
       </c>
       <c r="C1041">
-        <v>6140</v>
+        <v>6050</v>
       </c>
       <c r="D1041" t="s">
         <v>1043</v>
@@ -19004,7 +19580,7 @@
         <v>81</v>
       </c>
       <c r="C1042">
-        <v>6210</v>
+        <v>6050</v>
       </c>
       <c r="D1042" t="s">
         <v>1044</v>
@@ -19018,7 +19594,7 @@
         <v>82</v>
       </c>
       <c r="C1043">
-        <v>6240</v>
+        <v>6050</v>
       </c>
       <c r="D1043" t="s">
         <v>1045</v>
@@ -19032,7 +19608,7 @@
         <v>83</v>
       </c>
       <c r="C1044">
-        <v>6190</v>
+        <v>6050</v>
       </c>
       <c r="D1044" t="s">
         <v>1046</v>
@@ -19046,7 +19622,7 @@
         <v>84</v>
       </c>
       <c r="C1045">
-        <v>6110</v>
+        <v>6020</v>
       </c>
       <c r="D1045" t="s">
         <v>1047</v>
@@ -19060,7 +19636,7 @@
         <v>85</v>
       </c>
       <c r="C1046">
-        <v>5950</v>
+        <v>5940</v>
       </c>
       <c r="D1046" t="s">
         <v>1048</v>
@@ -19074,7 +19650,7 @@
         <v>86</v>
       </c>
       <c r="C1047">
-        <v>5780</v>
+        <v>5840</v>
       </c>
       <c r="D1047" t="s">
         <v>1049</v>
@@ -19088,7 +19664,7 @@
         <v>87</v>
       </c>
       <c r="C1048">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="D1048" t="s">
         <v>1050</v>
@@ -19102,7 +19678,7 @@
         <v>88</v>
       </c>
       <c r="C1049">
-        <v>5640</v>
+        <v>5740</v>
       </c>
       <c r="D1049" t="s">
         <v>1051</v>
@@ -19116,7 +19692,7 @@
         <v>89</v>
       </c>
       <c r="C1050">
-        <v>5530</v>
+        <v>5640</v>
       </c>
       <c r="D1050" t="s">
         <v>1052</v>
@@ -19130,7 +19706,7 @@
         <v>90</v>
       </c>
       <c r="C1051">
-        <v>5420</v>
+        <v>5570</v>
       </c>
       <c r="D1051" t="s">
         <v>1053</v>
@@ -19144,7 +19720,7 @@
         <v>91</v>
       </c>
       <c r="C1052">
-        <v>5250</v>
+        <v>5430</v>
       </c>
       <c r="D1052" t="s">
         <v>1054</v>
@@ -19158,7 +19734,7 @@
         <v>92</v>
       </c>
       <c r="C1053">
-        <v>5180</v>
+        <v>5300</v>
       </c>
       <c r="D1053" t="s">
         <v>1055</v>
@@ -19186,7 +19762,7 @@
         <v>94</v>
       </c>
       <c r="C1055">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="D1055" t="s">
         <v>1057</v>
@@ -19200,7 +19776,7 @@
         <v>95</v>
       </c>
       <c r="C1056">
-        <v>5020</v>
+        <v>4920</v>
       </c>
       <c r="D1056" t="s">
         <v>1058</v>
@@ -19214,7 +19790,7 @@
         <v>96</v>
       </c>
       <c r="C1057">
-        <v>4990</v>
+        <v>4820</v>
       </c>
       <c r="D1057" t="s">
         <v>1059</v>
@@ -19228,7 +19804,7 @@
         <v>1</v>
       </c>
       <c r="C1058">
-        <v>4990</v>
+        <v>4950</v>
       </c>
       <c r="D1058" t="s">
         <v>1060</v>
@@ -19242,7 +19818,7 @@
         <v>2</v>
       </c>
       <c r="C1059">
-        <v>4950</v>
+        <v>4880</v>
       </c>
       <c r="D1059" t="s">
         <v>1061</v>
@@ -19256,7 +19832,7 @@
         <v>3</v>
       </c>
       <c r="C1060">
-        <v>4890</v>
+        <v>4840</v>
       </c>
       <c r="D1060" t="s">
         <v>1062</v>
@@ -19270,7 +19846,7 @@
         <v>4</v>
       </c>
       <c r="C1061">
-        <v>4830</v>
+        <v>4800</v>
       </c>
       <c r="D1061" t="s">
         <v>1063</v>
@@ -19284,7 +19860,7 @@
         <v>5</v>
       </c>
       <c r="C1062">
-        <v>4800</v>
+        <v>4760</v>
       </c>
       <c r="D1062" t="s">
         <v>1064</v>
@@ -19298,7 +19874,7 @@
         <v>6</v>
       </c>
       <c r="C1063">
-        <v>4780</v>
+        <v>4720</v>
       </c>
       <c r="D1063" t="s">
         <v>1065</v>
@@ -19312,7 +19888,7 @@
         <v>7</v>
       </c>
       <c r="C1064">
-        <v>4760</v>
+        <v>4690</v>
       </c>
       <c r="D1064" t="s">
         <v>1066</v>
@@ -19326,7 +19902,7 @@
         <v>8</v>
       </c>
       <c r="C1065">
-        <v>4740</v>
+        <v>4670</v>
       </c>
       <c r="D1065" t="s">
         <v>1067</v>
@@ -19340,7 +19916,7 @@
         <v>9</v>
       </c>
       <c r="C1066">
-        <v>4710</v>
+        <v>4640</v>
       </c>
       <c r="D1066" t="s">
         <v>1068</v>
@@ -19354,7 +19930,7 @@
         <v>10</v>
       </c>
       <c r="C1067">
-        <v>4690</v>
+        <v>4610</v>
       </c>
       <c r="D1067" t="s">
         <v>1069</v>
@@ -19368,7 +19944,7 @@
         <v>11</v>
       </c>
       <c r="C1068">
-        <v>4690</v>
+        <v>4590</v>
       </c>
       <c r="D1068" t="s">
         <v>1070</v>
@@ -19382,7 +19958,7 @@
         <v>12</v>
       </c>
       <c r="C1069">
-        <v>4700</v>
+        <v>4580</v>
       </c>
       <c r="D1069" t="s">
         <v>1071</v>
@@ -19396,7 +19972,7 @@
         <v>13</v>
       </c>
       <c r="C1070">
-        <v>4730</v>
+        <v>4570</v>
       </c>
       <c r="D1070" t="s">
         <v>1072</v>
@@ -19410,7 +19986,7 @@
         <v>14</v>
       </c>
       <c r="C1071">
-        <v>4760</v>
+        <v>4550</v>
       </c>
       <c r="D1071" t="s">
         <v>1073</v>
@@ -19424,7 +20000,7 @@
         <v>15</v>
       </c>
       <c r="C1072">
-        <v>4800</v>
+        <v>4550</v>
       </c>
       <c r="D1072" t="s">
         <v>1074</v>
@@ -19438,7 +20014,7 @@
         <v>16</v>
       </c>
       <c r="C1073">
-        <v>4840</v>
+        <v>4560</v>
       </c>
       <c r="D1073" t="s">
         <v>1075</v>
@@ -19452,7 +20028,7 @@
         <v>17</v>
       </c>
       <c r="C1074">
-        <v>4880</v>
+        <v>4610</v>
       </c>
       <c r="D1074" t="s">
         <v>1076</v>
@@ -19466,7 +20042,7 @@
         <v>18</v>
       </c>
       <c r="C1075">
-        <v>4930</v>
+        <v>4640</v>
       </c>
       <c r="D1075" t="s">
         <v>1077</v>
@@ -19480,7 +20056,7 @@
         <v>19</v>
       </c>
       <c r="C1076">
-        <v>4970</v>
+        <v>4700</v>
       </c>
       <c r="D1076" t="s">
         <v>1078</v>
@@ -19494,7 +20070,7 @@
         <v>20</v>
       </c>
       <c r="C1077">
-        <v>5030</v>
+        <v>4770</v>
       </c>
       <c r="D1077" t="s">
         <v>1079</v>
@@ -19508,7 +20084,7 @@
         <v>21</v>
       </c>
       <c r="C1078">
-        <v>5100</v>
+        <v>4870</v>
       </c>
       <c r="D1078" t="s">
         <v>1080</v>
@@ -19522,7 +20098,7 @@
         <v>22</v>
       </c>
       <c r="C1079">
-        <v>5190</v>
+        <v>4980</v>
       </c>
       <c r="D1079" t="s">
         <v>1081</v>
@@ -19536,7 +20112,7 @@
         <v>23</v>
       </c>
       <c r="C1080">
-        <v>5310</v>
+        <v>5120</v>
       </c>
       <c r="D1080" t="s">
         <v>1082</v>
@@ -19550,7 +20126,7 @@
         <v>24</v>
       </c>
       <c r="C1081">
-        <v>5450</v>
+        <v>5270</v>
       </c>
       <c r="D1081" t="s">
         <v>1083</v>
@@ -19564,7 +20140,7 @@
         <v>25</v>
       </c>
       <c r="C1082">
-        <v>5600</v>
+        <v>5430</v>
       </c>
       <c r="D1082" t="s">
         <v>1084</v>
@@ -19578,7 +20154,7 @@
         <v>26</v>
       </c>
       <c r="C1083">
-        <v>5770</v>
+        <v>5600</v>
       </c>
       <c r="D1083" t="s">
         <v>1085</v>
@@ -19592,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="C1084">
-        <v>5940</v>
+        <v>5770</v>
       </c>
       <c r="D1084" t="s">
         <v>1086</v>
@@ -19606,7 +20182,7 @@
         <v>28</v>
       </c>
       <c r="C1085">
-        <v>6110</v>
+        <v>5930</v>
       </c>
       <c r="D1085" t="s">
         <v>1087</v>
@@ -19620,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="C1086">
-        <v>6250</v>
+        <v>6080</v>
       </c>
       <c r="D1086" t="s">
         <v>1088</v>
@@ -19634,7 +20210,7 @@
         <v>30</v>
       </c>
       <c r="C1087">
-        <v>6370</v>
+        <v>6200</v>
       </c>
       <c r="D1087" t="s">
         <v>1089</v>
@@ -19648,7 +20224,7 @@
         <v>31</v>
       </c>
       <c r="C1088">
-        <v>6460</v>
+        <v>6310</v>
       </c>
       <c r="D1088" t="s">
         <v>1090</v>
@@ -19662,7 +20238,7 @@
         <v>32</v>
       </c>
       <c r="C1089">
-        <v>6500</v>
+        <v>6390</v>
       </c>
       <c r="D1089" t="s">
         <v>1091</v>
@@ -19676,7 +20252,7 @@
         <v>33</v>
       </c>
       <c r="C1090">
-        <v>6500</v>
+        <v>6430</v>
       </c>
       <c r="D1090" t="s">
         <v>1092</v>
@@ -19704,7 +20280,7 @@
         <v>35</v>
       </c>
       <c r="C1092">
-        <v>6360</v>
+        <v>6440</v>
       </c>
       <c r="D1092" t="s">
         <v>1094</v>
@@ -19718,7 +20294,7 @@
         <v>36</v>
       </c>
       <c r="C1093">
-        <v>6240</v>
+        <v>6410</v>
       </c>
       <c r="D1093" t="s">
         <v>1095</v>
@@ -19732,7 +20308,7 @@
         <v>37</v>
       </c>
       <c r="C1094">
-        <v>6090</v>
+        <v>6360</v>
       </c>
       <c r="D1094" t="s">
         <v>1096</v>
@@ -19746,7 +20322,7 @@
         <v>38</v>
       </c>
       <c r="C1095">
-        <v>5910</v>
+        <v>6290</v>
       </c>
       <c r="D1095" t="s">
         <v>1097</v>
@@ -19760,7 +20336,7 @@
         <v>39</v>
       </c>
       <c r="C1096">
-        <v>5720</v>
+        <v>6220</v>
       </c>
       <c r="D1096" t="s">
         <v>1098</v>
@@ -19774,7 +20350,7 @@
         <v>40</v>
       </c>
       <c r="C1097">
-        <v>5530</v>
+        <v>6140</v>
       </c>
       <c r="D1097" t="s">
         <v>1099</v>
@@ -19788,7 +20364,7 @@
         <v>41</v>
       </c>
       <c r="C1098">
-        <v>5330</v>
+        <v>6060</v>
       </c>
       <c r="D1098" t="s">
         <v>1100</v>
@@ -19802,7 +20378,7 @@
         <v>42</v>
       </c>
       <c r="C1099">
-        <v>5150</v>
+        <v>5980</v>
       </c>
       <c r="D1099" t="s">
         <v>1101</v>
@@ -19816,7 +20392,7 @@
         <v>43</v>
       </c>
       <c r="C1100">
-        <v>4980</v>
+        <v>5910</v>
       </c>
       <c r="D1100" t="s">
         <v>1102</v>
@@ -19830,7 +20406,7 @@
         <v>44</v>
       </c>
       <c r="C1101">
-        <v>4820</v>
+        <v>5850</v>
       </c>
       <c r="D1101" t="s">
         <v>1103</v>
@@ -19844,7 +20420,7 @@
         <v>45</v>
       </c>
       <c r="C1102">
-        <v>4690</v>
+        <v>5790</v>
       </c>
       <c r="D1102" t="s">
         <v>1104</v>
@@ -19858,7 +20434,7 @@
         <v>46</v>
       </c>
       <c r="C1103">
-        <v>4570</v>
+        <v>5740</v>
       </c>
       <c r="D1103" t="s">
         <v>1105</v>
@@ -19872,7 +20448,7 @@
         <v>47</v>
       </c>
       <c r="C1104">
-        <v>4490</v>
+        <v>5690</v>
       </c>
       <c r="D1104" t="s">
         <v>1106</v>
@@ -19886,7 +20462,7 @@
         <v>48</v>
       </c>
       <c r="C1105">
-        <v>4420</v>
+        <v>5650</v>
       </c>
       <c r="D1105" t="s">
         <v>1107</v>
@@ -19900,7 +20476,7 @@
         <v>49</v>
       </c>
       <c r="C1106">
-        <v>4370</v>
+        <v>5610</v>
       </c>
       <c r="D1106" t="s">
         <v>1108</v>
@@ -19914,7 +20490,7 @@
         <v>50</v>
       </c>
       <c r="C1107">
-        <v>4340</v>
+        <v>5580</v>
       </c>
       <c r="D1107" t="s">
         <v>1109</v>
@@ -19928,7 +20504,7 @@
         <v>51</v>
       </c>
       <c r="C1108">
-        <v>4330</v>
+        <v>5550</v>
       </c>
       <c r="D1108" t="s">
         <v>1110</v>
@@ -19942,7 +20518,7 @@
         <v>52</v>
       </c>
       <c r="C1109">
-        <v>4320</v>
+        <v>5530</v>
       </c>
       <c r="D1109" t="s">
         <v>1111</v>
@@ -19956,7 +20532,7 @@
         <v>53</v>
       </c>
       <c r="C1110">
-        <v>4330</v>
+        <v>5510</v>
       </c>
       <c r="D1110" t="s">
         <v>1112</v>
@@ -19970,7 +20546,7 @@
         <v>54</v>
       </c>
       <c r="C1111">
-        <v>4350</v>
+        <v>5500</v>
       </c>
       <c r="D1111" t="s">
         <v>1113</v>
@@ -19984,7 +20560,7 @@
         <v>55</v>
       </c>
       <c r="C1112">
-        <v>4380</v>
+        <v>5490</v>
       </c>
       <c r="D1112" t="s">
         <v>1114</v>
@@ -19998,7 +20574,7 @@
         <v>56</v>
       </c>
       <c r="C1113">
-        <v>4410</v>
+        <v>5490</v>
       </c>
       <c r="D1113" t="s">
         <v>1115</v>
@@ -20012,7 +20588,7 @@
         <v>57</v>
       </c>
       <c r="C1114">
-        <v>4450</v>
+        <v>5500</v>
       </c>
       <c r="D1114" t="s">
         <v>1116</v>
@@ -20026,7 +20602,7 @@
         <v>58</v>
       </c>
       <c r="C1115">
-        <v>4500</v>
+        <v>5510</v>
       </c>
       <c r="D1115" t="s">
         <v>1117</v>
@@ -20040,7 +20616,7 @@
         <v>59</v>
       </c>
       <c r="C1116">
-        <v>4550</v>
+        <v>5520</v>
       </c>
       <c r="D1116" t="s">
         <v>1118</v>
@@ -20054,7 +20630,7 @@
         <v>60</v>
       </c>
       <c r="C1117">
-        <v>4620</v>
+        <v>5540</v>
       </c>
       <c r="D1117" t="s">
         <v>1119</v>
@@ -20068,7 +20644,7 @@
         <v>61</v>
       </c>
       <c r="C1118">
-        <v>4700</v>
+        <v>5570</v>
       </c>
       <c r="D1118" t="s">
         <v>1120</v>
@@ -20082,7 +20658,7 @@
         <v>62</v>
       </c>
       <c r="C1119">
-        <v>4800</v>
+        <v>5590</v>
       </c>
       <c r="D1119" t="s">
         <v>1121</v>
@@ -20096,7 +20672,7 @@
         <v>63</v>
       </c>
       <c r="C1120">
-        <v>4910</v>
+        <v>5630</v>
       </c>
       <c r="D1120" t="s">
         <v>1122</v>
@@ -20110,7 +20686,7 @@
         <v>64</v>
       </c>
       <c r="C1121">
-        <v>5030</v>
+        <v>5680</v>
       </c>
       <c r="D1121" t="s">
         <v>1123</v>
@@ -20124,7 +20700,7 @@
         <v>65</v>
       </c>
       <c r="C1122">
-        <v>5150</v>
+        <v>5740</v>
       </c>
       <c r="D1122" t="s">
         <v>1124</v>
@@ -20138,7 +20714,7 @@
         <v>66</v>
       </c>
       <c r="C1123">
-        <v>5290</v>
+        <v>5810</v>
       </c>
       <c r="D1123" t="s">
         <v>1125</v>
@@ -20152,7 +20728,7 @@
         <v>67</v>
       </c>
       <c r="C1124">
-        <v>5430</v>
+        <v>5890</v>
       </c>
       <c r="D1124" t="s">
         <v>1126</v>
@@ -20166,7 +20742,7 @@
         <v>68</v>
       </c>
       <c r="C1125">
-        <v>5580</v>
+        <v>5980</v>
       </c>
       <c r="D1125" t="s">
         <v>1127</v>
@@ -20180,7 +20756,7 @@
         <v>69</v>
       </c>
       <c r="C1126">
-        <v>5730</v>
+        <v>6080</v>
       </c>
       <c r="D1126" t="s">
         <v>1128</v>
@@ -20194,7 +20770,7 @@
         <v>70</v>
       </c>
       <c r="C1127">
-        <v>5880</v>
+        <v>6170</v>
       </c>
       <c r="D1127" t="s">
         <v>1129</v>
@@ -20208,7 +20784,7 @@
         <v>71</v>
       </c>
       <c r="C1128">
-        <v>6030</v>
+        <v>6270</v>
       </c>
       <c r="D1128" t="s">
         <v>1130</v>
@@ -20222,7 +20798,7 @@
         <v>72</v>
       </c>
       <c r="C1129">
-        <v>6180</v>
+        <v>6370</v>
       </c>
       <c r="D1129" t="s">
         <v>1131</v>
@@ -20236,7 +20812,7 @@
         <v>73</v>
       </c>
       <c r="C1130">
-        <v>6330</v>
+        <v>6480</v>
       </c>
       <c r="D1130" t="s">
         <v>1132</v>
@@ -20250,7 +20826,7 @@
         <v>74</v>
       </c>
       <c r="C1131">
-        <v>6470</v>
+        <v>6600</v>
       </c>
       <c r="D1131" t="s">
         <v>1133</v>
@@ -20264,7 +20840,7 @@
         <v>75</v>
       </c>
       <c r="C1132">
-        <v>6610</v>
+        <v>6730</v>
       </c>
       <c r="D1132" t="s">
         <v>1134</v>
@@ -20278,7 +20854,7 @@
         <v>76</v>
       </c>
       <c r="C1133">
-        <v>6740</v>
+        <v>6860</v>
       </c>
       <c r="D1133" t="s">
         <v>1135</v>
@@ -20292,7 +20868,7 @@
         <v>77</v>
       </c>
       <c r="C1134">
-        <v>6860</v>
+        <v>7000</v>
       </c>
       <c r="D1134" t="s">
         <v>1136</v>
@@ -20306,7 +20882,7 @@
         <v>78</v>
       </c>
       <c r="C1135">
-        <v>6960</v>
+        <v>7110</v>
       </c>
       <c r="D1135" t="s">
         <v>1137</v>
@@ -20320,7 +20896,7 @@
         <v>79</v>
       </c>
       <c r="C1136">
-        <v>7030</v>
+        <v>7150</v>
       </c>
       <c r="D1136" t="s">
         <v>1138</v>
@@ -20334,7 +20910,7 @@
         <v>80</v>
       </c>
       <c r="C1137">
-        <v>7070</v>
+        <v>7150</v>
       </c>
       <c r="D1137" t="s">
         <v>1139</v>
@@ -20348,7 +20924,7 @@
         <v>81</v>
       </c>
       <c r="C1138">
-        <v>7100</v>
+        <v>7150</v>
       </c>
       <c r="D1138" t="s">
         <v>1140</v>
@@ -20362,7 +20938,7 @@
         <v>82</v>
       </c>
       <c r="C1139">
-        <v>7100</v>
+        <v>7150</v>
       </c>
       <c r="D1139" t="s">
         <v>1141</v>
@@ -20376,7 +20952,7 @@
         <v>83</v>
       </c>
       <c r="C1140">
-        <v>7040</v>
+        <v>7130</v>
       </c>
       <c r="D1140" t="s">
         <v>1142</v>
@@ -20390,7 +20966,7 @@
         <v>84</v>
       </c>
       <c r="C1141">
-        <v>6940</v>
+        <v>7060</v>
       </c>
       <c r="D1141" t="s">
         <v>1143</v>
@@ -20404,7 +20980,7 @@
         <v>85</v>
       </c>
       <c r="C1142">
-        <v>6770</v>
+        <v>6940</v>
       </c>
       <c r="D1142" t="s">
         <v>1144</v>
@@ -20418,7 +20994,7 @@
         <v>86</v>
       </c>
       <c r="C1143">
-        <v>6590</v>
+        <v>6790</v>
       </c>
       <c r="D1143" t="s">
         <v>1145</v>
@@ -20432,7 +21008,7 @@
         <v>87</v>
       </c>
       <c r="C1144">
-        <v>6490</v>
+        <v>6710</v>
       </c>
       <c r="D1144" t="s">
         <v>1146</v>
@@ -20446,7 +21022,7 @@
         <v>88</v>
       </c>
       <c r="C1145">
-        <v>6400</v>
+        <v>6610</v>
       </c>
       <c r="D1145" t="s">
         <v>1147</v>
@@ -20460,7 +21036,7 @@
         <v>89</v>
       </c>
       <c r="C1146">
-        <v>6270</v>
+        <v>6480</v>
       </c>
       <c r="D1146" t="s">
         <v>1148</v>
@@ -20474,7 +21050,7 @@
         <v>90</v>
       </c>
       <c r="C1147">
-        <v>6130</v>
+        <v>6390</v>
       </c>
       <c r="D1147" t="s">
         <v>1149</v>
@@ -20488,7 +21064,7 @@
         <v>91</v>
       </c>
       <c r="C1148">
-        <v>5940</v>
+        <v>6220</v>
       </c>
       <c r="D1148" t="s">
         <v>1150</v>
@@ -20502,7 +21078,7 @@
         <v>92</v>
       </c>
       <c r="C1149">
-        <v>5860</v>
+        <v>6080</v>
       </c>
       <c r="D1149" t="s">
         <v>1151</v>
@@ -20516,7 +21092,7 @@
         <v>93</v>
       </c>
       <c r="C1150">
-        <v>5800</v>
+        <v>5930</v>
       </c>
       <c r="D1150" t="s">
         <v>1152</v>
@@ -20530,7 +21106,7 @@
         <v>94</v>
       </c>
       <c r="C1151">
-        <v>5740</v>
+        <v>5770</v>
       </c>
       <c r="D1151" t="s">
         <v>1153</v>
@@ -20558,7 +21134,7 @@
         <v>96</v>
       </c>
       <c r="C1153">
-        <v>5590</v>
+        <v>5570</v>
       </c>
       <c r="D1153" t="s">
         <v>1155</v>
@@ -20572,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="C1154">
-        <v>5590</v>
+        <v>5420</v>
       </c>
       <c r="D1154" t="s">
         <v>1156</v>
@@ -20586,7 +21162,7 @@
         <v>2</v>
       </c>
       <c r="C1155">
-        <v>5540</v>
+        <v>5360</v>
       </c>
       <c r="D1155" t="s">
         <v>1157</v>
@@ -20600,7 +21176,7 @@
         <v>3</v>
       </c>
       <c r="C1156">
-        <v>5490</v>
+        <v>5310</v>
       </c>
       <c r="D1156" t="s">
         <v>1158</v>
@@ -20614,7 +21190,7 @@
         <v>4</v>
       </c>
       <c r="C1157">
-        <v>5430</v>
+        <v>5260</v>
       </c>
       <c r="D1157" t="s">
         <v>1159</v>
@@ -20628,7 +21204,7 @@
         <v>5</v>
       </c>
       <c r="C1158">
-        <v>5390</v>
+        <v>5220</v>
       </c>
       <c r="D1158" t="s">
         <v>1160</v>
@@ -20642,7 +21218,7 @@
         <v>6</v>
       </c>
       <c r="C1159">
-        <v>5350</v>
+        <v>5180</v>
       </c>
       <c r="D1159" t="s">
         <v>1161</v>
@@ -20656,7 +21232,7 @@
         <v>7</v>
       </c>
       <c r="C1160">
-        <v>5310</v>
+        <v>5150</v>
       </c>
       <c r="D1160" t="s">
         <v>1162</v>
@@ -20670,7 +21246,7 @@
         <v>8</v>
       </c>
       <c r="C1161">
-        <v>5280</v>
+        <v>5110</v>
       </c>
       <c r="D1161" t="s">
         <v>1163</v>
@@ -20684,7 +21260,7 @@
         <v>9</v>
       </c>
       <c r="C1162">
-        <v>5250</v>
+        <v>5080</v>
       </c>
       <c r="D1162" t="s">
         <v>1164</v>
@@ -20698,7 +21274,7 @@
         <v>10</v>
       </c>
       <c r="C1163">
-        <v>5230</v>
+        <v>5060</v>
       </c>
       <c r="D1163" t="s">
         <v>1165</v>
@@ -20712,7 +21288,7 @@
         <v>11</v>
       </c>
       <c r="C1164">
-        <v>5230</v>
+        <v>5050</v>
       </c>
       <c r="D1164" t="s">
         <v>1166</v>
@@ -20726,7 +21302,7 @@
         <v>12</v>
       </c>
       <c r="C1165">
-        <v>5240</v>
+        <v>5050</v>
       </c>
       <c r="D1165" t="s">
         <v>1167</v>
@@ -20740,7 +21316,7 @@
         <v>13</v>
       </c>
       <c r="C1166">
-        <v>5250</v>
+        <v>5050</v>
       </c>
       <c r="D1166" t="s">
         <v>1168</v>
@@ -20754,7 +21330,7 @@
         <v>14</v>
       </c>
       <c r="C1167">
-        <v>5280</v>
+        <v>5060</v>
       </c>
       <c r="D1167" t="s">
         <v>1169</v>
@@ -20768,7 +21344,7 @@
         <v>15</v>
       </c>
       <c r="C1168">
-        <v>5300</v>
+        <v>5070</v>
       </c>
       <c r="D1168" t="s">
         <v>1170</v>
@@ -20782,7 +21358,7 @@
         <v>16</v>
       </c>
       <c r="C1169">
-        <v>5310</v>
+        <v>5070</v>
       </c>
       <c r="D1169" t="s">
         <v>1171</v>
@@ -20796,7 +21372,7 @@
         <v>17</v>
       </c>
       <c r="C1170">
-        <v>5320</v>
+        <v>5080</v>
       </c>
       <c r="D1170" t="s">
         <v>1172</v>
@@ -20810,7 +21386,7 @@
         <v>18</v>
       </c>
       <c r="C1171">
-        <v>5330</v>
+        <v>5100</v>
       </c>
       <c r="D1171" t="s">
         <v>1173</v>
@@ -20824,7 +21400,7 @@
         <v>19</v>
       </c>
       <c r="C1172">
-        <v>5350</v>
+        <v>5130</v>
       </c>
       <c r="D1172" t="s">
         <v>1174</v>
@@ -20838,7 +21414,7 @@
         <v>20</v>
       </c>
       <c r="C1173">
-        <v>5380</v>
+        <v>5180</v>
       </c>
       <c r="D1173" t="s">
         <v>1175</v>
@@ -20852,7 +21428,7 @@
         <v>21</v>
       </c>
       <c r="C1174">
-        <v>5430</v>
+        <v>5250</v>
       </c>
       <c r="D1174" t="s">
         <v>1176</v>
@@ -20866,7 +21442,7 @@
         <v>22</v>
       </c>
       <c r="C1175">
-        <v>5500</v>
+        <v>5350</v>
       </c>
       <c r="D1175" t="s">
         <v>1177</v>
@@ -20880,7 +21456,7 @@
         <v>23</v>
       </c>
       <c r="C1176">
-        <v>5600</v>
+        <v>5470</v>
       </c>
       <c r="D1176" t="s">
         <v>1178</v>
@@ -20894,7 +21470,7 @@
         <v>24</v>
       </c>
       <c r="C1177">
-        <v>5720</v>
+        <v>5620</v>
       </c>
       <c r="D1177" t="s">
         <v>1179</v>
@@ -20908,7 +21484,7 @@
         <v>25</v>
       </c>
       <c r="C1178">
-        <v>5860</v>
+        <v>5770</v>
       </c>
       <c r="D1178" t="s">
         <v>1180</v>
@@ -20922,7 +21498,7 @@
         <v>26</v>
       </c>
       <c r="C1179">
-        <v>6020</v>
+        <v>5940</v>
       </c>
       <c r="D1179" t="s">
         <v>1181</v>
@@ -20936,7 +21512,7 @@
         <v>27</v>
       </c>
       <c r="C1180">
-        <v>6180</v>
+        <v>6110</v>
       </c>
       <c r="D1180" t="s">
         <v>1182</v>
@@ -20950,7 +21526,7 @@
         <v>28</v>
       </c>
       <c r="C1181">
-        <v>6320</v>
+        <v>6260</v>
       </c>
       <c r="D1181" t="s">
         <v>1183</v>
@@ -20964,7 +21540,7 @@
         <v>29</v>
       </c>
       <c r="C1182">
-        <v>6450</v>
+        <v>6400</v>
       </c>
       <c r="D1182" t="s">
         <v>1184</v>
@@ -20978,7 +21554,7 @@
         <v>30</v>
       </c>
       <c r="C1183">
-        <v>6550</v>
+        <v>6520</v>
       </c>
       <c r="D1183" t="s">
         <v>1185</v>
@@ -21006,7 +21582,7 @@
         <v>32</v>
       </c>
       <c r="C1185">
-        <v>6630</v>
+        <v>6670</v>
       </c>
       <c r="D1185" t="s">
         <v>1187</v>
@@ -21020,7 +21596,7 @@
         <v>33</v>
       </c>
       <c r="C1186">
-        <v>6610</v>
+        <v>6700</v>
       </c>
       <c r="D1186" t="s">
         <v>1188</v>
@@ -21034,7 +21610,7 @@
         <v>34</v>
       </c>
       <c r="C1187">
-        <v>6550</v>
+        <v>6700</v>
       </c>
       <c r="D1187" t="s">
         <v>1189</v>
@@ -21048,7 +21624,7 @@
         <v>35</v>
       </c>
       <c r="C1188">
-        <v>6450</v>
+        <v>6690</v>
       </c>
       <c r="D1188" t="s">
         <v>1190</v>
@@ -21062,7 +21638,7 @@
         <v>36</v>
       </c>
       <c r="C1189">
-        <v>6320</v>
+        <v>6650</v>
       </c>
       <c r="D1189" t="s">
         <v>1191</v>
@@ -21076,7 +21652,7 @@
         <v>37</v>
       </c>
       <c r="C1190">
-        <v>6170</v>
+        <v>6600</v>
       </c>
       <c r="D1190" t="s">
         <v>1192</v>
@@ -21090,7 +21666,7 @@
         <v>38</v>
       </c>
       <c r="C1191">
-        <v>6000</v>
+        <v>6540</v>
       </c>
       <c r="D1191" t="s">
         <v>1193</v>
@@ -21104,7 +21680,7 @@
         <v>39</v>
       </c>
       <c r="C1192">
-        <v>5820</v>
+        <v>6480</v>
       </c>
       <c r="D1192" t="s">
         <v>1194</v>
@@ -21118,7 +21694,7 @@
         <v>40</v>
       </c>
       <c r="C1193">
-        <v>5650</v>
+        <v>6410</v>
       </c>
       <c r="D1193" t="s">
         <v>1195</v>
@@ -21132,7 +21708,7 @@
         <v>41</v>
       </c>
       <c r="C1194">
-        <v>5480</v>
+        <v>6340</v>
       </c>
       <c r="D1194" t="s">
         <v>1196</v>
@@ -21146,7 +21722,7 @@
         <v>42</v>
       </c>
       <c r="C1195">
-        <v>5310</v>
+        <v>6280</v>
       </c>
       <c r="D1195" t="s">
         <v>1197</v>
@@ -21160,7 +21736,7 @@
         <v>43</v>
       </c>
       <c r="C1196">
-        <v>5170</v>
+        <v>6220</v>
       </c>
       <c r="D1196" t="s">
         <v>1198</v>
@@ -21174,7 +21750,7 @@
         <v>44</v>
       </c>
       <c r="C1197">
-        <v>5040</v>
+        <v>6170</v>
       </c>
       <c r="D1197" t="s">
         <v>1199</v>
@@ -21188,7 +21764,7 @@
         <v>45</v>
       </c>
       <c r="C1198">
-        <v>4920</v>
+        <v>6120</v>
       </c>
       <c r="D1198" t="s">
         <v>1200</v>
@@ -21202,7 +21778,7 @@
         <v>46</v>
       </c>
       <c r="C1199">
-        <v>4830</v>
+        <v>6080</v>
       </c>
       <c r="D1199" t="s">
         <v>1201</v>
@@ -21216,7 +21792,7 @@
         <v>47</v>
       </c>
       <c r="C1200">
-        <v>4750</v>
+        <v>6040</v>
       </c>
       <c r="D1200" t="s">
         <v>1202</v>
@@ -21230,7 +21806,7 @@
         <v>48</v>
       </c>
       <c r="C1201">
-        <v>4690</v>
+        <v>6000</v>
       </c>
       <c r="D1201" t="s">
         <v>1203</v>
@@ -21244,7 +21820,7 @@
         <v>49</v>
       </c>
       <c r="C1202">
-        <v>4640</v>
+        <v>5970</v>
       </c>
       <c r="D1202" t="s">
         <v>1204</v>
@@ -21258,7 +21834,7 @@
         <v>50</v>
       </c>
       <c r="C1203">
-        <v>4620</v>
+        <v>5930</v>
       </c>
       <c r="D1203" t="s">
         <v>1205</v>
@@ -21272,7 +21848,7 @@
         <v>51</v>
       </c>
       <c r="C1204">
-        <v>4600</v>
+        <v>5910</v>
       </c>
       <c r="D1204" t="s">
         <v>1206</v>
@@ -21286,7 +21862,7 @@
         <v>52</v>
       </c>
       <c r="C1205">
-        <v>4600</v>
+        <v>5880</v>
       </c>
       <c r="D1205" t="s">
         <v>1207</v>
@@ -21300,7 +21876,7 @@
         <v>53</v>
       </c>
       <c r="C1206">
-        <v>4620</v>
+        <v>5860</v>
       </c>
       <c r="D1206" t="s">
         <v>1208</v>
@@ -21314,7 +21890,7 @@
         <v>54</v>
       </c>
       <c r="C1207">
-        <v>4640</v>
+        <v>5850</v>
       </c>
       <c r="D1207" t="s">
         <v>1209</v>
@@ -21328,7 +21904,7 @@
         <v>55</v>
       </c>
       <c r="C1208">
-        <v>4680</v>
+        <v>5840</v>
       </c>
       <c r="D1208" t="s">
         <v>1210</v>
@@ -21342,7 +21918,7 @@
         <v>56</v>
       </c>
       <c r="C1209">
-        <v>4720</v>
+        <v>5840</v>
       </c>
       <c r="D1209" t="s">
         <v>1211</v>
@@ -21356,7 +21932,7 @@
         <v>57</v>
       </c>
       <c r="C1210">
-        <v>4770</v>
+        <v>5850</v>
       </c>
       <c r="D1210" t="s">
         <v>1212</v>
@@ -21370,7 +21946,7 @@
         <v>58</v>
       </c>
       <c r="C1211">
-        <v>4830</v>
+        <v>5860</v>
       </c>
       <c r="D1211" t="s">
         <v>1213</v>
@@ -21384,7 +21960,7 @@
         <v>59</v>
       </c>
       <c r="C1212">
-        <v>4900</v>
+        <v>5880</v>
       </c>
       <c r="D1212" t="s">
         <v>1214</v>
@@ -21398,7 +21974,7 @@
         <v>60</v>
       </c>
       <c r="C1213">
-        <v>4980</v>
+        <v>5900</v>
       </c>
       <c r="D1213" t="s">
         <v>1215</v>
@@ -21412,7 +21988,7 @@
         <v>61</v>
       </c>
       <c r="C1214">
-        <v>5060</v>
+        <v>5920</v>
       </c>
       <c r="D1214" t="s">
         <v>1216</v>
@@ -21426,7 +22002,7 @@
         <v>62</v>
       </c>
       <c r="C1215">
-        <v>5160</v>
+        <v>5950</v>
       </c>
       <c r="D1215" t="s">
         <v>1217</v>
@@ -21440,7 +22016,7 @@
         <v>63</v>
       </c>
       <c r="C1216">
-        <v>5270</v>
+        <v>5970</v>
       </c>
       <c r="D1216" t="s">
         <v>1218</v>
@@ -21454,7 +22030,7 @@
         <v>64</v>
       </c>
       <c r="C1217">
-        <v>5400</v>
+        <v>6010</v>
       </c>
       <c r="D1217" t="s">
         <v>1219</v>
@@ -21468,7 +22044,7 @@
         <v>65</v>
       </c>
       <c r="C1218">
-        <v>5530</v>
+        <v>6040</v>
       </c>
       <c r="D1218" t="s">
         <v>1220</v>
@@ -21482,7 +22058,7 @@
         <v>66</v>
       </c>
       <c r="C1219">
-        <v>5670</v>
+        <v>6090</v>
       </c>
       <c r="D1219" t="s">
         <v>1221</v>
@@ -21496,7 +22072,7 @@
         <v>67</v>
       </c>
       <c r="C1220">
-        <v>5810</v>
+        <v>6150</v>
       </c>
       <c r="D1220" t="s">
         <v>1222</v>
@@ -21510,7 +22086,7 @@
         <v>68</v>
       </c>
       <c r="C1221">
-        <v>5950</v>
+        <v>6220</v>
       </c>
       <c r="D1221" t="s">
         <v>1223</v>
@@ -21524,7 +22100,7 @@
         <v>69</v>
       </c>
       <c r="C1222">
-        <v>6090</v>
+        <v>6300</v>
       </c>
       <c r="D1222" t="s">
         <v>1224</v>
@@ -21538,7 +22114,7 @@
         <v>70</v>
       </c>
       <c r="C1223">
-        <v>6210</v>
+        <v>6380</v>
       </c>
       <c r="D1223" t="s">
         <v>1225</v>
@@ -21552,7 +22128,7 @@
         <v>71</v>
       </c>
       <c r="C1224">
-        <v>6320</v>
+        <v>6480</v>
       </c>
       <c r="D1224" t="s">
         <v>1226</v>
@@ -21566,7 +22142,7 @@
         <v>72</v>
       </c>
       <c r="C1225">
-        <v>6430</v>
+        <v>6580</v>
       </c>
       <c r="D1225" t="s">
         <v>1227</v>
@@ -21580,7 +22156,7 @@
         <v>73</v>
       </c>
       <c r="C1226">
-        <v>6530</v>
+        <v>6680</v>
       </c>
       <c r="D1226" t="s">
         <v>1228</v>
@@ -21594,7 +22170,7 @@
         <v>74</v>
       </c>
       <c r="C1227">
-        <v>6640</v>
+        <v>6800</v>
       </c>
       <c r="D1227" t="s">
         <v>1229</v>
@@ -21608,7 +22184,7 @@
         <v>75</v>
       </c>
       <c r="C1228">
-        <v>6760</v>
+        <v>6910</v>
       </c>
       <c r="D1228" t="s">
         <v>1230</v>
@@ -21622,7 +22198,7 @@
         <v>76</v>
       </c>
       <c r="C1229">
-        <v>6890</v>
+        <v>7030</v>
       </c>
       <c r="D1229" t="s">
         <v>1231</v>
@@ -21636,7 +22212,7 @@
         <v>77</v>
       </c>
       <c r="C1230">
-        <v>7020</v>
+        <v>7140</v>
       </c>
       <c r="D1230" t="s">
         <v>1232</v>
@@ -21650,7 +22226,7 @@
         <v>78</v>
       </c>
       <c r="C1231">
-        <v>7150</v>
+        <v>7220</v>
       </c>
       <c r="D1231" t="s">
         <v>1233</v>
@@ -21678,7 +22254,7 @@
         <v>80</v>
       </c>
       <c r="C1233">
-        <v>7330</v>
+        <v>7250</v>
       </c>
       <c r="D1233" t="s">
         <v>1235</v>
@@ -21692,7 +22268,7 @@
         <v>81</v>
       </c>
       <c r="C1234">
-        <v>7370</v>
+        <v>7250</v>
       </c>
       <c r="D1234" t="s">
         <v>1236</v>
@@ -21706,7 +22282,7 @@
         <v>82</v>
       </c>
       <c r="C1235">
-        <v>7380</v>
+        <v>7250</v>
       </c>
       <c r="D1235" t="s">
         <v>1237</v>
@@ -21720,7 +22296,7 @@
         <v>83</v>
       </c>
       <c r="C1236">
-        <v>7320</v>
+        <v>7240</v>
       </c>
       <c r="D1236" t="s">
         <v>1238</v>
@@ -21734,7 +22310,7 @@
         <v>84</v>
       </c>
       <c r="C1237">
-        <v>7230</v>
+        <v>7170</v>
       </c>
       <c r="D1237" t="s">
         <v>1239</v>
@@ -21748,7 +22324,7 @@
         <v>85</v>
       </c>
       <c r="C1238">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="D1238" t="s">
         <v>1240</v>
@@ -21762,7 +22338,7 @@
         <v>86</v>
       </c>
       <c r="C1239">
-        <v>6860</v>
+        <v>6900</v>
       </c>
       <c r="D1239" t="s">
         <v>1241</v>
@@ -21776,7 +22352,7 @@
         <v>87</v>
       </c>
       <c r="C1240">
-        <v>6730</v>
+        <v>6810</v>
       </c>
       <c r="D1240" t="s">
         <v>1242</v>
@@ -21790,7 +22366,7 @@
         <v>88</v>
       </c>
       <c r="C1241">
-        <v>6620</v>
+        <v>6720</v>
       </c>
       <c r="D1241" t="s">
         <v>1243</v>
@@ -21804,7 +22380,7 @@
         <v>89</v>
       </c>
       <c r="C1242">
-        <v>6470</v>
+        <v>6590</v>
       </c>
       <c r="D1242" t="s">
         <v>1244</v>
@@ -21818,7 +22394,7 @@
         <v>90</v>
       </c>
       <c r="C1243">
-        <v>6350</v>
+        <v>6490</v>
       </c>
       <c r="D1243" t="s">
         <v>1245</v>
@@ -21832,7 +22408,7 @@
         <v>91</v>
       </c>
       <c r="C1244">
-        <v>6160</v>
+        <v>6320</v>
       </c>
       <c r="D1244" t="s">
         <v>1246</v>
@@ -21846,7 +22422,7 @@
         <v>92</v>
       </c>
       <c r="C1245">
-        <v>6010</v>
+        <v>6180</v>
       </c>
       <c r="D1245" t="s">
         <v>1247</v>
@@ -21860,7 +22436,7 @@
         <v>93</v>
       </c>
       <c r="C1246">
-        <v>5880</v>
+        <v>6030</v>
       </c>
       <c r="D1246" t="s">
         <v>1248</v>
@@ -21874,7 +22450,7 @@
         <v>94</v>
       </c>
       <c r="C1247">
-        <v>5720</v>
+        <v>5870</v>
       </c>
       <c r="D1247" t="s">
         <v>1249</v>
@@ -21888,7 +22464,7 @@
         <v>95</v>
       </c>
       <c r="C1248">
-        <v>5640</v>
+        <v>5780</v>
       </c>
       <c r="D1248" t="s">
         <v>1250</v>
@@ -21902,7 +22478,7 @@
         <v>96</v>
       </c>
       <c r="C1249">
-        <v>5580</v>
+        <v>5670</v>
       </c>
       <c r="D1249" t="s">
         <v>1251</v>
@@ -21916,7 +22492,7 @@
         <v>1</v>
       </c>
       <c r="C1250">
-        <v>5510</v>
+        <v>5450</v>
       </c>
       <c r="D1250" t="s">
         <v>1252</v>
@@ -21930,7 +22506,7 @@
         <v>2</v>
       </c>
       <c r="C1251">
-        <v>5470</v>
+        <v>5390</v>
       </c>
       <c r="D1251" t="s">
         <v>1253</v>
@@ -21944,7 +22520,7 @@
         <v>3</v>
       </c>
       <c r="C1252">
-        <v>5410</v>
+        <v>5340</v>
       </c>
       <c r="D1252" t="s">
         <v>1254</v>
@@ -21958,7 +22534,7 @@
         <v>4</v>
       </c>
       <c r="C1253">
-        <v>5340</v>
+        <v>5290</v>
       </c>
       <c r="D1253" t="s">
         <v>1255</v>
@@ -21972,7 +22548,7 @@
         <v>5</v>
       </c>
       <c r="C1254">
-        <v>5290</v>
+        <v>5250</v>
       </c>
       <c r="D1254" t="s">
         <v>1256</v>
@@ -21986,7 +22562,7 @@
         <v>6</v>
       </c>
       <c r="C1255">
-        <v>5250</v>
+        <v>5210</v>
       </c>
       <c r="D1255" t="s">
         <v>1257</v>
@@ -22000,7 +22576,7 @@
         <v>7</v>
       </c>
       <c r="C1256">
-        <v>5220</v>
+        <v>5170</v>
       </c>
       <c r="D1256" t="s">
         <v>1258</v>
@@ -22014,7 +22590,7 @@
         <v>8</v>
       </c>
       <c r="C1257">
-        <v>5200</v>
+        <v>5140</v>
       </c>
       <c r="D1257" t="s">
         <v>1259</v>
@@ -22028,7 +22604,7 @@
         <v>9</v>
       </c>
       <c r="C1258">
-        <v>5180</v>
+        <v>5110</v>
       </c>
       <c r="D1258" t="s">
         <v>1260</v>
@@ -22042,7 +22618,7 @@
         <v>10</v>
       </c>
       <c r="C1259">
-        <v>5170</v>
+        <v>5090</v>
       </c>
       <c r="D1259" t="s">
         <v>1261</v>
@@ -22056,7 +22632,7 @@
         <v>11</v>
       </c>
       <c r="C1260">
-        <v>5160</v>
+        <v>5080</v>
       </c>
       <c r="D1260" t="s">
         <v>1262</v>
@@ -22070,7 +22646,7 @@
         <v>12</v>
       </c>
       <c r="C1261">
-        <v>5170</v>
+        <v>5080</v>
       </c>
       <c r="D1261" t="s">
         <v>1263</v>
@@ -22084,7 +22660,7 @@
         <v>13</v>
       </c>
       <c r="C1262">
-        <v>5170</v>
+        <v>5080</v>
       </c>
       <c r="D1262" t="s">
         <v>1264</v>
@@ -22098,7 +22674,7 @@
         <v>14</v>
       </c>
       <c r="C1263">
-        <v>5180</v>
+        <v>5090</v>
       </c>
       <c r="D1263" t="s">
         <v>1265</v>
@@ -22112,7 +22688,7 @@
         <v>15</v>
       </c>
       <c r="C1264">
-        <v>5190</v>
+        <v>5090</v>
       </c>
       <c r="D1264" t="s">
         <v>1266</v>
@@ -22126,7 +22702,7 @@
         <v>16</v>
       </c>
       <c r="C1265">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="D1265" t="s">
         <v>1267</v>
@@ -22140,7 +22716,7 @@
         <v>17</v>
       </c>
       <c r="C1266">
-        <v>5210</v>
+        <v>5110</v>
       </c>
       <c r="D1266" t="s">
         <v>1268</v>
@@ -22154,7 +22730,7 @@
         <v>18</v>
       </c>
       <c r="C1267">
-        <v>5220</v>
+        <v>5130</v>
       </c>
       <c r="D1267" t="s">
         <v>1269</v>
@@ -22168,7 +22744,7 @@
         <v>19</v>
       </c>
       <c r="C1268">
-        <v>5230</v>
+        <v>5160</v>
       </c>
       <c r="D1268" t="s">
         <v>1270</v>
@@ -22182,7 +22758,7 @@
         <v>20</v>
       </c>
       <c r="C1269">
-        <v>5250</v>
+        <v>5210</v>
       </c>
       <c r="D1269" t="s">
         <v>1271</v>
@@ -22196,7 +22772,7 @@
         <v>21</v>
       </c>
       <c r="C1270">
-        <v>5280</v>
+        <v>5290</v>
       </c>
       <c r="D1270" t="s">
         <v>1272</v>
@@ -22210,7 +22786,7 @@
         <v>22</v>
       </c>
       <c r="C1271">
-        <v>5340</v>
+        <v>5390</v>
       </c>
       <c r="D1271" t="s">
         <v>1273</v>
@@ -22224,7 +22800,7 @@
         <v>23</v>
       </c>
       <c r="C1272">
-        <v>5410</v>
+        <v>5510</v>
       </c>
       <c r="D1272" t="s">
         <v>1274</v>
@@ -22238,7 +22814,7 @@
         <v>24</v>
       </c>
       <c r="C1273">
-        <v>5520</v>
+        <v>5650</v>
       </c>
       <c r="D1273" t="s">
         <v>1275</v>
@@ -22252,7 +22828,7 @@
         <v>25</v>
       </c>
       <c r="C1274">
-        <v>5650</v>
+        <v>5800</v>
       </c>
       <c r="D1274" t="s">
         <v>1276</v>
@@ -22266,7 +22842,7 @@
         <v>26</v>
       </c>
       <c r="C1275">
-        <v>5790</v>
+        <v>5960</v>
       </c>
       <c r="D1275" t="s">
         <v>1277</v>
@@ -22280,7 +22856,7 @@
         <v>27</v>
       </c>
       <c r="C1276">
-        <v>5960</v>
+        <v>6120</v>
       </c>
       <c r="D1276" t="s">
         <v>1278</v>
@@ -22294,7 +22870,7 @@
         <v>28</v>
       </c>
       <c r="C1277">
-        <v>6130</v>
+        <v>6260</v>
       </c>
       <c r="D1277" t="s">
         <v>1279</v>
@@ -22308,7 +22884,7 @@
         <v>29</v>
       </c>
       <c r="C1278">
-        <v>6290</v>
+        <v>6390</v>
       </c>
       <c r="D1278" t="s">
         <v>1280</v>
@@ -22322,7 +22898,7 @@
         <v>30</v>
       </c>
       <c r="C1279">
-        <v>6440</v>
+        <v>6490</v>
       </c>
       <c r="D1279" t="s">
         <v>1281</v>
@@ -22350,7 +22926,7 @@
         <v>32</v>
       </c>
       <c r="C1281">
-        <v>6660</v>
+        <v>6610</v>
       </c>
       <c r="D1281" t="s">
         <v>1283</v>
@@ -22364,7 +22940,7 @@
         <v>33</v>
       </c>
       <c r="C1282">
-        <v>6720</v>
+        <v>6620</v>
       </c>
       <c r="D1282" t="s">
         <v>1284</v>
@@ -22378,7 +22954,7 @@
         <v>34</v>
       </c>
       <c r="C1283">
-        <v>6740</v>
+        <v>6600</v>
       </c>
       <c r="D1283" t="s">
         <v>1285</v>
@@ -22392,7 +22968,7 @@
         <v>35</v>
       </c>
       <c r="C1284">
-        <v>6730</v>
+        <v>6560</v>
       </c>
       <c r="D1284" t="s">
         <v>1286</v>
@@ -22406,7 +22982,7 @@
         <v>36</v>
       </c>
       <c r="C1285">
-        <v>6690</v>
+        <v>6490</v>
       </c>
       <c r="D1285" t="s">
         <v>1287</v>
@@ -22420,7 +22996,7 @@
         <v>37</v>
       </c>
       <c r="C1286">
-        <v>6630</v>
+        <v>6410</v>
       </c>
       <c r="D1286" t="s">
         <v>1288</v>
@@ -22434,7 +23010,7 @@
         <v>38</v>
       </c>
       <c r="C1287">
-        <v>6560</v>
+        <v>6320</v>
       </c>
       <c r="D1287" t="s">
         <v>1289</v>
@@ -22448,7 +23024,7 @@
         <v>39</v>
       </c>
       <c r="C1288">
-        <v>6480</v>
+        <v>6220</v>
       </c>
       <c r="D1288" t="s">
         <v>1290</v>
@@ -22462,7 +23038,7 @@
         <v>40</v>
       </c>
       <c r="C1289">
-        <v>6390</v>
+        <v>6120</v>
       </c>
       <c r="D1289" t="s">
         <v>1291</v>
@@ -22476,7 +23052,7 @@
         <v>41</v>
       </c>
       <c r="C1290">
-        <v>6320</v>
+        <v>6020</v>
       </c>
       <c r="D1290" t="s">
         <v>1292</v>
@@ -22490,7 +23066,7 @@
         <v>42</v>
       </c>
       <c r="C1291">
-        <v>6250</v>
+        <v>5930</v>
       </c>
       <c r="D1291" t="s">
         <v>1293</v>
@@ -22504,7 +23080,7 @@
         <v>43</v>
       </c>
       <c r="C1292">
-        <v>6190</v>
+        <v>5850</v>
       </c>
       <c r="D1292" t="s">
         <v>1294</v>
@@ -22518,7 +23094,7 @@
         <v>44</v>
       </c>
       <c r="C1293">
-        <v>6140</v>
+        <v>5770</v>
       </c>
       <c r="D1293" t="s">
         <v>1295</v>
@@ -22532,7 +23108,7 @@
         <v>45</v>
       </c>
       <c r="C1294">
-        <v>6090</v>
+        <v>5700</v>
       </c>
       <c r="D1294" t="s">
         <v>1296</v>
@@ -22546,7 +23122,7 @@
         <v>46</v>
       </c>
       <c r="C1295">
-        <v>6050</v>
+        <v>5650</v>
       </c>
       <c r="D1295" t="s">
         <v>1297</v>
@@ -22560,7 +23136,7 @@
         <v>47</v>
       </c>
       <c r="C1296">
-        <v>6010</v>
+        <v>5590</v>
       </c>
       <c r="D1296" t="s">
         <v>1298</v>
@@ -22574,7 +23150,7 @@
         <v>48</v>
       </c>
       <c r="C1297">
-        <v>5970</v>
+        <v>5550</v>
       </c>
       <c r="D1297" t="s">
         <v>1299</v>
@@ -22588,7 +23164,7 @@
         <v>49</v>
       </c>
       <c r="C1298">
-        <v>5930</v>
+        <v>5510</v>
       </c>
       <c r="D1298" t="s">
         <v>1300</v>
@@ -22602,7 +23178,7 @@
         <v>50</v>
       </c>
       <c r="C1299">
-        <v>5890</v>
+        <v>5480</v>
       </c>
       <c r="D1299" t="s">
         <v>1301</v>
@@ -22616,7 +23192,7 @@
         <v>51</v>
       </c>
       <c r="C1300">
-        <v>5860</v>
+        <v>5450</v>
       </c>
       <c r="D1300" t="s">
         <v>1302</v>
@@ -22630,7 +23206,7 @@
         <v>52</v>
       </c>
       <c r="C1301">
-        <v>5830</v>
+        <v>5430</v>
       </c>
       <c r="D1301" t="s">
         <v>1303</v>
@@ -22644,7 +23220,7 @@
         <v>53</v>
       </c>
       <c r="C1302">
-        <v>5810</v>
+        <v>5410</v>
       </c>
       <c r="D1302" t="s">
         <v>1304</v>
@@ -22658,7 +23234,7 @@
         <v>54</v>
       </c>
       <c r="C1303">
-        <v>5800</v>
+        <v>5400</v>
       </c>
       <c r="D1303" t="s">
         <v>1305</v>
@@ -22672,7 +23248,7 @@
         <v>55</v>
       </c>
       <c r="C1304">
-        <v>5810</v>
+        <v>5390</v>
       </c>
       <c r="D1304" t="s">
         <v>1306</v>
@@ -22686,7 +23262,7 @@
         <v>56</v>
       </c>
       <c r="C1305">
-        <v>5820</v>
+        <v>5390</v>
       </c>
       <c r="D1305" t="s">
         <v>1307</v>
@@ -22700,7 +23276,7 @@
         <v>57</v>
       </c>
       <c r="C1306">
-        <v>5830</v>
+        <v>5400</v>
       </c>
       <c r="D1306" t="s">
         <v>1308</v>
@@ -22714,7 +23290,7 @@
         <v>58</v>
       </c>
       <c r="C1307">
-        <v>5840</v>
+        <v>5410</v>
       </c>
       <c r="D1307" t="s">
         <v>1309</v>
@@ -22728,7 +23304,7 @@
         <v>59</v>
       </c>
       <c r="C1308">
-        <v>5860</v>
+        <v>5430</v>
       </c>
       <c r="D1308" t="s">
         <v>1310</v>
@@ -22742,7 +23318,7 @@
         <v>60</v>
       </c>
       <c r="C1309">
-        <v>5870</v>
+        <v>5450</v>
       </c>
       <c r="D1309" t="s">
         <v>1311</v>
@@ -22756,7 +23332,7 @@
         <v>61</v>
       </c>
       <c r="C1310">
-        <v>5890</v>
+        <v>5470</v>
       </c>
       <c r="D1310" t="s">
         <v>1312</v>
@@ -22770,7 +23346,7 @@
         <v>62</v>
       </c>
       <c r="C1311">
-        <v>5900</v>
+        <v>5510</v>
       </c>
       <c r="D1311" t="s">
         <v>1313</v>
@@ -22784,7 +23360,7 @@
         <v>63</v>
       </c>
       <c r="C1312">
-        <v>5930</v>
+        <v>5560</v>
       </c>
       <c r="D1312" t="s">
         <v>1314</v>
@@ -22798,7 +23374,7 @@
         <v>64</v>
       </c>
       <c r="C1313">
-        <v>5970</v>
+        <v>5620</v>
       </c>
       <c r="D1313" t="s">
         <v>1315</v>
@@ -22812,7 +23388,7 @@
         <v>65</v>
       </c>
       <c r="C1314">
-        <v>6020</v>
+        <v>5700</v>
       </c>
       <c r="D1314" t="s">
         <v>1316</v>
@@ -22826,7 +23402,7 @@
         <v>66</v>
       </c>
       <c r="C1315">
-        <v>6090</v>
+        <v>5800</v>
       </c>
       <c r="D1315" t="s">
         <v>1317</v>
@@ -22840,7 +23416,7 @@
         <v>67</v>
       </c>
       <c r="C1316">
-        <v>6180</v>
+        <v>5910</v>
       </c>
       <c r="D1316" t="s">
         <v>1318</v>
@@ -22854,7 +23430,7 @@
         <v>68</v>
       </c>
       <c r="C1317">
-        <v>6270</v>
+        <v>6030</v>
       </c>
       <c r="D1317" t="s">
         <v>1319</v>
@@ -22868,7 +23444,7 @@
         <v>69</v>
       </c>
       <c r="C1318">
-        <v>6360</v>
+        <v>6140</v>
       </c>
       <c r="D1318" t="s">
         <v>1320</v>
@@ -22882,7 +23458,7 @@
         <v>70</v>
       </c>
       <c r="C1319">
-        <v>6440</v>
+        <v>6260</v>
       </c>
       <c r="D1319" t="s">
         <v>1321</v>
@@ -22896,7 +23472,7 @@
         <v>71</v>
       </c>
       <c r="C1320">
-        <v>6520</v>
+        <v>6370</v>
       </c>
       <c r="D1320" t="s">
         <v>1322</v>
@@ -22910,7 +23486,7 @@
         <v>72</v>
       </c>
       <c r="C1321">
-        <v>6590</v>
+        <v>6470</v>
       </c>
       <c r="D1321" t="s">
         <v>1323</v>
@@ -22924,7 +23500,7 @@
         <v>73</v>
       </c>
       <c r="C1322">
-        <v>6670</v>
+        <v>6570</v>
       </c>
       <c r="D1322" t="s">
         <v>1324</v>
@@ -22938,7 +23514,7 @@
         <v>74</v>
       </c>
       <c r="C1323">
-        <v>6770</v>
+        <v>6690</v>
       </c>
       <c r="D1323" t="s">
         <v>1325</v>
@@ -22952,7 +23528,7 @@
         <v>75</v>
       </c>
       <c r="C1324">
-        <v>6880</v>
+        <v>6810</v>
       </c>
       <c r="D1324" t="s">
         <v>1326</v>
@@ -22966,7 +23542,7 @@
         <v>76</v>
       </c>
       <c r="C1325">
-        <v>7010</v>
+        <v>6950</v>
       </c>
       <c r="D1325" t="s">
         <v>1327</v>
@@ -22980,7 +23556,7 @@
         <v>77</v>
       </c>
       <c r="C1326">
-        <v>7150</v>
+        <v>7080</v>
       </c>
       <c r="D1326" t="s">
         <v>1328</v>
@@ -22994,7 +23570,7 @@
         <v>78</v>
       </c>
       <c r="C1327">
-        <v>7270</v>
+        <v>7200</v>
       </c>
       <c r="D1327" t="s">
         <v>1329</v>
@@ -23008,7 +23584,7 @@
         <v>79</v>
       </c>
       <c r="C1328">
-        <v>7360</v>
+        <v>7290</v>
       </c>
       <c r="D1328" t="s">
         <v>1330</v>
@@ -23022,7 +23598,7 @@
         <v>80</v>
       </c>
       <c r="C1329">
-        <v>7390</v>
+        <v>7320</v>
       </c>
       <c r="D1329" t="s">
         <v>1331</v>
@@ -23036,7 +23612,7 @@
         <v>81</v>
       </c>
       <c r="C1330">
-        <v>7390</v>
+        <v>7320</v>
       </c>
       <c r="D1330" t="s">
         <v>1332</v>
@@ -23050,7 +23626,7 @@
         <v>82</v>
       </c>
       <c r="C1331">
-        <v>7370</v>
+        <v>7300</v>
       </c>
       <c r="D1331" t="s">
         <v>1333</v>
@@ -23064,7 +23640,7 @@
         <v>83</v>
       </c>
       <c r="C1332">
-        <v>7300</v>
+        <v>7230</v>
       </c>
       <c r="D1332" t="s">
         <v>1334</v>
@@ -23078,7 +23654,7 @@
         <v>84</v>
       </c>
       <c r="C1333">
-        <v>7230</v>
+        <v>7160</v>
       </c>
       <c r="D1333" t="s">
         <v>1335</v>
@@ -23092,7 +23668,7 @@
         <v>85</v>
       </c>
       <c r="C1334">
-        <v>7110</v>
+        <v>7040</v>
       </c>
       <c r="D1334" t="s">
         <v>1336</v>
@@ -23106,7 +23682,7 @@
         <v>86</v>
       </c>
       <c r="C1335">
-        <v>6970</v>
+        <v>6900</v>
       </c>
       <c r="D1335" t="s">
         <v>1337</v>
@@ -23120,7 +23696,7 @@
         <v>87</v>
       </c>
       <c r="C1336">
-        <v>6880</v>
+        <v>6810</v>
       </c>
       <c r="D1336" t="s">
         <v>1338</v>
@@ -23134,7 +23710,7 @@
         <v>88</v>
       </c>
       <c r="C1337">
-        <v>6770</v>
+        <v>6700</v>
       </c>
       <c r="D1337" t="s">
         <v>1339</v>
@@ -23148,7 +23724,7 @@
         <v>89</v>
       </c>
       <c r="C1338">
-        <v>6620</v>
+        <v>6560</v>
       </c>
       <c r="D1338" t="s">
         <v>1340</v>
@@ -23162,7 +23738,7 @@
         <v>90</v>
       </c>
       <c r="C1339">
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="D1339" t="s">
         <v>1341</v>
@@ -23176,7 +23752,7 @@
         <v>91</v>
       </c>
       <c r="C1340">
-        <v>6340</v>
+        <v>6300</v>
       </c>
       <c r="D1340" t="s">
         <v>1342</v>
@@ -23190,7 +23766,7 @@
         <v>92</v>
       </c>
       <c r="C1341">
-        <v>6200</v>
+        <v>6150</v>
       </c>
       <c r="D1341" t="s">
         <v>1343</v>
@@ -23204,7 +23780,7 @@
         <v>93</v>
       </c>
       <c r="C1342">
-        <v>6050</v>
+        <v>5980</v>
       </c>
       <c r="D1342" t="s">
         <v>1344</v>
@@ -23218,7 +23794,7 @@
         <v>94</v>
       </c>
       <c r="C1343">
-        <v>5890</v>
+        <v>5820</v>
       </c>
       <c r="D1343" t="s">
         <v>1345</v>
@@ -23232,7 +23808,7 @@
         <v>95</v>
       </c>
       <c r="C1344">
-        <v>5800</v>
+        <v>5730</v>
       </c>
       <c r="D1344" t="s">
         <v>1346</v>
@@ -23246,10 +23822,2698 @@
         <v>96</v>
       </c>
       <c r="C1345">
-        <v>5690</v>
+        <v>5620</v>
       </c>
       <c r="D1345" t="s">
         <v>1347</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4">
+      <c r="A1346" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1346">
+        <v>1</v>
+      </c>
+      <c r="C1346">
+        <v>5470</v>
+      </c>
+      <c r="D1346" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4">
+      <c r="A1347" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1347">
+        <v>2</v>
+      </c>
+      <c r="C1347">
+        <v>5400</v>
+      </c>
+      <c r="D1347" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4">
+      <c r="A1348" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1348">
+        <v>3</v>
+      </c>
+      <c r="C1348">
+        <v>5360</v>
+      </c>
+      <c r="D1348" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4">
+      <c r="A1349" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1349">
+        <v>4</v>
+      </c>
+      <c r="C1349">
+        <v>5310</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4">
+      <c r="A1350" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1350">
+        <v>5</v>
+      </c>
+      <c r="C1350">
+        <v>5270</v>
+      </c>
+      <c r="D1350" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4">
+      <c r="A1351" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1351">
+        <v>6</v>
+      </c>
+      <c r="C1351">
+        <v>5230</v>
+      </c>
+      <c r="D1351" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4">
+      <c r="A1352" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1352">
+        <v>7</v>
+      </c>
+      <c r="C1352">
+        <v>5190</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4">
+      <c r="A1353" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1353">
+        <v>8</v>
+      </c>
+      <c r="C1353">
+        <v>5160</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4">
+      <c r="A1354" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1354">
+        <v>9</v>
+      </c>
+      <c r="C1354">
+        <v>5130</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4">
+      <c r="A1355" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1355">
+        <v>10</v>
+      </c>
+      <c r="C1355">
+        <v>5110</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4">
+      <c r="A1356" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1356">
+        <v>11</v>
+      </c>
+      <c r="C1356">
+        <v>5100</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4">
+      <c r="A1357" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1357">
+        <v>12</v>
+      </c>
+      <c r="C1357">
+        <v>5100</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4">
+      <c r="A1358" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1358">
+        <v>13</v>
+      </c>
+      <c r="C1358">
+        <v>5100</v>
+      </c>
+      <c r="D1358" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4">
+      <c r="A1359" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1359">
+        <v>14</v>
+      </c>
+      <c r="C1359">
+        <v>5110</v>
+      </c>
+      <c r="D1359" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4">
+      <c r="A1360" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1360">
+        <v>15</v>
+      </c>
+      <c r="C1360">
+        <v>5110</v>
+      </c>
+      <c r="D1360" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4">
+      <c r="A1361" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1361">
+        <v>16</v>
+      </c>
+      <c r="C1361">
+        <v>5120</v>
+      </c>
+      <c r="D1361" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4">
+      <c r="A1362" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1362">
+        <v>17</v>
+      </c>
+      <c r="C1362">
+        <v>5130</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4">
+      <c r="A1363" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1363">
+        <v>18</v>
+      </c>
+      <c r="C1363">
+        <v>5150</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4">
+      <c r="A1364" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1364">
+        <v>19</v>
+      </c>
+      <c r="C1364">
+        <v>5180</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4">
+      <c r="A1365" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1365">
+        <v>20</v>
+      </c>
+      <c r="C1365">
+        <v>5240</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4">
+      <c r="A1366" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1366">
+        <v>21</v>
+      </c>
+      <c r="C1366">
+        <v>5310</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4">
+      <c r="A1367" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1367">
+        <v>22</v>
+      </c>
+      <c r="C1367">
+        <v>5410</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4">
+      <c r="A1368" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1368">
+        <v>23</v>
+      </c>
+      <c r="C1368">
+        <v>5530</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4">
+      <c r="A1369" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1369">
+        <v>24</v>
+      </c>
+      <c r="C1369">
+        <v>5660</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4">
+      <c r="A1370" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1370">
+        <v>25</v>
+      </c>
+      <c r="C1370">
+        <v>5820</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4">
+      <c r="A1371" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1371">
+        <v>26</v>
+      </c>
+      <c r="C1371">
+        <v>5980</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4">
+      <c r="A1372" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1372">
+        <v>27</v>
+      </c>
+      <c r="C1372">
+        <v>6140</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4">
+      <c r="A1373" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1373">
+        <v>28</v>
+      </c>
+      <c r="C1373">
+        <v>6280</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4">
+      <c r="A1374" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1374">
+        <v>29</v>
+      </c>
+      <c r="C1374">
+        <v>6410</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4">
+      <c r="A1375" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1375">
+        <v>30</v>
+      </c>
+      <c r="C1375">
+        <v>6520</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4">
+      <c r="A1376" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1376">
+        <v>31</v>
+      </c>
+      <c r="C1376">
+        <v>6590</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4">
+      <c r="A1377" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1377">
+        <v>32</v>
+      </c>
+      <c r="C1377">
+        <v>6620</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4">
+      <c r="A1378" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1378">
+        <v>33</v>
+      </c>
+      <c r="C1378">
+        <v>6630</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4">
+      <c r="A1379" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1379">
+        <v>34</v>
+      </c>
+      <c r="C1379">
+        <v>6600</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4">
+      <c r="A1380" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1380">
+        <v>35</v>
+      </c>
+      <c r="C1380">
+        <v>6540</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4">
+      <c r="A1381" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1381">
+        <v>36</v>
+      </c>
+      <c r="C1381">
+        <v>6450</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4">
+      <c r="A1382" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1382">
+        <v>37</v>
+      </c>
+      <c r="C1382">
+        <v>6350</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4">
+      <c r="A1383" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1383">
+        <v>38</v>
+      </c>
+      <c r="C1383">
+        <v>6240</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4">
+      <c r="A1384" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1384">
+        <v>39</v>
+      </c>
+      <c r="C1384">
+        <v>6130</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4">
+      <c r="A1385" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1385">
+        <v>40</v>
+      </c>
+      <c r="C1385">
+        <v>6020</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4">
+      <c r="A1386" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1386">
+        <v>41</v>
+      </c>
+      <c r="C1386">
+        <v>5920</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4">
+      <c r="A1387" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1387">
+        <v>42</v>
+      </c>
+      <c r="C1387">
+        <v>5820</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4">
+      <c r="A1388" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1388">
+        <v>43</v>
+      </c>
+      <c r="C1388">
+        <v>5740</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4">
+      <c r="A1389" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1389">
+        <v>44</v>
+      </c>
+      <c r="C1389">
+        <v>5670</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4">
+      <c r="A1390" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1390">
+        <v>45</v>
+      </c>
+      <c r="C1390">
+        <v>5600</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4">
+      <c r="A1391" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1391">
+        <v>46</v>
+      </c>
+      <c r="C1391">
+        <v>5550</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4">
+      <c r="A1392" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1392">
+        <v>47</v>
+      </c>
+      <c r="C1392">
+        <v>5500</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4">
+      <c r="A1393" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1393">
+        <v>48</v>
+      </c>
+      <c r="C1393">
+        <v>5450</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4">
+      <c r="A1394" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1394">
+        <v>49</v>
+      </c>
+      <c r="C1394">
+        <v>5410</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4">
+      <c r="A1395" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1395">
+        <v>50</v>
+      </c>
+      <c r="C1395">
+        <v>5380</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4">
+      <c r="A1396" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1396">
+        <v>51</v>
+      </c>
+      <c r="C1396">
+        <v>5350</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4">
+      <c r="A1397" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1397">
+        <v>52</v>
+      </c>
+      <c r="C1397">
+        <v>5330</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4">
+      <c r="A1398" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1398">
+        <v>53</v>
+      </c>
+      <c r="C1398">
+        <v>5310</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4">
+      <c r="A1399" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1399">
+        <v>54</v>
+      </c>
+      <c r="C1399">
+        <v>5300</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4">
+      <c r="A1400" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1400">
+        <v>55</v>
+      </c>
+      <c r="C1400">
+        <v>5290</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4">
+      <c r="A1401" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1401">
+        <v>56</v>
+      </c>
+      <c r="C1401">
+        <v>5300</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4">
+      <c r="A1402" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1402">
+        <v>57</v>
+      </c>
+      <c r="C1402">
+        <v>5300</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4">
+      <c r="A1403" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1403">
+        <v>58</v>
+      </c>
+      <c r="C1403">
+        <v>5310</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4">
+      <c r="A1404" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1404">
+        <v>59</v>
+      </c>
+      <c r="C1404">
+        <v>5330</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4">
+      <c r="A1405" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1405">
+        <v>60</v>
+      </c>
+      <c r="C1405">
+        <v>5350</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4">
+      <c r="A1406" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1406">
+        <v>61</v>
+      </c>
+      <c r="C1406">
+        <v>5370</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4">
+      <c r="A1407" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1407">
+        <v>62</v>
+      </c>
+      <c r="C1407">
+        <v>5410</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4">
+      <c r="A1408" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1408">
+        <v>63</v>
+      </c>
+      <c r="C1408">
+        <v>5460</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4">
+      <c r="A1409" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1409">
+        <v>64</v>
+      </c>
+      <c r="C1409">
+        <v>5540</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4">
+      <c r="A1410" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1410">
+        <v>65</v>
+      </c>
+      <c r="C1410">
+        <v>5630</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4">
+      <c r="A1411" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1411">
+        <v>66</v>
+      </c>
+      <c r="C1411">
+        <v>5740</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4">
+      <c r="A1412" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1412">
+        <v>67</v>
+      </c>
+      <c r="C1412">
+        <v>5870</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4">
+      <c r="A1413" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1413">
+        <v>68</v>
+      </c>
+      <c r="C1413">
+        <v>6000</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4">
+      <c r="A1414" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1414">
+        <v>69</v>
+      </c>
+      <c r="C1414">
+        <v>6130</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4">
+      <c r="A1415" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1415">
+        <v>70</v>
+      </c>
+      <c r="C1415">
+        <v>6260</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4">
+      <c r="A1416" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1416">
+        <v>71</v>
+      </c>
+      <c r="C1416">
+        <v>6370</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4">
+      <c r="A1417" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1417">
+        <v>72</v>
+      </c>
+      <c r="C1417">
+        <v>6480</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4">
+      <c r="A1418" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1418">
+        <v>73</v>
+      </c>
+      <c r="C1418">
+        <v>6590</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4">
+      <c r="A1419" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1419">
+        <v>74</v>
+      </c>
+      <c r="C1419">
+        <v>6700</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4">
+      <c r="A1420" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1420">
+        <v>75</v>
+      </c>
+      <c r="C1420">
+        <v>6830</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4">
+      <c r="A1421" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1421">
+        <v>76</v>
+      </c>
+      <c r="C1421">
+        <v>6970</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4">
+      <c r="A1422" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1422">
+        <v>77</v>
+      </c>
+      <c r="C1422">
+        <v>7100</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4">
+      <c r="A1423" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1423">
+        <v>78</v>
+      </c>
+      <c r="C1423">
+        <v>7220</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4">
+      <c r="A1424" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1424">
+        <v>79</v>
+      </c>
+      <c r="C1424">
+        <v>7310</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4">
+      <c r="A1425" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1425">
+        <v>80</v>
+      </c>
+      <c r="C1425">
+        <v>7340</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4">
+      <c r="A1426" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1426">
+        <v>81</v>
+      </c>
+      <c r="C1426">
+        <v>7340</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4">
+      <c r="A1427" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1427">
+        <v>82</v>
+      </c>
+      <c r="C1427">
+        <v>7310</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4">
+      <c r="A1428" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1428">
+        <v>83</v>
+      </c>
+      <c r="C1428">
+        <v>7250</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4">
+      <c r="A1429" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1429">
+        <v>84</v>
+      </c>
+      <c r="C1429">
+        <v>7180</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4">
+      <c r="A1430" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1430">
+        <v>85</v>
+      </c>
+      <c r="C1430">
+        <v>7060</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4">
+      <c r="A1431" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1431">
+        <v>86</v>
+      </c>
+      <c r="C1431">
+        <v>6920</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4">
+      <c r="A1432" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1432">
+        <v>87</v>
+      </c>
+      <c r="C1432">
+        <v>6830</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4">
+      <c r="A1433" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1433">
+        <v>88</v>
+      </c>
+      <c r="C1433">
+        <v>6720</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4">
+      <c r="A1434" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1434">
+        <v>89</v>
+      </c>
+      <c r="C1434">
+        <v>6580</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4">
+      <c r="A1435" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1435">
+        <v>90</v>
+      </c>
+      <c r="C1435">
+        <v>6470</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4">
+      <c r="A1436" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1436">
+        <v>91</v>
+      </c>
+      <c r="C1436">
+        <v>6320</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4">
+      <c r="A1437" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1437">
+        <v>92</v>
+      </c>
+      <c r="C1437">
+        <v>6170</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4">
+      <c r="A1438" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1438">
+        <v>93</v>
+      </c>
+      <c r="C1438">
+        <v>6000</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4">
+      <c r="A1439" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1439">
+        <v>94</v>
+      </c>
+      <c r="C1439">
+        <v>5840</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4">
+      <c r="A1440" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1440">
+        <v>95</v>
+      </c>
+      <c r="C1440">
+        <v>5750</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4">
+      <c r="A1441" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1441">
+        <v>96</v>
+      </c>
+      <c r="C1441">
+        <v>5640</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4">
+      <c r="A1442" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1442">
+        <v>1</v>
+      </c>
+      <c r="C1442">
+        <v>5450</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4">
+      <c r="A1443" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1443">
+        <v>2</v>
+      </c>
+      <c r="C1443">
+        <v>5390</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4">
+      <c r="A1444" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1444">
+        <v>3</v>
+      </c>
+      <c r="C1444">
+        <v>5340</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4">
+      <c r="A1445" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1445">
+        <v>4</v>
+      </c>
+      <c r="C1445">
+        <v>5290</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4">
+      <c r="A1446" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1446">
+        <v>5</v>
+      </c>
+      <c r="C1446">
+        <v>5250</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4">
+      <c r="A1447" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1447">
+        <v>6</v>
+      </c>
+      <c r="C1447">
+        <v>5210</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4">
+      <c r="A1448" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1448">
+        <v>7</v>
+      </c>
+      <c r="C1448">
+        <v>5170</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4">
+      <c r="A1449" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1449">
+        <v>8</v>
+      </c>
+      <c r="C1449">
+        <v>5140</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4">
+      <c r="A1450" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1450">
+        <v>9</v>
+      </c>
+      <c r="C1450">
+        <v>5110</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4">
+      <c r="A1451" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1451">
+        <v>10</v>
+      </c>
+      <c r="C1451">
+        <v>5090</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4">
+      <c r="A1452" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1452">
+        <v>11</v>
+      </c>
+      <c r="C1452">
+        <v>5080</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4">
+      <c r="A1453" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1453">
+        <v>12</v>
+      </c>
+      <c r="C1453">
+        <v>5080</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4">
+      <c r="A1454" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1454">
+        <v>13</v>
+      </c>
+      <c r="C1454">
+        <v>5080</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4">
+      <c r="A1455" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1455">
+        <v>14</v>
+      </c>
+      <c r="C1455">
+        <v>5090</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4">
+      <c r="A1456" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1456">
+        <v>15</v>
+      </c>
+      <c r="C1456">
+        <v>5090</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4">
+      <c r="A1457" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1457">
+        <v>16</v>
+      </c>
+      <c r="C1457">
+        <v>5100</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4">
+      <c r="A1458" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1458">
+        <v>17</v>
+      </c>
+      <c r="C1458">
+        <v>5110</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4">
+      <c r="A1459" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1459">
+        <v>18</v>
+      </c>
+      <c r="C1459">
+        <v>5130</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4">
+      <c r="A1460" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1460">
+        <v>19</v>
+      </c>
+      <c r="C1460">
+        <v>5160</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4">
+      <c r="A1461" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1461">
+        <v>20</v>
+      </c>
+      <c r="C1461">
+        <v>5210</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4">
+      <c r="A1462" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1462">
+        <v>21</v>
+      </c>
+      <c r="C1462">
+        <v>5290</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4">
+      <c r="A1463" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1463">
+        <v>22</v>
+      </c>
+      <c r="C1463">
+        <v>5390</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4">
+      <c r="A1464" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1464">
+        <v>23</v>
+      </c>
+      <c r="C1464">
+        <v>5510</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4">
+      <c r="A1465" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1465">
+        <v>24</v>
+      </c>
+      <c r="C1465">
+        <v>5650</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4">
+      <c r="A1466" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1466">
+        <v>25</v>
+      </c>
+      <c r="C1466">
+        <v>5800</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4">
+      <c r="A1467" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1467">
+        <v>26</v>
+      </c>
+      <c r="C1467">
+        <v>5960</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4">
+      <c r="A1468" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1468">
+        <v>27</v>
+      </c>
+      <c r="C1468">
+        <v>6120</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4">
+      <c r="A1469" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1469">
+        <v>28</v>
+      </c>
+      <c r="C1469">
+        <v>6260</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4">
+      <c r="A1470" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1470">
+        <v>29</v>
+      </c>
+      <c r="C1470">
+        <v>6390</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4">
+      <c r="A1471" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1471">
+        <v>30</v>
+      </c>
+      <c r="C1471">
+        <v>6490</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4">
+      <c r="A1472" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1472">
+        <v>31</v>
+      </c>
+      <c r="C1472">
+        <v>6550</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4">
+      <c r="A1473" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1473">
+        <v>32</v>
+      </c>
+      <c r="C1473">
+        <v>6590</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4">
+      <c r="A1474" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1474">
+        <v>33</v>
+      </c>
+      <c r="C1474">
+        <v>6590</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4">
+      <c r="A1475" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1475">
+        <v>34</v>
+      </c>
+      <c r="C1475">
+        <v>6560</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4">
+      <c r="A1476" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1476">
+        <v>35</v>
+      </c>
+      <c r="C1476">
+        <v>6510</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4">
+      <c r="A1477" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1477">
+        <v>36</v>
+      </c>
+      <c r="C1477">
+        <v>6430</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4">
+      <c r="A1478" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1478">
+        <v>37</v>
+      </c>
+      <c r="C1478">
+        <v>6330</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4">
+      <c r="A1479" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1479">
+        <v>38</v>
+      </c>
+      <c r="C1479">
+        <v>6220</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:4">
+      <c r="A1480" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1480">
+        <v>39</v>
+      </c>
+      <c r="C1480">
+        <v>6110</v>
+      </c>
+      <c r="D1480" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:4">
+      <c r="A1481" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1481">
+        <v>40</v>
+      </c>
+      <c r="C1481">
+        <v>6000</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:4">
+      <c r="A1482" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1482">
+        <v>41</v>
+      </c>
+      <c r="C1482">
+        <v>5890</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:4">
+      <c r="A1483" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1483">
+        <v>42</v>
+      </c>
+      <c r="C1483">
+        <v>5790</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:4">
+      <c r="A1484" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1484">
+        <v>43</v>
+      </c>
+      <c r="C1484">
+        <v>5700</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:4">
+      <c r="A1485" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1485">
+        <v>44</v>
+      </c>
+      <c r="C1485">
+        <v>5620</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:4">
+      <c r="A1486" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1486">
+        <v>45</v>
+      </c>
+      <c r="C1486">
+        <v>5550</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:4">
+      <c r="A1487" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1487">
+        <v>46</v>
+      </c>
+      <c r="C1487">
+        <v>5490</v>
+      </c>
+      <c r="D1487" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:4">
+      <c r="A1488" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1488">
+        <v>47</v>
+      </c>
+      <c r="C1488">
+        <v>5440</v>
+      </c>
+      <c r="D1488" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:4">
+      <c r="A1489" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1489">
+        <v>48</v>
+      </c>
+      <c r="C1489">
+        <v>5400</v>
+      </c>
+      <c r="D1489" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:4">
+      <c r="A1490" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1490">
+        <v>49</v>
+      </c>
+      <c r="C1490">
+        <v>5360</v>
+      </c>
+      <c r="D1490" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:4">
+      <c r="A1491" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1491">
+        <v>50</v>
+      </c>
+      <c r="C1491">
+        <v>5330</v>
+      </c>
+      <c r="D1491" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:4">
+      <c r="A1492" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1492">
+        <v>51</v>
+      </c>
+      <c r="C1492">
+        <v>5300</v>
+      </c>
+      <c r="D1492" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:4">
+      <c r="A1493" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1493">
+        <v>52</v>
+      </c>
+      <c r="C1493">
+        <v>5280</v>
+      </c>
+      <c r="D1493" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:4">
+      <c r="A1494" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1494">
+        <v>53</v>
+      </c>
+      <c r="C1494">
+        <v>5260</v>
+      </c>
+      <c r="D1494" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:4">
+      <c r="A1495" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1495">
+        <v>54</v>
+      </c>
+      <c r="C1495">
+        <v>5250</v>
+      </c>
+      <c r="D1495" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:4">
+      <c r="A1496" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1496">
+        <v>55</v>
+      </c>
+      <c r="C1496">
+        <v>5250</v>
+      </c>
+      <c r="D1496" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:4">
+      <c r="A1497" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1497">
+        <v>56</v>
+      </c>
+      <c r="C1497">
+        <v>5240</v>
+      </c>
+      <c r="D1497" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:4">
+      <c r="A1498" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1498">
+        <v>57</v>
+      </c>
+      <c r="C1498">
+        <v>5250</v>
+      </c>
+      <c r="D1498" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:4">
+      <c r="A1499" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1499">
+        <v>58</v>
+      </c>
+      <c r="C1499">
+        <v>5260</v>
+      </c>
+      <c r="D1499" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:4">
+      <c r="A1500" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1500">
+        <v>59</v>
+      </c>
+      <c r="C1500">
+        <v>5270</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:4">
+      <c r="A1501" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1501">
+        <v>60</v>
+      </c>
+      <c r="C1501">
+        <v>5290</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:4">
+      <c r="A1502" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1502">
+        <v>61</v>
+      </c>
+      <c r="C1502">
+        <v>5320</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:4">
+      <c r="A1503" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1503">
+        <v>62</v>
+      </c>
+      <c r="C1503">
+        <v>5360</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:4">
+      <c r="A1504" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1504">
+        <v>63</v>
+      </c>
+      <c r="C1504">
+        <v>5420</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:4">
+      <c r="A1505" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1505">
+        <v>64</v>
+      </c>
+      <c r="C1505">
+        <v>5490</v>
+      </c>
+      <c r="D1505" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:4">
+      <c r="A1506" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1506">
+        <v>65</v>
+      </c>
+      <c r="C1506">
+        <v>5580</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:4">
+      <c r="A1507" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1507">
+        <v>66</v>
+      </c>
+      <c r="C1507">
+        <v>5690</v>
+      </c>
+      <c r="D1507" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:4">
+      <c r="A1508" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1508">
+        <v>67</v>
+      </c>
+      <c r="C1508">
+        <v>5810</v>
+      </c>
+      <c r="D1508" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:4">
+      <c r="A1509" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1509">
+        <v>68</v>
+      </c>
+      <c r="C1509">
+        <v>5940</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:4">
+      <c r="A1510" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1510">
+        <v>69</v>
+      </c>
+      <c r="C1510">
+        <v>6080</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:4">
+      <c r="A1511" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1511">
+        <v>70</v>
+      </c>
+      <c r="C1511">
+        <v>6210</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:4">
+      <c r="A1512" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1512">
+        <v>71</v>
+      </c>
+      <c r="C1512">
+        <v>6330</v>
+      </c>
+      <c r="D1512" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:4">
+      <c r="A1513" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1513">
+        <v>72</v>
+      </c>
+      <c r="C1513">
+        <v>6440</v>
+      </c>
+      <c r="D1513" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:4">
+      <c r="A1514" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1514">
+        <v>73</v>
+      </c>
+      <c r="C1514">
+        <v>6560</v>
+      </c>
+      <c r="D1514" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:4">
+      <c r="A1515" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1515">
+        <v>74</v>
+      </c>
+      <c r="C1515">
+        <v>6680</v>
+      </c>
+      <c r="D1515" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:4">
+      <c r="A1516" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1516">
+        <v>75</v>
+      </c>
+      <c r="C1516">
+        <v>6810</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:4">
+      <c r="A1517" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1517">
+        <v>76</v>
+      </c>
+      <c r="C1517">
+        <v>6950</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:4">
+      <c r="A1518" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1518">
+        <v>77</v>
+      </c>
+      <c r="C1518">
+        <v>7090</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:4">
+      <c r="A1519" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1519">
+        <v>78</v>
+      </c>
+      <c r="C1519">
+        <v>7210</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:4">
+      <c r="A1520" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1520">
+        <v>79</v>
+      </c>
+      <c r="C1520">
+        <v>7290</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:4">
+      <c r="A1521" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1521">
+        <v>80</v>
+      </c>
+      <c r="C1521">
+        <v>7320</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:4">
+      <c r="A1522" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1522">
+        <v>81</v>
+      </c>
+      <c r="C1522">
+        <v>7320</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4">
+      <c r="A1523" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1523">
+        <v>82</v>
+      </c>
+      <c r="C1523">
+        <v>7290</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4">
+      <c r="A1524" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1524">
+        <v>83</v>
+      </c>
+      <c r="C1524">
+        <v>7230</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4">
+      <c r="A1525" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1525">
+        <v>84</v>
+      </c>
+      <c r="C1525">
+        <v>7160</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:4">
+      <c r="A1526" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1526">
+        <v>85</v>
+      </c>
+      <c r="C1526">
+        <v>7040</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:4">
+      <c r="A1527" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1527">
+        <v>86</v>
+      </c>
+      <c r="C1527">
+        <v>6900</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:4">
+      <c r="A1528" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1528">
+        <v>87</v>
+      </c>
+      <c r="C1528">
+        <v>6810</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:4">
+      <c r="A1529" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1529">
+        <v>88</v>
+      </c>
+      <c r="C1529">
+        <v>6700</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:4">
+      <c r="A1530" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1530">
+        <v>89</v>
+      </c>
+      <c r="C1530">
+        <v>6560</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:4">
+      <c r="A1531" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1531">
+        <v>90</v>
+      </c>
+      <c r="C1531">
+        <v>6450</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:4">
+      <c r="A1532" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1532">
+        <v>91</v>
+      </c>
+      <c r="C1532">
+        <v>6300</v>
+      </c>
+      <c r="D1532" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:4">
+      <c r="A1533" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1533">
+        <v>92</v>
+      </c>
+      <c r="C1533">
+        <v>6150</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:4">
+      <c r="A1534" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1534">
+        <v>93</v>
+      </c>
+      <c r="C1534">
+        <v>5980</v>
+      </c>
+      <c r="D1534" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:4">
+      <c r="A1535" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1535">
+        <v>94</v>
+      </c>
+      <c r="C1535">
+        <v>5820</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:4">
+      <c r="A1536" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1536">
+        <v>95</v>
+      </c>
+      <c r="C1536">
+        <v>5730</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4">
+      <c r="A1537" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1537">
+        <v>96</v>
+      </c>
+      <c r="C1537">
+        <v>5620</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>1539</v>
       </c>
     </row>
   </sheetData>
